--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61763F67-6824-FC4D-953F-21D72C134DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140A3142-36D1-F149-839D-45937D2A3882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2396,18 +2396,6 @@
     <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2415,6 +2403,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2426,16 +2423,19 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12567,7 +12567,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -12820,12 +12820,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>85.92</v>
-    <v>2.1190000000000002</v>
-    <v>25.89</v>
-    <v>5.8631999999999997E-2</v>
-    <v>-0.5111</v>
-    <v>-1.093E-3</v>
+    <v>99.72</v>
+    <v>2.121</v>
+    <v>-13.75</v>
+    <v>-2.9831E-2</v>
+    <v>-0.08</v>
+    <v>-1.7889999999999998E-4</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12833,26 +12833,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>468.19490000000002</v>
+    <v>472.42919999999998</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46269.900749339846</v>
+    <v>46276.999938633591</v>
     <v>4</v>
-    <v>442.15</v>
-    <v>168538495860</v>
+    <v>442.78</v>
+    <v>161226724380</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>452.22</v>
-    <v>19.255400000000002</v>
-    <v>441.57</v>
-    <v>467.46</v>
-    <v>466.94889999999998</v>
+    <v>464.16</v>
+    <v>18.986499999999999</v>
+    <v>460.93</v>
+    <v>447.18</v>
+    <v>447.1</v>
     <v>360541000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>5767493</v>
-    <v>7478900</v>
+    <v>5130471</v>
+    <v>6900971</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12874,19 +12874,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>48.12</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>0.22</v>
+    <v>4.62E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>48.12</v>
     <v>Index</v>
     <v>7</v>
-    <v>47.32</v>
+    <v>47.48</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
+    <v>47.54</v>
     <v>47.62</v>
+    <v>47.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13128,9 +13128,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13723,18 +13723,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="246" t="s">
+      <c r="B2" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="247"/>
-      <c r="E2" s="246" t="s">
+      <c r="C2" s="243"/>
+      <c r="E2" s="242" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="247"/>
-      <c r="H2" s="246" t="s">
+      <c r="F2" s="243"/>
+      <c r="H2" s="242" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="247"/>
+      <c r="I2" s="243"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>186516.53999999998</v>
+        <v>178424.82</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>185989.53999999998</v>
+        <v>177897.82</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13814,14 +13814,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>466.94889999999998</v>
+        <v>447.1</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>19.308550185873603</v>
+        <v>18.470879801734821</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13838,14 +13838,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>25.89</v>
+        <v>-13.75</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>13.867485486492763</v>
+        <v>13.265866940165647</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13862,14 +13862,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.5111</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>2.6801912581050455E-2</v>
+        <v>2.8017402511601244E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.78241599905319159</v>
+        <v>-0.77254837630798545</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13886,14 +13886,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>5.8631999999999997E-2</v>
+        <v>-2.9831E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>5.1790527531767425E-2</v>
+        <v>5.4139272776063334E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13902,14 +13902,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.093E-3</v>
+        <v>-1.7889999999999998E-4</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>2.3123954583330789E-2</v>
+        <v>2.4172645935694372E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>371</v>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>1.0696102340307192E-3</v>
+        <v>1.1181179838096517E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>85.92</v>
+        <v>99.72</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>101</v>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1190000000000002</v>
+        <v>2.121</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>103</v>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>7478900</v>
+        <v>6900971</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.8254866833793938E-3</v>
+        <v>2.9536249497127136E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14002,10 +14002,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="248" t="s">
+      <c r="B17" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="248"/>
+      <c r="C17" s="244"/>
       <c r="E17" s="184" t="s">
         <v>300</v>
       </c>
@@ -14078,14 +14078,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="248" t="s">
+      <c r="B25" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="248"/>
-      <c r="E25" s="246" t="s">
+      <c r="C25" s="244"/>
+      <c r="E25" s="242" t="s">
         <v>345</v>
       </c>
-      <c r="F25" s="247"/>
+      <c r="F25" s="243"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14134,15 +14134,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="243" t="s">
+      <c r="B33" s="245" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
+      <c r="C33" s="245"/>
+      <c r="D33" s="245"/>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14209,24 +14209,24 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="243"/>
-      <c r="C46" s="243"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="243"/>
-      <c r="F46" s="243"/>
-      <c r="G46" s="243"/>
-      <c r="H46" s="243"/>
+      <c r="B46" s="245"/>
+      <c r="C46" s="245"/>
+      <c r="D46" s="245"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
+      <c r="G46" s="245"/>
+      <c r="H46" s="245"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="245" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="243"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="243"/>
-      <c r="F49" s="243"/>
-      <c r="G49" s="243"/>
-      <c r="H49" s="243"/>
+      <c r="C49" s="245"/>
+      <c r="D49" s="245"/>
+      <c r="E49" s="245"/>
+      <c r="F49" s="245"/>
+      <c r="G49" s="245"/>
+      <c r="H49" s="245"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="41" t="s">
@@ -14321,24 +14321,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="243"/>
-      <c r="C66" s="243"/>
-      <c r="D66" s="243"/>
-      <c r="E66" s="243"/>
-      <c r="F66" s="243"/>
-      <c r="G66" s="243"/>
-      <c r="H66" s="243"/>
+      <c r="B66" s="245"/>
+      <c r="C66" s="245"/>
+      <c r="D66" s="245"/>
+      <c r="E66" s="245"/>
+      <c r="F66" s="245"/>
+      <c r="G66" s="245"/>
+      <c r="H66" s="245"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="243" t="s">
+      <c r="B69" s="245" t="s">
         <v>108</v>
       </c>
-      <c r="C69" s="243"/>
-      <c r="D69" s="243"/>
-      <c r="E69" s="243"/>
-      <c r="F69" s="243"/>
-      <c r="G69" s="243"/>
-      <c r="H69" s="243"/>
+      <c r="C69" s="245"/>
+      <c r="D69" s="245"/>
+      <c r="E69" s="245"/>
+      <c r="F69" s="245"/>
+      <c r="G69" s="245"/>
+      <c r="H69" s="245"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -14353,28 +14353,28 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="243"/>
-      <c r="C76" s="243"/>
-      <c r="D76" s="243"/>
-      <c r="E76" s="243"/>
-      <c r="F76" s="243"/>
-      <c r="G76" s="243"/>
-      <c r="H76" s="243"/>
+      <c r="B76" s="245"/>
+      <c r="C76" s="245"/>
+      <c r="D76" s="245"/>
+      <c r="E76" s="245"/>
+      <c r="F76" s="245"/>
+      <c r="G76" s="245"/>
+      <c r="H76" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14444,36 +14444,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
+      <c r="AA2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="245"/>
+      <c r="AC2" s="245"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14484,32 +14484,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="254" t="s">
+      <c r="S4" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="255"/>
-      <c r="U4" s="255"/>
-      <c r="V4" s="255"/>
-      <c r="W4" s="255"/>
-      <c r="X4" s="255"/>
-      <c r="Y4" s="255"/>
-      <c r="Z4" s="255"/>
-      <c r="AA4" s="255"/>
-      <c r="AB4" s="255"/>
-      <c r="AC4" s="255"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14999,33 +14999,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="254" t="s">
+      <c r="S11" s="252" t="s">
         <v>121</v>
       </c>
-      <c r="T11" s="255"/>
-      <c r="U11" s="255"/>
-      <c r="V11" s="255"/>
-      <c r="W11" s="255"/>
-      <c r="X11" s="255"/>
-      <c r="Y11" s="255"/>
-      <c r="Z11" s="255"/>
-      <c r="AA11" s="255"/>
-      <c r="AB11" s="255"/>
-      <c r="AC11" s="255"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
+      <c r="AA11" s="253"/>
+      <c r="AB11" s="253"/>
+      <c r="AC11" s="253"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15456,32 +15456,32 @@
     <row r="19" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="86"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="242" t="s">
+      <c r="C19" s="251" t="s">
         <v>423</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="E19" s="242"/>
-      <c r="F19" s="242"/>
-      <c r="G19" s="242"/>
-      <c r="H19" s="242"/>
-      <c r="I19" s="242"/>
-      <c r="J19" s="242"/>
-      <c r="K19" s="242"/>
-      <c r="L19" s="242"/>
+      <c r="D19" s="251"/>
+      <c r="E19" s="251"/>
+      <c r="F19" s="251"/>
+      <c r="G19" s="251"/>
+      <c r="H19" s="251"/>
+      <c r="I19" s="251"/>
+      <c r="J19" s="251"/>
+      <c r="K19" s="251"/>
+      <c r="L19" s="251"/>
       <c r="O19" s="5"/>
-      <c r="S19" s="254" t="s">
+      <c r="S19" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="T19" s="255"/>
-      <c r="U19" s="255"/>
-      <c r="V19" s="255"/>
-      <c r="W19" s="255"/>
-      <c r="X19" s="255"/>
-      <c r="Y19" s="255"/>
-      <c r="Z19" s="255"/>
-      <c r="AA19" s="255"/>
-      <c r="AB19" s="255"/>
-      <c r="AC19" s="255"/>
+      <c r="T19" s="253"/>
+      <c r="U19" s="253"/>
+      <c r="V19" s="253"/>
+      <c r="W19" s="253"/>
+      <c r="X19" s="253"/>
+      <c r="Y19" s="253"/>
+      <c r="Z19" s="253"/>
+      <c r="AA19" s="253"/>
+      <c r="AB19" s="253"/>
+      <c r="AC19" s="253"/>
       <c r="AE19" s="87"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
@@ -15976,35 +15976,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="P2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="245"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16013,31 +16013,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="P4" s="255" t="s">
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="P4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="255"/>
-      <c r="R4" s="255"/>
-      <c r="S4" s="255"/>
-      <c r="T4" s="255"/>
-      <c r="U4" s="255"/>
-      <c r="V4" s="255"/>
-      <c r="W4" s="255"/>
-      <c r="X4" s="255"/>
-      <c r="Y4" s="255"/>
-      <c r="Z4" s="255"/>
+      <c r="Q4" s="253"/>
+      <c r="R4" s="253"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -16232,32 +16232,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="251" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="255" t="s">
+      <c r="P9" s="253" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="255"/>
-      <c r="R9" s="255"/>
-      <c r="S9" s="255"/>
-      <c r="T9" s="255"/>
-      <c r="U9" s="255"/>
-      <c r="V9" s="255"/>
-      <c r="W9" s="255"/>
-      <c r="X9" s="255"/>
-      <c r="Y9" s="255"/>
-      <c r="Z9" s="255"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
+      <c r="T9" s="253"/>
+      <c r="U9" s="253"/>
+      <c r="V9" s="253"/>
+      <c r="W9" s="253"/>
+      <c r="X9" s="253"/>
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16734,31 +16734,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="242" t="s">
+      <c r="C17" s="251" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
-      <c r="P17" s="255" t="s">
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
+      <c r="P17" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="255"/>
-      <c r="R17" s="255"/>
-      <c r="S17" s="255"/>
-      <c r="T17" s="255"/>
-      <c r="U17" s="255"/>
-      <c r="V17" s="255"/>
-      <c r="W17" s="255"/>
-      <c r="X17" s="255"/>
-      <c r="Y17" s="255"/>
-      <c r="Z17" s="255"/>
+      <c r="Q17" s="253"/>
+      <c r="R17" s="253"/>
+      <c r="S17" s="253"/>
+      <c r="T17" s="253"/>
+      <c r="U17" s="253"/>
+      <c r="V17" s="253"/>
+      <c r="W17" s="253"/>
+      <c r="X17" s="253"/>
+      <c r="Y17" s="253"/>
+      <c r="Z17" s="253"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17236,20 +17236,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -17267,18 +17267,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -17475,18 +17475,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="242" t="s">
+      <c r="C11" s="251" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
       <c r="P11" s="256"/>
       <c r="Q11" s="256"/>
@@ -17740,18 +17740,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="251" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17969,18 +17969,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="242" t="s">
+      <c r="C26" s="251" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
-      <c r="F26" s="242"/>
-      <c r="G26" s="242"/>
-      <c r="H26" s="242"/>
-      <c r="I26" s="242"/>
-      <c r="J26" s="242"/>
-      <c r="K26" s="242"/>
-      <c r="L26" s="242"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18172,18 +18172,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="242" t="s">
+      <c r="C33" s="251" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="242"/>
-      <c r="E33" s="242"/>
-      <c r="F33" s="242"/>
-      <c r="G33" s="242"/>
-      <c r="H33" s="242"/>
-      <c r="I33" s="242"/>
-      <c r="J33" s="242"/>
-      <c r="K33" s="242"/>
-      <c r="L33" s="242"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18367,18 +18367,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="242" t="s">
+      <c r="C40" s="251" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="242"/>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
-      <c r="G40" s="242"/>
-      <c r="H40" s="242"/>
-      <c r="I40" s="242"/>
-      <c r="J40" s="242"/>
-      <c r="K40" s="242"/>
-      <c r="L40" s="242"/>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="251"/>
+      <c r="G40" s="251"/>
+      <c r="H40" s="251"/>
+      <c r="I40" s="251"/>
+      <c r="J40" s="251"/>
+      <c r="K40" s="251"/>
+      <c r="L40" s="251"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18642,6 +18642,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18649,12 +18655,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18692,20 +18692,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
       <c r="S2" s="256"/>
       <c r="T2" s="256"/>
       <c r="U2" s="256"/>
@@ -18723,18 +18723,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="S4" s="256"/>
       <c r="T4" s="256"/>
       <c r="U4" s="256"/>
@@ -19108,18 +19108,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="242" t="s">
+      <c r="C13" s="251" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="242"/>
-      <c r="G13" s="242"/>
-      <c r="H13" s="242"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="251"/>
+      <c r="L13" s="251"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19212,18 +19212,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="242" t="s">
+      <c r="C18" s="251" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19415,18 +19415,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="242" t="s">
+      <c r="C25" s="251" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
-      <c r="F25" s="242"/>
-      <c r="G25" s="242"/>
-      <c r="H25" s="242"/>
-      <c r="I25" s="242"/>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242"/>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="251"/>
+      <c r="G25" s="251"/>
+      <c r="H25" s="251"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="251"/>
+      <c r="K25" s="251"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19564,18 +19564,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="242" t="s">
+      <c r="C31" s="251" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="242"/>
-      <c r="G31" s="242"/>
-      <c r="H31" s="242"/>
-      <c r="I31" s="242"/>
-      <c r="J31" s="242"/>
-      <c r="K31" s="242"/>
-      <c r="L31" s="242"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19714,16 +19714,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19786,10 +19786,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="245" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="245"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19806,7 +19806,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>186516.53999999998</v>
+        <v>178424.82</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.7840000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1190000000000002</v>
+        <v>2.121</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="C11" s="135">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19874,10 +19874,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="245" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="245"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.6086164556167044E-3</v>
+        <v>5.8614811650886164E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99439138354438328</v>
+        <v>0.99413851883491133</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14297500000000002</v>
+        <v>0.14116399999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14232818630725602</v>
+        <v>0.14049863982702609</v>
       </c>
     </row>
   </sheetData>
@@ -19966,20 +19966,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -19997,18 +19997,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -20265,10 +20265,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="245" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="245"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20288,10 +20288,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="245" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="245"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20405,37 +20405,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20624,18 +20624,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="242" t="s">
+      <c r="C10" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="242"/>
-      <c r="E10" s="242"/>
-      <c r="F10" s="242"/>
-      <c r="G10" s="242"/>
-      <c r="H10" s="242"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="242"/>
-      <c r="K10" s="242"/>
-      <c r="L10" s="242"/>
+      <c r="D10" s="251"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="251"/>
+      <c r="H10" s="251"/>
+      <c r="I10" s="251"/>
+      <c r="J10" s="251"/>
+      <c r="K10" s="251"/>
+      <c r="L10" s="251"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20829,18 +20829,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="242" t="s">
+      <c r="C16" s="251" t="s">
         <v>195</v>
       </c>
-      <c r="D16" s="242"/>
-      <c r="E16" s="242"/>
-      <c r="F16" s="242"/>
-      <c r="G16" s="242"/>
-      <c r="H16" s="242"/>
-      <c r="I16" s="242"/>
-      <c r="J16" s="242"/>
-      <c r="K16" s="242"/>
-      <c r="L16" s="242"/>
+      <c r="D16" s="251"/>
+      <c r="E16" s="251"/>
+      <c r="F16" s="251"/>
+      <c r="G16" s="251"/>
+      <c r="H16" s="251"/>
+      <c r="I16" s="251"/>
+      <c r="J16" s="251"/>
+      <c r="K16" s="251"/>
+      <c r="L16" s="251"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20974,18 +20974,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="242" t="s">
+      <c r="C21" s="251" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="E21" s="242"/>
-      <c r="F21" s="242"/>
-      <c r="G21" s="242"/>
-      <c r="H21" s="242"/>
-      <c r="I21" s="242"/>
-      <c r="J21" s="242"/>
-      <c r="K21" s="242"/>
-      <c r="L21" s="242"/>
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="251"/>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21069,18 +21069,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="242" t="s">
+      <c r="C26" s="251" t="s">
         <v>199</v>
       </c>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
-      <c r="F26" s="242"/>
-      <c r="G26" s="242"/>
-      <c r="H26" s="242"/>
-      <c r="I26" s="242"/>
-      <c r="J26" s="242"/>
-      <c r="K26" s="242"/>
-      <c r="L26" s="242"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21350,10 +21350,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="245" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="243"/>
+      <c r="C37" s="245"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21446,10 +21446,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="245" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="243"/>
+      <c r="C49" s="245"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21505,10 +21505,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="243" t="s">
+      <c r="B57" s="245" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="243"/>
+      <c r="C57" s="245"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21648,10 +21648,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="245" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="245"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21705,7 +21705,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.78241599905319159</v>
+        <v>-0.77254837630798545</v>
       </c>
     </row>
   </sheetData>
@@ -21770,37 +21770,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21913,18 +21913,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="242" t="s">
+      <c r="C9" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22045,18 +22045,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="242" t="s">
+      <c r="C14" s="251" t="s">
         <v>374</v>
       </c>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+      <c r="K14" s="251"/>
+      <c r="L14" s="251"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22146,10 +22146,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="245" t="s">
         <v>376</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="245"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22250,20 +22250,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -22281,18 +22281,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="P5" s="256"/>
       <c r="Q5" s="256"/>
       <c r="R5" s="256"/>
@@ -22543,7 +22543,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>168753.06</v>
+        <v>161431.98000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>168226.06</v>
+        <v>160904.98000000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22719,18 +22719,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="242" t="s">
+      <c r="C39" s="251" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="242"/>
-      <c r="E39" s="242"/>
-      <c r="F39" s="242"/>
-      <c r="G39" s="242"/>
-      <c r="H39" s="242"/>
-      <c r="I39" s="242"/>
-      <c r="J39" s="242"/>
-      <c r="K39" s="242"/>
-      <c r="L39" s="242"/>
+      <c r="D39" s="251"/>
+      <c r="E39" s="251"/>
+      <c r="F39" s="251"/>
+      <c r="G39" s="251"/>
+      <c r="H39" s="251"/>
+      <c r="I39" s="251"/>
+      <c r="J39" s="251"/>
+      <c r="K39" s="251"/>
+      <c r="L39" s="251"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23162,17 +23162,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29902,7 +29902,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31345,7 +31345,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>19.308550185873603</v>
+        <v>18.470879801734821</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31386,7 +31386,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>13.867485486492763</v>
+        <v>13.265866940165647</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>19.038025722021661</v>
+        <v>18.212091606498195</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>186516.53999999998</v>
+        <v>178424.82</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31581,7 +31581,7 @@
       </c>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>185989.53999999998</v>
+        <v>177897.82</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31622,7 +31622,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>14.396589519312638</v>
+        <v>13.770246923136467</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31663,7 +31663,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>41.767244554233095</v>
+        <v>39.950105546822371</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31810,7 +31810,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>37.310770154030799</v>
+        <v>35.692102420484098</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31851,7 +31851,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="204"/>
-        <v>52.159912199210972</v>
+        <v>49.890626492387895</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31892,7 +31892,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>2.6801912581050455E-2</v>
+        <v>2.8017402511601244E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31933,7 +31933,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>5.1790527531767425E-2</v>
+        <v>5.4139272776063334E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31974,7 +31974,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>1.0696102340307192E-3</v>
+        <v>1.1181179838096517E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32015,7 +32015,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>2.3123954583330789E-2</v>
+        <v>2.4172645935694372E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32056,7 +32056,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.4651969203374674E-2</v>
+        <v>2.576995734113673E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32603,7 +32603,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.8254866833793938E-3</v>
+        <v>2.9536249497127136E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -34041,15 +34041,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="245" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="245"/>
+      <c r="E4" s="245" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34057,7 +34057,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>186516.53999999998</v>
+        <v>178424.82</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34093,7 +34093,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>185989.53999999998</v>
+        <v>177897.82</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>19.308550185873603</v>
+        <v>18.470879801734821</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -34133,7 +34133,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>13.867485486492763</v>
+        <v>13.265866940165647</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -34153,7 +34153,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>19.038025722021661</v>
+        <v>18.212091606498195</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>14.396589519312638</v>
+        <v>13.770246923136467</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34182,18 +34182,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>41.767244554233095</v>
+        <v>39.950105546822371</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="245" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="245"/>
+      <c r="E15" s="245" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34244,14 +34244,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="245" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="245"/>
+      <c r="E21" s="245" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="245"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34320,14 +34320,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="245" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="245"/>
+      <c r="E29" s="245" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="245"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34403,14 +34403,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="245" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="245"/>
+      <c r="E37" s="245" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="245"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>5.1790527531767425E-2</v>
+        <v>5.4139272776063334E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -34434,7 +34434,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>2.6801912581050455E-2</v>
+        <v>2.8017402511601244E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.0696102340307192E-3</v>
+        <v>1.1181179838096517E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -34466,7 +34466,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.3123954583330789E-2</v>
+        <v>2.4172645935694372E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34475,18 +34475,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.4651969203374674E-2</v>
+        <v>2.576995734113673E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="245" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="245"/>
+      <c r="E45" s="245" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="245"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34519,18 +34519,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>2.8254866833793938E-3</v>
+        <v>2.9536249497127136E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="245" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="245"/>
+      <c r="E51" s="245" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="245"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34698,7 +34698,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>467.46</v>
+        <v>447.18</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34727,7 +34727,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>186516.53999999998</v>
+        <v>178424.82</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34756,7 +34756,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>185989.53999999998</v>
+        <v>177897.82</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34785,7 +34785,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>19.308550185873603</v>
+        <v>18.470879801734821</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>13.867485486492763</v>
+        <v>13.265866940165647</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34843,7 +34843,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>19.038025722021661</v>
+        <v>18.212091606498195</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34872,7 +34872,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>14.396589519312638</v>
+        <v>13.770246923136467</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34901,7 +34901,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>41.767244554233095</v>
+        <v>39.950105546822371</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>5.1790527531767425E-2</v>
+        <v>5.4139272776063334E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35703,7 +35703,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>2.6801912581050455E-2</v>
+        <v>2.8017402511601244E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35732,7 +35732,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.0696102340307192E-3</v>
+        <v>1.1181179838096517E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35761,7 +35761,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.3123954583330789E-2</v>
+        <v>2.4172645935694372E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35790,7 +35790,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.4651969203374674E-2</v>
+        <v>2.576995734113673E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36026,7 +36026,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>2.8254866833793938E-3</v>
+        <v>2.9536249497127136E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36515,14 +36515,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="248" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36589,19 +36589,19 @@
       <c r="B7" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="252">
+      <c r="C7" s="246">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="253"/>
-      <c r="F7" s="252">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="253"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36628,19 +36628,19 @@
       <c r="B9" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="252">
+      <c r="C9" s="246">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="253"/>
-      <c r="F9" s="252">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="253"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36667,19 +36667,19 @@
       <c r="B11" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="252">
+      <c r="C11" s="246">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="253"/>
-      <c r="F11" s="252">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="253"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36706,19 +36706,19 @@
       <c r="B13" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="252">
+      <c r="C13" s="246">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="253"/>
-      <c r="F13" s="252">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="253"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36745,19 +36745,19 @@
       <c r="B15" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="252">
+      <c r="C15" s="246">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="253"/>
-      <c r="F15" s="252">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="253"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36784,19 +36784,19 @@
       <c r="B17" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="252">
+      <c r="C17" s="246">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="253"/>
-      <c r="F17" s="252">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="253"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36823,22 +36823,22 @@
       <c r="B19" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="252">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="253"/>
-      <c r="F19" s="252">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="253"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36865,22 +36865,22 @@
       <c r="B21" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="252">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="253"/>
-      <c r="F21" s="252">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="253"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36929,22 +36929,22 @@
       <c r="B25" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="252">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="253"/>
-      <c r="F25" s="252">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="253"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36972,22 +36972,22 @@
       <c r="B27" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="252">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="253"/>
-      <c r="F27" s="252">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="253"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37015,49 +37015,49 @@
       <c r="B29" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="252">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="253"/>
-      <c r="F29" s="252">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="253"/>
+      <c r="G29" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140A3142-36D1-F149-839D-45937D2A3882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60BA008-79EF-444A-B337-EAD7A9D0591C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2396,6 +2426,9 @@
     <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2405,15 +2438,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2421,6 +2445,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12782,7 +12812,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12820,12 +12850,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>99.72</v>
-    <v>2.121</v>
-    <v>-13.75</v>
-    <v>-2.9831E-2</v>
-    <v>-0.08</v>
-    <v>-1.7889999999999998E-4</v>
+    <v>105.42</v>
+    <v>2.1177000000000001</v>
+    <v>11.994999999999999</v>
+    <v>2.6764E-2</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12833,36 +12861,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>472.42919999999998</v>
+    <v>474.54</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46276.999938633591</v>
+    <v>46287.764522476566</v>
     <v>4</v>
-    <v>442.78</v>
-    <v>161226724380</v>
+    <v>438</v>
+    <v>165908349265</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>464.16</v>
-    <v>18.986499999999999</v>
-    <v>460.93</v>
-    <v>447.18</v>
-    <v>447.1</v>
+    <v>438.58</v>
+    <v>18.954899999999999</v>
+    <v>448.17</v>
+    <v>460.16500000000002</v>
     <v>360541000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>5130471</v>
-    <v>6900971</v>
+    <v>5156355</v>
+    <v>6519780</v>
     <v>2000</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12874,30 +12916,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.12</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.62E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>48.12</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>7</v>
-    <v>47.48</v>
+    <v>10</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.54</v>
-    <v>47.62</v>
-    <v>47.84</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12931,8 +12973,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12954,7 +12994,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12964,6 +13003,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12999,7 +13043,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13010,16 +13054,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13120,19 +13161,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13213,9 +13248,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13223,9 +13255,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13723,18 +13752,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="242" t="s">
+      <c r="B2" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="243"/>
-      <c r="E2" s="242" t="s">
+      <c r="C2" s="244"/>
+      <c r="E2" s="243" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="243"/>
-      <c r="H2" s="242" t="s">
+      <c r="F2" s="244"/>
+      <c r="H2" s="243" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="243"/>
+      <c r="I2" s="244"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13749,7 +13778,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>178424.82</v>
+        <v>183605.83500000002</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13773,7 +13802,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>177897.82</v>
+        <v>183078.83500000002</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13790,7 +13819,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13812,16 +13841,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>447.1</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>18.470879801734821</v>
+        <v>19.007228418009088</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13838,14 +13867,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-13.75</v>
+        <v>11.994999999999999</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>13.265866940165647</v>
+        <v>13.651074870346003</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13860,16 +13889,16 @@
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.08</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>2.8017402511601244E-2</v>
+        <v>2.7226803549026637E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13877,7 +13906,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.77254837630798545</v>
+        <v>-0.77896663787425147</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13886,30 +13915,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.9831E-2</v>
+        <v>2.6764E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>5.4139272776063334E-2</v>
+        <v>5.2611563243619139E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.7889999999999998E-4</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>2.4172645935694372E-2</v>
+        <v>2.3490538849160209E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>371</v>
@@ -13932,7 +13961,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>1.1181179838096517E-3</v>
+        <v>1.0865667749611551E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13941,7 +13970,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>99.72</v>
+        <v>105.42</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>101</v>
@@ -13957,7 +13986,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.121</v>
+        <v>2.1177000000000001</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>103</v>
@@ -13973,7 +14002,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>6900971</v>
+        <v>6519780</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13989,7 +14018,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.9536249497127136E-3</v>
+        <v>2.8702791498973874E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14002,10 +14031,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="244" t="s">
+      <c r="B17" s="245" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="244"/>
+      <c r="C17" s="245"/>
       <c r="E17" s="184" t="s">
         <v>300</v>
       </c>
@@ -14078,14 +14107,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="244" t="s">
+      <c r="B25" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="244"/>
-      <c r="E25" s="242" t="s">
+      <c r="C25" s="245"/>
+      <c r="E25" s="243" t="s">
         <v>345</v>
       </c>
-      <c r="F25" s="243"/>
+      <c r="F25" s="244"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14094,12 +14123,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.84</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14114,7 +14143,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14134,15 +14163,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="245" t="s">
+      <c r="B33" s="242" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="245"/>
-      <c r="D33" s="245"/>
-      <c r="E33" s="245"/>
-      <c r="F33" s="245"/>
-      <c r="G33" s="245"/>
-      <c r="H33" s="245"/>
+      <c r="C33" s="242"/>
+      <c r="D33" s="242"/>
+      <c r="E33" s="242"/>
+      <c r="F33" s="242"/>
+      <c r="G33" s="242"/>
+      <c r="H33" s="242"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14209,24 +14238,24 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="245"/>
-      <c r="C46" s="245"/>
-      <c r="D46" s="245"/>
-      <c r="E46" s="245"/>
-      <c r="F46" s="245"/>
-      <c r="G46" s="245"/>
-      <c r="H46" s="245"/>
+      <c r="B46" s="242"/>
+      <c r="C46" s="242"/>
+      <c r="D46" s="242"/>
+      <c r="E46" s="242"/>
+      <c r="F46" s="242"/>
+      <c r="G46" s="242"/>
+      <c r="H46" s="242"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="245" t="s">
+      <c r="B49" s="242" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="245"/>
-      <c r="D49" s="245"/>
-      <c r="E49" s="245"/>
-      <c r="F49" s="245"/>
-      <c r="G49" s="245"/>
-      <c r="H49" s="245"/>
+      <c r="C49" s="242"/>
+      <c r="D49" s="242"/>
+      <c r="E49" s="242"/>
+      <c r="F49" s="242"/>
+      <c r="G49" s="242"/>
+      <c r="H49" s="242"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="41" t="s">
@@ -14321,24 +14350,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="245"/>
-      <c r="C66" s="245"/>
-      <c r="D66" s="245"/>
-      <c r="E66" s="245"/>
-      <c r="F66" s="245"/>
-      <c r="G66" s="245"/>
-      <c r="H66" s="245"/>
+      <c r="B66" s="242"/>
+      <c r="C66" s="242"/>
+      <c r="D66" s="242"/>
+      <c r="E66" s="242"/>
+      <c r="F66" s="242"/>
+      <c r="G66" s="242"/>
+      <c r="H66" s="242"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="245" t="s">
+      <c r="B69" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="C69" s="245"/>
-      <c r="D69" s="245"/>
-      <c r="E69" s="245"/>
-      <c r="F69" s="245"/>
-      <c r="G69" s="245"/>
-      <c r="H69" s="245"/>
+      <c r="C69" s="242"/>
+      <c r="D69" s="242"/>
+      <c r="E69" s="242"/>
+      <c r="F69" s="242"/>
+      <c r="G69" s="242"/>
+      <c r="H69" s="242"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -14353,28 +14382,28 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="245"/>
-      <c r="C76" s="245"/>
-      <c r="D76" s="245"/>
-      <c r="E76" s="245"/>
-      <c r="F76" s="245"/>
-      <c r="G76" s="245"/>
-      <c r="H76" s="245"/>
+      <c r="B76" s="242"/>
+      <c r="C76" s="242"/>
+      <c r="D76" s="242"/>
+      <c r="E76" s="242"/>
+      <c r="F76" s="242"/>
+      <c r="G76" s="242"/>
+      <c r="H76" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B76:H76"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14444,36 +14473,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="245" t="s">
+      <c r="S2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245"/>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
-      <c r="AA2" s="245" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="245"/>
-      <c r="AC2" s="245"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15976,35 +16005,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
-      <c r="P2" s="245" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="245"/>
-      <c r="R2" s="245"/>
-      <c r="S2" s="245"/>
-      <c r="T2" s="245"/>
-      <c r="U2" s="245"/>
-      <c r="V2" s="245"/>
-      <c r="W2" s="245"/>
-      <c r="X2" s="245" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -17236,20 +17265,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
       <c r="G3" s="254"/>
       <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="245"/>
-      <c r="J3" s="245"/>
-      <c r="K3" s="245"/>
-      <c r="L3" s="245"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -18642,12 +18671,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18655,6 +18678,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18692,20 +18721,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="S2" s="256"/>
       <c r="T2" s="256"/>
       <c r="U2" s="256"/>
@@ -19168,24 +19197,24 @@
         <v>72</v>
       </c>
       <c r="C15" s="129">
-        <f>-Statement!M82</f>
-        <v>-0.29345266132830899</v>
+        <f>Statement!M82</f>
+        <v>0.29345266132830899</v>
       </c>
       <c r="D15" s="129">
-        <f>-Statement!N82</f>
+        <f>Statement!N82</f>
         <v>0</v>
       </c>
       <c r="E15" s="129">
-        <f>-Statement!O82</f>
+        <f>Statement!O82</f>
         <v>0</v>
       </c>
       <c r="F15" s="129">
-        <f>-Statement!P82</f>
+        <f>Statement!P82</f>
         <v>0</v>
       </c>
       <c r="G15" s="130">
-        <f>-Statement!Q82</f>
-        <v>-4.8561332660272592E-2</v>
+        <f>Statement!Q82</f>
+        <v>4.8561332660272592E-2</v>
       </c>
       <c r="H15" s="129">
         <f>Overview!$C$26</f>
@@ -19479,7 +19508,7 @@
       </c>
       <c r="C27" s="126">
         <f>C10*(1-C15)</f>
-        <v>3092.645313235987</v>
+        <v>1689.354686764013</v>
       </c>
       <c r="D27" s="126">
         <f t="shared" ref="D27:L27" si="6">D10*(1-D15)</f>
@@ -19495,7 +19524,7 @@
       </c>
       <c r="G27" s="131">
         <f t="shared" si="6"/>
-        <v>4669.2436143361938</v>
+        <v>4236.7563856638062</v>
       </c>
       <c r="H27" s="126">
         <f t="shared" si="6"/>
@@ -19524,7 +19553,7 @@
       </c>
       <c r="C28" s="94">
         <f>C27+C20-C21+C22</f>
-        <v>1824.645313235987</v>
+        <v>421.35468676401297</v>
       </c>
       <c r="D28" s="94">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
@@ -19540,7 +19569,7 @@
       </c>
       <c r="G28" s="127">
         <f t="shared" si="7"/>
-        <v>3968.2436143361938</v>
+        <v>3535.7563856638062</v>
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
@@ -19714,16 +19743,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19786,10 +19815,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="245" t="s">
+      <c r="B4" s="242" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="245"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19806,7 +19835,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19815,7 +19844,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>178424.82</v>
+        <v>183605.83500000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19833,7 +19862,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.7840000000000001E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19842,7 +19871,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.121</v>
+        <v>2.1177000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19874,10 +19903,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="245" t="s">
+      <c r="B15" s="242" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="245"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19885,7 +19914,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.8614811650886164E-3</v>
+        <v>5.697023362155198E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19894,7 +19923,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99413851883491133</v>
+        <v>0.99430297663784484</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19912,7 +19941,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14116399999999998</v>
+        <v>0.14280880000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19921,7 +19950,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14049863982702609</v>
+        <v>0.14215273762604225</v>
       </c>
     </row>
   </sheetData>
@@ -19966,20 +19995,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
       <c r="G3" s="254"/>
       <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="245"/>
-      <c r="J3" s="245"/>
-      <c r="K3" s="245"/>
-      <c r="L3" s="245"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -20086,7 +20115,7 @@
       </c>
       <c r="C7" s="112">
         <f>'FCF &amp; Other'!C28</f>
-        <v>1824.645313235987</v>
+        <v>421.35468676401297</v>
       </c>
       <c r="D7" s="112">
         <f>'FCF &amp; Other'!D28</f>
@@ -20102,7 +20131,7 @@
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3968.2436143361938</v>
+        <v>3535.7563856638062</v>
       </c>
       <c r="H7" s="112">
         <f>'FCF &amp; Other'!H28</f>
@@ -20265,10 +20294,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="245" t="s">
+      <c r="B13" s="242" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="245"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20288,10 +20317,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="245" t="s">
+      <c r="B18" s="242" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="245"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20405,20 +20434,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20580,7 +20609,7 @@
       </c>
       <c r="C8" s="92">
         <f>'FCF &amp; Other'!C28</f>
-        <v>1824.645313235987</v>
+        <v>421.35468676401297</v>
       </c>
       <c r="D8" s="92">
         <f>'FCF &amp; Other'!D28</f>
@@ -20596,7 +20625,7 @@
       </c>
       <c r="G8" s="93">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3968.2436143361938</v>
+        <v>3535.7563856638062</v>
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
@@ -20786,7 +20815,7 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>-1.2460752217118316</v>
+        <v>-2.0656105511684277</v>
       </c>
       <c r="E14" s="95">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
@@ -20801,11 +20830,11 @@
       </c>
       <c r="G14" s="96">
         <f t="shared" si="3"/>
-        <v>1.9569624547959714</v>
+        <v>1.6346917925959807</v>
       </c>
       <c r="H14" s="95">
         <f t="shared" si="3"/>
-        <v>-1.6357718957062378E-2</v>
+        <v>0.10395959867775496</v>
       </c>
       <c r="I14" s="95">
         <f t="shared" si="3"/>
@@ -21318,7 +21347,7 @@
       </c>
       <c r="C34" s="149">
         <f>C32/C8</f>
-        <v>10.644282732163019</v>
+        <v>46.094279261874334</v>
       </c>
       <c r="D34" s="149">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
@@ -21334,7 +21363,7 @@
       </c>
       <c r="G34" s="150">
         <f t="shared" si="13"/>
-        <v>52.587393836388685</v>
+        <v>59.019787288499579</v>
       </c>
       <c r="H34" s="137"/>
       <c r="I34" s="137"/>
@@ -21350,10 +21379,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="245" t="s">
+      <c r="B37" s="242" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="245"/>
+      <c r="C37" s="242"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21446,10 +21475,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="245" t="s">
+      <c r="B49" s="242" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="245"/>
+      <c r="C49" s="242"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21505,10 +21534,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="245" t="s">
+      <c r="B57" s="242" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="245"/>
+      <c r="C57" s="242"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21648,10 +21677,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="245" t="s">
+      <c r="B4" s="242" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="245"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21705,7 +21734,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21714,7 +21743,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.77254837630798545</v>
+        <v>-0.77896663787425147</v>
       </c>
     </row>
   </sheetData>
@@ -21770,20 +21799,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="245" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="245"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="G2" s="254"/>
       <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="245"/>
-      <c r="J2" s="245"/>
-      <c r="K2" s="245"/>
-      <c r="L2" s="245"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22146,10 +22175,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="245" t="s">
+      <c r="B20" s="242" t="s">
         <v>376</v>
       </c>
-      <c r="C20" s="245"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22250,20 +22279,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="E3" s="245"/>
-      <c r="F3" s="245"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
       <c r="G3" s="254"/>
       <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="245"/>
-      <c r="J3" s="245"/>
-      <c r="K3" s="245"/>
-      <c r="L3" s="245"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
       <c r="P3" s="256"/>
       <c r="Q3" s="256"/>
       <c r="R3" s="256"/>
@@ -22370,7 +22399,7 @@
       </c>
       <c r="C7" s="112">
         <f>'FCF &amp; Other'!C28</f>
-        <v>1824.645313235987</v>
+        <v>421.35468676401297</v>
       </c>
       <c r="D7" s="112">
         <f>'FCF &amp; Other'!D28</f>
@@ -22386,27 +22415,27 @@
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3968.2436143361938</v>
+        <v>3535.7563856638062</v>
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>5277.7640070671378</v>
+        <v>4702.5559929328629</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>7019.426129399294</v>
+        <v>6254.3994706007079</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>9335.8367521010623</v>
+        <v>8318.3512958989413</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>12416.662880294414</v>
+        <v>11063.407223545593</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>16514.161630791572</v>
+        <v>14714.33160731564</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22438,7 +22467,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>210555.56079259253</v>
+        <v>187607.72799327443</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22492,23 +22521,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f>H7/(1+$C$21)^H9</f>
-        <v>4797.9672791519433</v>
+        <v>4275.0509026662385</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>5801.1786193382586</v>
+        <v>5168.9251823146342</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" si="1"/>
-        <v>7014.1523306544395</v>
+        <v>6249.7004477076925</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" si="1"/>
-        <v>8480.747817973097</v>
+        <v>7556.4559958647569</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>10253.995089003834</v>
+        <v>9136.4422495455692</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22527,7 +22556,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f>L8/(1+C21)^L9</f>
-        <v>130738.43738479889</v>
+        <v>116489.63868170603</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22543,7 +22572,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22552,7 +22581,7 @@
       </c>
       <c r="C16" s="156">
         <f>C36</f>
-        <v>464.30326460088776</v>
+        <v>413.85931706317149</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22609,7 +22638,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>161431.98000000001</v>
+        <v>166119.565</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22636,7 +22665,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>160904.98000000001</v>
+        <v>165592.565</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22652,7 +22681,7 @@
       </c>
       <c r="C29" s="161">
         <f>SUM(H10:L10)</f>
-        <v>36348.041136121574</v>
+        <v>32386.574778098893</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22661,7 +22690,7 @@
       </c>
       <c r="C30" s="161">
         <f>L11</f>
-        <v>130738.43738479889</v>
+        <v>116489.63868170603</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22670,7 +22699,7 @@
       </c>
       <c r="C31" s="164">
         <f>C29+C30</f>
-        <v>167086.47852092047</v>
+        <v>148876.21345980492</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22697,7 +22726,7 @@
       </c>
       <c r="C34" s="164">
         <f>C31+C32-C33</f>
-        <v>167613.47852092047</v>
+        <v>149403.21345980492</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22715,7 +22744,7 @@
       </c>
       <c r="C36" s="167">
         <f>C34/C35</f>
-        <v>464.30326460088776</v>
+        <v>413.85931706317149</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22780,7 +22809,7 @@
       </c>
       <c r="C41" s="112">
         <f>C7</f>
-        <v>1824.645313235987</v>
+        <v>421.35468676401297</v>
       </c>
       <c r="D41" s="112">
         <f t="shared" si="2"/>
@@ -22796,27 +22825,27 @@
       </c>
       <c r="G41" s="113">
         <f t="shared" si="2"/>
-        <v>3968.2436143361938</v>
+        <v>3535.7563856638062</v>
       </c>
       <c r="H41" s="143">
         <f t="shared" si="2"/>
-        <v>5277.7640070671378</v>
+        <v>4702.5559929328629</v>
       </c>
       <c r="I41" s="143">
         <f t="shared" si="2"/>
-        <v>7019.426129399294</v>
+        <v>6254.3994706007079</v>
       </c>
       <c r="J41" s="143">
         <f t="shared" si="2"/>
-        <v>9335.8367521010623</v>
+        <v>8318.3512958989413</v>
       </c>
       <c r="K41" s="143">
         <f t="shared" si="2"/>
-        <v>12416.662880294414</v>
+        <v>11063.407223545593</v>
       </c>
       <c r="L41" s="143">
         <f t="shared" si="2"/>
-        <v>16514.161630791572</v>
+        <v>14714.33160731564</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -22845,23 +22874,23 @@
       </c>
       <c r="H42" s="143">
         <f>H41/H43</f>
-        <v>4797.9672791519433</v>
+        <v>4275.0509026662385</v>
       </c>
       <c r="I42" s="143">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>6381.2964812720847</v>
+        <v>5685.8177005460975</v>
       </c>
       <c r="J42" s="143">
         <f t="shared" si="3"/>
-        <v>8487.1243200918743</v>
+        <v>7562.1375417263098</v>
       </c>
       <c r="K42" s="143">
         <f t="shared" si="3"/>
-        <v>11287.875345722194</v>
+        <v>10057.642930495993</v>
       </c>
       <c r="L42" s="143">
         <f t="shared" si="3"/>
-        <v>15012.874209810519</v>
+        <v>13376.665097559671</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -22870,7 +22899,7 @@
       </c>
       <c r="C43" s="95">
         <f>C41/C42</f>
-        <v>0.76313062034127432</v>
+        <v>0.1762252976846562</v>
       </c>
       <c r="D43" s="95">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
@@ -22886,7 +22915,7 @@
       </c>
       <c r="G43" s="96">
         <f t="shared" si="4"/>
-        <v>0.89113936993851195</v>
+        <v>0.79401670461796681</v>
       </c>
       <c r="H43" s="168">
         <v>1.1000000000000001</v>
@@ -22930,23 +22959,23 @@
       </c>
       <c r="H44" s="143">
         <f>H41/H45</f>
-        <v>527776.40070671379</v>
+        <v>470255.59929328627</v>
       </c>
       <c r="I44" s="143">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>350971.30646996468</v>
+        <v>312719.97353003541</v>
       </c>
       <c r="J44" s="143">
         <f t="shared" si="5"/>
-        <v>222281.82743097766</v>
+        <v>198055.98323568905</v>
       </c>
       <c r="K44" s="143">
         <f t="shared" si="5"/>
-        <v>177380.89828992018</v>
+        <v>158048.67462207988</v>
       </c>
       <c r="L44" s="143">
         <f t="shared" si="5"/>
-        <v>110094.41087194382</v>
+        <v>98095.544048770942</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -22955,7 +22984,7 @@
       </c>
       <c r="C45" s="95">
         <f>C41/C44</f>
-        <v>9.7091752952481611E-2</v>
+        <v>2.2420831520460437E-2</v>
       </c>
       <c r="D45" s="95">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
@@ -22971,7 +23000,7 @@
       </c>
       <c r="G45" s="96">
         <f t="shared" si="6"/>
-        <v>0.30716337288769979</v>
+        <v>0.27368653809612248</v>
       </c>
       <c r="H45" s="168">
         <v>0.01</v>
@@ -22996,7 +23025,7 @@
       <c r="C46" s="137"/>
       <c r="D46" s="95">
         <f>D41/C41-1</f>
-        <v>-1.2460752217118316</v>
+        <v>-2.0656105511684277</v>
       </c>
       <c r="E46" s="95">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
@@ -23008,7 +23037,7 @@
       </c>
       <c r="G46" s="96">
         <f t="shared" si="7"/>
-        <v>1.9569624547959714</v>
+        <v>1.634691792595981</v>
       </c>
       <c r="H46" s="169">
         <f t="shared" si="7"/>
@@ -23054,7 +23083,7 @@
       </c>
       <c r="H47" s="169">
         <f t="shared" si="7"/>
-        <v>7.7468510925655432E-2</v>
+        <v>-3.9961620780094687E-2</v>
       </c>
       <c r="I47" s="169">
         <f t="shared" si="7"/>
@@ -23062,7 +23091,7 @@
       </c>
       <c r="J47" s="169">
         <f t="shared" si="7"/>
-        <v>0.33000000000000029</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="K47" s="169">
         <f t="shared" si="7"/>
@@ -23096,7 +23125,7 @@
       </c>
       <c r="H48" s="169">
         <f t="shared" si="8"/>
-        <v>39.852728594064075</v>
+        <v>35.400309566784294</v>
       </c>
       <c r="I48" s="169">
         <f t="shared" si="8"/>
@@ -23104,7 +23133,7 @@
       </c>
       <c r="J48" s="169">
         <f t="shared" si="8"/>
-        <v>-0.36666666666666659</v>
+        <v>-0.36666666666666681</v>
       </c>
       <c r="K48" s="169">
         <f t="shared" si="8"/>
@@ -23157,22 +23186,22 @@
       </c>
       <c r="L49" s="169">
         <f t="shared" si="9"/>
-        <v>0.13636363636363635</v>
+        <v>0.13636363636363633</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29902,7 +29931,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29976,7 +30005,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31345,7 +31374,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>18.470879801734821</v>
+        <v>19.007228418009088</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31386,7 +31415,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>13.265866940165647</v>
+        <v>13.651074870346003</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31451,7 +31480,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>18.212091606498195</v>
+        <v>18.740925654332131</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31516,7 +31545,7 @@
       </c>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>178424.82</v>
+        <v>183605.83500000002</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31581,7 +31610,7 @@
       </c>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>177897.82</v>
+        <v>183078.83500000002</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31622,7 +31651,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>13.770246923136467</v>
+        <v>14.171285316200946</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31663,7 +31692,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>39.950105546822371</v>
+        <v>41.113594206153159</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31810,7 +31839,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>35.692102420484098</v>
+        <v>36.728512702540513</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31851,7 +31880,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="204"/>
-        <v>49.890626492387895</v>
+        <v>51.343618351515005</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31892,7 +31921,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>2.8017402511601244E-2</v>
+        <v>2.7226803549026637E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31933,7 +31962,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>5.4139272776063334E-2</v>
+        <v>5.2611563243619139E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31974,7 +32003,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>1.1181179838096517E-3</v>
+        <v>1.0865667749611551E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32015,7 +32044,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>2.4172645935694372E-2</v>
+        <v>2.3490538849160209E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32056,7 +32085,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.576995734113673E-2</v>
+        <v>2.5042777099104716E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32603,7 +32632,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.9536249497127136E-3</v>
+        <v>2.8702791498973874E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -34041,15 +34070,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="245" t="s">
+      <c r="B4" s="242" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="245"/>
-      <c r="E4" s="245" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34057,7 +34086,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34073,7 +34102,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>178424.82</v>
+        <v>183605.83500000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34093,7 +34122,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>177897.82</v>
+        <v>183078.83500000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -34113,7 +34142,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>18.470879801734821</v>
+        <v>19.007228418009088</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -34133,7 +34162,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>13.265866940165647</v>
+        <v>13.651074870346003</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -34153,7 +34182,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>18.212091606498195</v>
+        <v>18.740925654332131</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34173,7 +34202,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>13.770246923136467</v>
+        <v>14.171285316200946</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34182,18 +34211,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>39.950105546822371</v>
+        <v>41.113594206153159</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="245" t="s">
+      <c r="B15" s="242" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="245"/>
-      <c r="E15" s="245" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="245"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34244,14 +34273,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="245" t="s">
+      <c r="B21" s="242" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="245"/>
-      <c r="E21" s="245" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="245"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34320,14 +34349,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="245" t="s">
+      <c r="B29" s="242" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="245"/>
-      <c r="E29" s="245" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="245"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34403,14 +34432,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="245" t="s">
+      <c r="B37" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="245"/>
-      <c r="E37" s="245" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="245"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34418,7 +34447,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>5.4139272776063334E-2</v>
+        <v>5.2611563243619139E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -34434,7 +34463,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>2.8017402511601244E-2</v>
+        <v>2.7226803549026637E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -34450,7 +34479,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.1181179838096517E-3</v>
+        <v>1.0865667749611551E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -34466,7 +34495,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.4172645935694372E-2</v>
+        <v>2.3490538849160209E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34475,18 +34504,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.576995734113673E-2</v>
+        <v>2.5042777099104716E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="245" t="s">
+      <c r="B45" s="242" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="245"/>
-      <c r="E45" s="245" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="245"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34519,18 +34548,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>2.9536249497127136E-3</v>
+        <v>2.8702791498973874E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="245" t="s">
+      <c r="B51" s="242" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="245"/>
-      <c r="E51" s="245" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="245"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34698,7 +34727,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>447.18</v>
+        <v>460.16500000000002</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34727,7 +34756,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>178424.82</v>
+        <v>183605.83500000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34756,7 +34785,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>177897.82</v>
+        <v>183078.83500000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34785,7 +34814,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>18.470879801734821</v>
+        <v>19.007228418009088</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34814,7 +34843,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>13.265866940165647</v>
+        <v>13.651074870346003</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34843,7 +34872,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>18.212091606498195</v>
+        <v>18.740925654332131</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34872,7 +34901,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>13.770246923136467</v>
+        <v>14.171285316200946</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34901,7 +34930,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>39.950105546822371</v>
+        <v>41.113594206153159</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35674,7 +35703,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>5.4139272776063334E-2</v>
+        <v>5.2611563243619139E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35703,7 +35732,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>2.8017402511601244E-2</v>
+        <v>2.7226803549026637E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35732,7 +35761,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>1.1181179838096517E-3</v>
+        <v>1.0865667749611551E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35761,7 +35790,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.4172645935694372E-2</v>
+        <v>2.3490538849160209E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35790,7 +35819,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.576995734113673E-2</v>
+        <v>2.5042777099104716E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36026,7 +36055,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>2.9536249497127136E-3</v>
+        <v>2.8702791498973874E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36515,14 +36544,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="246" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="F3" s="250" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="249"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36589,19 +36618,19 @@
       <c r="B7" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C7" s="246">
+      <c r="C7" s="249">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="F7" s="246">
+      <c r="D7" s="250"/>
+      <c r="F7" s="249">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="247"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="207" t="s">
@@ -36628,19 +36657,19 @@
       <c r="B9" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C9" s="246">
+      <c r="C9" s="249">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="247"/>
-      <c r="F9" s="246">
+      <c r="D9" s="250"/>
+      <c r="F9" s="249">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="247"/>
+      <c r="G9" s="250"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="207" t="s">
@@ -36667,19 +36696,19 @@
       <c r="B11" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="246">
+      <c r="C11" s="249">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="F11" s="246">
+      <c r="D11" s="250"/>
+      <c r="F11" s="249">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="247"/>
+      <c r="G11" s="250"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="207" t="s">
@@ -36706,19 +36735,19 @@
       <c r="B13" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="246">
+      <c r="C13" s="249">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="247"/>
-      <c r="F13" s="246">
+      <c r="D13" s="250"/>
+      <c r="F13" s="249">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="247"/>
+      <c r="G13" s="250"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="207" t="s">
@@ -36745,19 +36774,19 @@
       <c r="B15" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="246">
+      <c r="C15" s="249">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="247"/>
-      <c r="F15" s="246">
+      <c r="D15" s="250"/>
+      <c r="F15" s="249">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="247"/>
+      <c r="G15" s="250"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="207" t="s">
@@ -36784,19 +36813,19 @@
       <c r="B17" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="246">
+      <c r="C17" s="249">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="F17" s="246">
+      <c r="D17" s="250"/>
+      <c r="F17" s="249">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="247"/>
+      <c r="G17" s="250"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="207" t="s">
@@ -36823,22 +36852,22 @@
       <c r="B19" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="246">
+      <c r="C19" s="249">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="F19" s="246">
+      <c r="D19" s="250"/>
+      <c r="F19" s="249">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="247"/>
+      <c r="G19" s="250"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="207" t="s">
@@ -36865,22 +36894,22 @@
       <c r="B21" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C21" s="246">
+      <c r="C21" s="249">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="F21" s="246">
+      <c r="D21" s="250"/>
+      <c r="F21" s="249">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="247"/>
+      <c r="G21" s="250"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36929,22 +36958,22 @@
       <c r="B25" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="246">
+      <c r="C25" s="249">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="247"/>
-      <c r="F25" s="246">
+      <c r="D25" s="250"/>
+      <c r="F25" s="249">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="247"/>
+      <c r="G25" s="250"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36972,22 +37001,22 @@
       <c r="B27" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C27" s="246">
+      <c r="C27" s="249">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="247"/>
-      <c r="F27" s="246">
+      <c r="D27" s="250"/>
+      <c r="F27" s="249">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="247"/>
+      <c r="G27" s="250"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37015,49 +37044,49 @@
       <c r="B29" s="206" t="s">
         <v>319</v>
       </c>
-      <c r="C29" s="246">
+      <c r="C29" s="249">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="247"/>
-      <c r="F29" s="246">
+      <c r="D29" s="250"/>
+      <c r="F29" s="249">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="247"/>
+      <c r="G29" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAE6D56-C20A-A640-A0F8-0085E60A724C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2E6B17-C197-C840-ABDE-908957A6084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,28 +148,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -179,21 +158,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2433,6 +2403,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2440,12 +2416,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2457,14 +2427,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12798,7 +12768,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12838,8 +12808,10 @@
     <v>799.87</v>
     <v>105.42</v>
     <v>2.1198999999999999</v>
-    <v>5.7850000000000001</v>
-    <v>1.2846999999999999E-2</v>
+    <v>6.5</v>
+    <v>1.4435E-2</v>
+    <v>-1.81</v>
+    <v>-3.9620000000000002E-3</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12851,46 +12823,32 @@
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46290.718602568748</v>
+    <v>46290.838222140628</v>
     <v>4</v>
     <v>447.69</v>
-    <v>164440947395</v>
+    <v>164698734210</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>454.76</v>
-    <v>18.787299999999998</v>
+    <v>18.816700000000001</v>
     <v>450.31</v>
-    <v>456.09500000000003</v>
+    <v>456.81</v>
+    <v>455</v>
     <v>360541000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>3285271</v>
+    <v>5831760</v>
     <v>6317508</v>
     <v>2000</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="5">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12909,7 +12867,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>10</v>
+    <v>7</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -12919,13 +12877,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>11</v>
+    <v>8</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12959,6 +12917,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12980,6 +12940,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12989,11 +12950,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13029,7 +12985,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13040,13 +12996,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13147,13 +13106,19 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
     </spb>
     <spb s="5">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13234,6 +13199,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13241,6 +13209,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13764,7 +13735,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>181981.905</v>
+        <v>182267.19</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13788,7 +13759,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>181454.905</v>
+        <v>181740.19</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13796,7 +13767,7 @@
       </c>
       <c r="I4" s="207">
         <f>'AVG target price'!C6</f>
-        <v>128.29486036122091</v>
+        <v>126.97405835620837</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13805,7 +13776,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13827,16 +13798,16 @@
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="204" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>455</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>18.839116067740605</v>
+        <v>18.868649318463444</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13844,7 +13815,7 @@
       </c>
       <c r="I6" s="207">
         <f>'AVG target price'!C8</f>
-        <v>143.20461929004765</v>
+        <v>141.88381728503509</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13853,14 +13824,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>5.7850000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>13.530335842557475</v>
+        <v>13.551546752844647</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13868,23 +13839,23 @@
       </c>
       <c r="I7" s="208">
         <f>'AVG target price'!C9</f>
-        <v>123.75273100632222</v>
+        <v>123.09233000381593</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-1.81</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.7469764095501694E-2</v>
+        <v>2.7426768361327125E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B11</f>
@@ -13892,7 +13863,7 @@
       </c>
       <c r="I8" s="209">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.72866895930382436</v>
+        <v>-0.73053932706417135</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13901,30 +13872,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.2846999999999999E-2</v>
+        <v>1.4435E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>5.3081046711759609E-2</v>
+        <v>5.2997964142641366E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-3.9620000000000002E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.3700158540487858E-2</v>
+        <v>2.3663063001080994E-2</v>
       </c>
       <c r="H10" s="180" t="s">
         <v>362</v>
@@ -13947,7 +13918,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.0962628399785132E-3</v>
+        <v>1.0945469670103544E-3</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -14004,7 +13975,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>2.8958923141287041E-3</v>
+        <v>2.8913596572153221E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14109,7 +14080,7 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="5">
+      <c r="E26" s="181" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
@@ -14378,18 +14349,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B76:H76"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -18657,6 +18628,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18664,12 +18641,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19729,16 +19700,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19821,7 +19792,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19830,7 +19801,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>181981.905</v>
+        <v>182267.19</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19900,7 +19871,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.747569009140684E-3</v>
+        <v>5.7386245269794179E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19909,7 +19880,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99425243099085936</v>
+        <v>0.99426137547302063</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19936,7 +19907,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14632943855143943</v>
+        <v>0.14633050621402485</v>
       </c>
     </row>
   </sheetData>
@@ -21436,8 +21407,8 @@
         <v>426</v>
       </c>
       <c r="C43" s="24">
-        <f>C42/(1+C40)^5-G31+G32</f>
-        <v>37149.532944794868</v>
+        <f>C42/(1+C40)^5</f>
+        <v>36622.532944794868</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21446,7 +21417,7 @@
       </c>
       <c r="C44" s="108">
         <f>SUM(H9:K9)+C43</f>
-        <v>50662.649284127139</v>
+        <v>50135.649284127139</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21473,7 +21444,7 @@
       </c>
       <c r="C47" s="108">
         <f>C44+C45-C46</f>
-        <v>51189.649284127139</v>
+        <v>50662.649284127139</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -21491,7 +21462,7 @@
       </c>
       <c r="C49" s="239">
         <f>C47/C48</f>
-        <v>128.29486036122091</v>
+        <v>126.97405835620837</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
@@ -21599,8 +21570,8 @@
         <v>427</v>
       </c>
       <c r="C64" s="24">
-        <f>C63/(1+C61)^5-G31+G32</f>
-        <v>43098.526757396736</v>
+        <f>C63/(1+C61)^5</f>
+        <v>42571.526757396736</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -21609,7 +21580,7 @@
       </c>
       <c r="C65" s="108">
         <f>SUM(H9:K9)+C64</f>
-        <v>56611.643096729007</v>
+        <v>56084.643096729007</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21636,7 +21607,7 @@
       </c>
       <c r="C68" s="108">
         <f>C65+C66-C67</f>
-        <v>57138.643096729007</v>
+        <v>56611.643096729007</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -21654,7 +21625,7 @@
       </c>
       <c r="C70" s="239">
         <f>C68/C69</f>
-        <v>143.20461929004765</v>
+        <v>141.88381728503509</v>
       </c>
     </row>
   </sheetData>
@@ -21727,7 +21698,7 @@
       </c>
       <c r="C6" s="133">
         <f>Multiples!C49</f>
-        <v>128.29486036122091</v>
+        <v>126.97405835620837</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21745,7 +21716,7 @@
       </c>
       <c r="C8" s="133">
         <f>Multiples!C70</f>
-        <v>143.20461929004765</v>
+        <v>141.88381728503509</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21754,7 +21725,7 @@
       </c>
       <c r="C9" s="239">
         <f>AVERAGE(C5:C8)</f>
-        <v>123.75273100632222</v>
+        <v>123.09233000381593</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21763,7 +21734,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21772,7 +21743,7 @@
       </c>
       <c r="C11" s="152">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.72866895930382436</v>
+        <v>-0.73053932706417135</v>
       </c>
     </row>
   </sheetData>
@@ -22590,10 +22561,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="257"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22601,7 +22572,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22620,20 +22591,20 @@
       <c r="C17" s="156">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="255" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="256" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="257"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22667,7 +22638,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>164650.29500000001</v>
+        <v>164908.41</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22694,15 +22665,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>164123.29500000001</v>
+        <v>164381.41</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="256" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="257"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22778,16 +22749,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29517,7 +29488,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29591,7 +29562,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30960,7 +30931,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>18.839116067740605</v>
+        <v>18.868649318463444</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31001,7 +30972,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>13.530335842557475</v>
+        <v>13.551546752844647</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31066,7 +31037,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>18.575168659747295</v>
+        <v>18.604288131768953</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31131,7 +31102,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>181981.905</v>
+        <v>182267.19</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31196,7 +31167,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>181454.905</v>
+        <v>181740.19</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31237,7 +31208,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>14.045584410558092</v>
+        <v>14.067667002089944</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31278,7 +31249,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>40.748911969458788</v>
+        <v>40.812977767796994</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31425,7 +31396,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>36.403661732346471</v>
+        <v>36.460730146029206</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31466,7 +31437,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="204"/>
-        <v>50.888194642108196</v>
+        <v>50.968201509976964</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31507,7 +31478,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>2.7469764095501694E-2</v>
+        <v>2.7426768361327125E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31548,7 +31519,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>5.3081046711759609E-2</v>
+        <v>5.2997964142641366E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31589,7 +31560,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.0962628399785132E-3</v>
+        <v>1.0945469670103544E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31630,7 +31601,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.3700158540487858E-2</v>
+        <v>2.3663063001080994E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31671,7 +31642,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.5266248311885734E-2</v>
+        <v>2.5226701525381503E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32218,7 +32189,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.8958923141287041E-3</v>
+        <v>2.8913596572153221E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33672,7 +33643,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33688,7 +33659,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>181981.905</v>
+        <v>182267.19</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33708,7 +33679,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>181454.905</v>
+        <v>181740.19</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33728,7 +33699,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.839116067740605</v>
+        <v>18.868649318463444</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33748,7 +33719,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.530335842557475</v>
+        <v>13.551546752844647</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33768,7 +33739,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>18.575168659747295</v>
+        <v>18.604288131768953</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33788,7 +33759,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>14.045584410558092</v>
+        <v>14.067667002089944</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33797,7 +33768,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>40.748911969458788</v>
+        <v>40.812977767796994</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34033,7 +34004,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.3081046711759609E-2</v>
+        <v>5.2997964142641366E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34049,7 +34020,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.7469764095501694E-2</v>
+        <v>2.7426768361327125E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34065,7 +34036,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.0962628399785132E-3</v>
+        <v>1.0945469670103544E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34081,7 +34052,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.3700158540487858E-2</v>
+        <v>2.3663063001080994E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34090,7 +34061,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.5266248311885734E-2</v>
+        <v>2.5226701525381503E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34134,7 +34105,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>2.8958923141287041E-3</v>
+        <v>2.8913596572153221E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34313,7 +34284,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>456.09500000000003</v>
+        <v>456.81</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34342,7 +34313,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>181981.905</v>
+        <v>182267.19</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34371,7 +34342,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>181454.905</v>
+        <v>181740.19</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34400,7 +34371,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.839116067740605</v>
+        <v>18.868649318463444</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34429,7 +34400,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.530335842557475</v>
+        <v>13.551546752844647</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34458,7 +34429,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>18.575168659747295</v>
+        <v>18.604288131768953</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34487,7 +34458,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>14.045584410558092</v>
+        <v>14.067667002089944</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34516,7 +34487,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>40.748911969458788</v>
+        <v>40.812977767796994</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35289,7 +35260,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.3081046711759609E-2</v>
+        <v>5.2997964142641366E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35318,7 +35289,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.7469764095501694E-2</v>
+        <v>2.7426768361327125E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35347,7 +35318,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.0962628399785132E-3</v>
+        <v>1.0945469670103544E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35376,7 +35347,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.3700158540487858E-2</v>
+        <v>2.3663063001080994E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35405,7 +35376,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.5266248311885734E-2</v>
+        <v>2.5226701525381503E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35641,7 +35612,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.8958923141287041E-3</v>
+        <v>2.8913596572153221E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36130,14 +36101,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="249" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="F3" s="249" t="s">
+      <c r="D3" s="250"/>
+      <c r="F3" s="251" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="248"/>
+      <c r="G3" s="250"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36204,19 +36175,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="247">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36243,19 +36214,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="247">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36282,19 +36253,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="247">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36321,19 +36292,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="247">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36360,19 +36331,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="247">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36399,19 +36370,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="247">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36438,22 +36409,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36480,22 +36451,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36544,22 +36515,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36587,22 +36558,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -36630,49 +36601,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="250">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="F29" s="250">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="251"/>
+      <c r="G29" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2E6B17-C197-C840-ABDE-908957A6084A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD9A01-26BE-6246-BE2A-00AE83E16C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="434">
   <si>
     <t>Ticker</t>
   </si>
@@ -1457,6 +1457,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>EV/Sales price</t>
   </si>
 </sst>
 </file>
@@ -2403,12 +2418,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2416,6 +2425,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2427,14 +2442,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12807,11 +12822,11 @@
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
     <v>105.42</v>
-    <v>2.1198999999999999</v>
+    <v>2.1183000000000001</v>
     <v>6.5</v>
     <v>1.4435E-2</v>
-    <v>-1.81</v>
-    <v>-3.9620000000000002E-3</v>
+    <v>-0.81</v>
+    <v>-1.7730000000000001E-3</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12823,21 +12838,21 @@
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46290.838222140628</v>
+    <v>46290.999708008596</v>
     <v>4</v>
     <v>447.69</v>
     <v>164698734210</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>454.76</v>
-    <v>18.816700000000001</v>
+    <v>455.24</v>
+    <v>18.548999999999999</v>
     <v>450.31</v>
     <v>456.81</v>
-    <v>455</v>
+    <v>456</v>
     <v>360541000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>5831760</v>
+    <v>5941924</v>
     <v>6317508</v>
     <v>2000</v>
   </rv>
@@ -12860,19 +12875,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>7</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13114,9 +13129,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13800,7 +13815,7 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
@@ -13834,12 +13849,12 @@
         <v>13.551546752844647</v>
       </c>
       <c r="H7" s="180" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="208">
-        <f>'AVG target price'!C9</f>
-        <v>123.09233000381593</v>
+        <f>'AVG target price'!C10</f>
+        <v>136.10678192151076</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13848,7 +13863,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.81</v>
+        <v>-0.81</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
@@ -13858,12 +13873,12 @@
         <v>2.7426768361327125E-2</v>
       </c>
       <c r="H8" s="180" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="209">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>-0.73053932706417135</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.70204946931654133</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13888,7 +13903,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.9620000000000002E-3</v>
+        <v>-1.7730000000000001E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
@@ -13943,7 +13958,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1198999999999999</v>
+        <v>2.1183000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -14085,7 +14100,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14100,7 +14115,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14349,18 +14364,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="B76:H76"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B66:H66"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -18628,12 +18643,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18641,6 +18650,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19700,16 +19715,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19819,7 +19834,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19828,7 +19843,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1198999999999999</v>
+        <v>2.1183000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19898,7 +19913,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14701549999999999</v>
+        <v>0.1471635</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19907,7 +19922,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14633050621402485</v>
+        <v>0.14647765689759487</v>
       </c>
     </row>
   </sheetData>
@@ -20369,7 +20384,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -21355,285 +21370,421 @@
       <c r="N35" s="91"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="C36" s="147">
+        <f>C33/C6</f>
+        <v>1.0334720693875379</v>
+      </c>
+      <c r="D36" s="147">
+        <f t="shared" ref="D36:G36" si="11">D33/D6</f>
+        <v>3.3149199104716227</v>
+      </c>
+      <c r="E36" s="147">
+        <f t="shared" si="11"/>
+        <v>5.8180130220041146</v>
+      </c>
+      <c r="F36" s="147">
+        <f t="shared" si="11"/>
+        <v>2.679828781512605</v>
+      </c>
+      <c r="G36" s="148">
+        <f t="shared" si="11"/>
+        <v>16.152921262158983</v>
+      </c>
+      <c r="H36" s="137"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="137"/>
+      <c r="K36" s="137"/>
+      <c r="L36" s="137"/>
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="241" t="s">
+      <c r="N38" s="91"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="241" t="s">
         <v>204</v>
       </c>
-      <c r="C38" s="241"/>
-      <c r="N38" s="91"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="241"/>
+      <c r="N39" s="91"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="64">
+      <c r="C40" s="64">
         <f>L7</f>
         <v>3932.0637021947737</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="135">
+      <c r="C41" s="135">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="C41" s="105">
+      <c r="C42" s="105">
         <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>58980.955532921602</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>58980.955532921602</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C43" s="24">
-        <f>C42/(1+C40)^5</f>
+      <c r="C44" s="24">
+        <f>C43/(1+C41)^5</f>
         <v>36622.532944794868</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="C44" s="108">
-        <f>SUM(H9:K9)+C43</f>
+      <c r="C45" s="108">
+        <f>SUM(H9:K9)+C44</f>
         <v>50135.649284127139</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C45" s="88">
+      <c r="C46" s="88">
         <f>Statement!AC105</f>
         <v>1579</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C46" s="88">
+      <c r="C47" s="88">
         <f>Statement!AC106</f>
         <v>1052</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C47" s="108">
-        <f>C44+C45-C46</f>
+      <c r="C48" s="108">
+        <f>C45+C46-C47</f>
         <v>50662.649284127139</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="88">
+      <c r="C49" s="88">
         <f>Statement!AC77</f>
         <v>399</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="238" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="C49" s="239">
-        <f>C47/C48</f>
+      <c r="C50" s="239">
+        <f>C48/C49</f>
         <v>126.97405835620837</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="241" t="s">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="241" t="s">
         <v>209</v>
       </c>
-      <c r="C51" s="241"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="241"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C52" s="64">
+      <c r="C53" s="64">
         <f>L6</f>
         <v>16383.598759144892</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C53" s="135">
+      <c r="C54" s="135">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.11</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="C54" s="105">
+      <c r="C55" s="105">
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>475.94075857028014</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>206.54165625605603</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="238" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="C57" s="239">
-        <f>C56/(1+C53)^5</f>
+      <c r="C58" s="239">
+        <f>C57/(1+C54)^5</f>
         <v>122.57242020457076</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="241" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="241" t="s">
         <v>321</v>
       </c>
-      <c r="C59" s="241"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="241"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C60" s="64">
+      <c r="C61" s="64">
         <f>L8</f>
         <v>3264.8509313359541</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C61" s="135">
+      <c r="C62" s="135">
         <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="C62" s="105">
+      <c r="C63" s="105">
         <v>21</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C63" s="24">
-        <f>(C60*C62)</f>
-        <v>68561.869558055041</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C64" s="24">
+        <f>(C61*C63)</f>
+        <v>68561.869558055041</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C64" s="24">
-        <f>C63/(1+C61)^5</f>
+      <c r="C65" s="24">
+        <f>C64/(1+C62)^5</f>
         <v>42571.526757396736</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="C65" s="108">
-        <f>SUM(H9:K9)+C64</f>
+      <c r="C66" s="108">
+        <f>SUM(H9:K9)+C65</f>
         <v>56084.643096729007</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C66" s="88">
+      <c r="C67" s="88">
         <f>Statement!AC105</f>
         <v>1579</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C67" s="88">
+      <c r="C68" s="88">
         <f>Statement!AC106</f>
         <v>1052</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C68" s="108">
-        <f>C65+C66-C67</f>
+      <c r="C69" s="108">
+        <f>C66+C67-C68</f>
         <v>56611.643096729007</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="88">
+      <c r="C70" s="88">
         <f>Statement!AC77</f>
         <v>399</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="238" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="238" t="s">
         <v>208</v>
       </c>
-      <c r="C70" s="239">
-        <f>C68/C69</f>
+      <c r="C71" s="239">
+        <f>C69/C70</f>
         <v>141.88381728503509</v>
       </c>
     </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="241" t="s">
+        <v>430</v>
+      </c>
+      <c r="C73" s="241"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C74" s="64">
+        <f>L6</f>
+        <v>16383.598759144892</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="135">
+        <f>IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="C76" s="105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C77" s="24">
+        <f>(C74*C76)</f>
+        <v>98301.592554869349</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C78" s="24">
+        <f>C77/(1+C75)^5</f>
+        <v>61037.554907991456</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="C79" s="108">
+        <f>SUM(H9:K9)+C78</f>
+        <v>74550.671247323728</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C80" s="88">
+        <f>Statement!AC105</f>
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C81" s="88">
+        <f>Statement!AC106</f>
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C82" s="108">
+        <f>C79+C80-C81</f>
+        <v>75077.671247323728</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" s="88">
+        <f>Statement!AC77</f>
+        <v>399</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="238" t="s">
+        <v>208</v>
+      </c>
+      <c r="C84" s="239">
+        <f>C82/C83</f>
+        <v>188.16458959229004</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
@@ -21650,7 +21801,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="83" customWidth="1"/>
@@ -21697,7 +21848,7 @@
         <v>215</v>
       </c>
       <c r="C6" s="133">
-        <f>Multiples!C49</f>
+        <f>Multiples!C50</f>
         <v>126.97405835620837</v>
       </c>
     </row>
@@ -21706,7 +21857,7 @@
         <v>216</v>
       </c>
       <c r="C7" s="133">
-        <f>Multiples!C57</f>
+        <f>Multiples!C58</f>
         <v>122.57242020457076</v>
       </c>
     </row>
@@ -21715,35 +21866,44 @@
         <v>322</v>
       </c>
       <c r="C8" s="133">
-        <f>Multiples!C70</f>
+        <f>Multiples!C71</f>
         <v>141.88381728503509</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="238" t="s">
+      <c r="B9" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C9" s="133">
+        <f>Multiples!C84</f>
+        <v>188.16458959229004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="238" t="s">
         <v>217</v>
       </c>
-      <c r="C9" s="239">
-        <f>AVERAGE(C5:C8)</f>
-        <v>123.09233000381593</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="239">
+        <f>AVERAGE(C5:C9)</f>
+        <v>136.10678192151076</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="133">
+      <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
         <v>456.81</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="152">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>-0.73053932706417135</v>
+      <c r="C12" s="152">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>-0.70204946931654133</v>
       </c>
     </row>
   </sheetData>
@@ -22561,10 +22721,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="256" t="s">
+      <c r="B14" s="255" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="257"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22591,20 +22751,20 @@
       <c r="C17" s="156">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E17" s="255" t="s">
+      <c r="E17" s="257" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="256" t="s">
+      <c r="B19" s="255" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="257"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22670,10 +22830,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="256" t="s">
+      <c r="B28" s="255" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="257"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22749,16 +22909,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -36101,14 +36261,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="249" t="s">
+      <c r="C3" s="247" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="250"/>
-      <c r="F3" s="251" t="s">
+      <c r="D3" s="248"/>
+      <c r="F3" s="249" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="250"/>
+      <c r="G3" s="248"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36175,19 +36335,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="250">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="251"/>
+      <c r="F7" s="250">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36214,19 +36374,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="250">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="251"/>
+      <c r="F9" s="250">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36253,19 +36413,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="250">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="251"/>
+      <c r="F11" s="250">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="251"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36292,19 +36452,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="250">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="251"/>
+      <c r="F13" s="250">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="251"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36331,19 +36491,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="250">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="251"/>
+      <c r="F15" s="250">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="251"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36370,19 +36530,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="250">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="251"/>
+      <c r="F17" s="250">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="251"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36409,22 +36569,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="250">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="251"/>
+      <c r="F19" s="250">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="251"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36451,22 +36611,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="250">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="251"/>
+      <c r="F21" s="250">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="251"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36515,22 +36675,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="250">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="251"/>
+      <c r="F25" s="250">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="251"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36558,22 +36718,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="250">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="251"/>
+      <c r="F27" s="250">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="251"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -36601,49 +36761,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="250">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="251"/>
+      <c r="F29" s="250">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DD9A01-26BE-6246-BE2A-00AE83E16C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14C1598-FB6A-0545-B168-DA2FD8E4E68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="10" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="435">
   <si>
     <t>Ticker</t>
   </si>
@@ -1472,6 +1472,9 @@
   </si>
   <si>
     <t>EV/Sales price</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2397,18 +2400,6 @@
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2416,6 +2407,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2433,10 +2427,19 @@
     <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -12821,12 +12824,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>105.42</v>
-    <v>2.1183000000000001</v>
-    <v>6.5</v>
-    <v>1.4435E-2</v>
-    <v>-0.81</v>
-    <v>-1.7730000000000001E-3</v>
+    <v>111.83</v>
+    <v>2.1196000000000002</v>
+    <v>0.25</v>
+    <v>5.5159999999999996E-4</v>
+    <v>0.31</v>
+    <v>6.8360000000000003E-4</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12834,26 +12837,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>461.98</v>
+    <v>465.9</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46290.999708008596</v>
+    <v>46294.96077729141</v>
     <v>4</v>
-    <v>447.69</v>
-    <v>164698734210</v>
+    <v>447.03</v>
+    <v>163498132680</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>455.24</v>
-    <v>18.548999999999999</v>
-    <v>450.31</v>
-    <v>456.81</v>
-    <v>456</v>
+    <v>463.15</v>
+    <v>18.679600000000001</v>
+    <v>453.23</v>
+    <v>453.48</v>
+    <v>453.79</v>
     <v>360541000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>5941924</v>
-    <v>6317508</v>
+    <v>6114581</v>
+    <v>6463752</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12875,19 +12878,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.15</v>
+    <v>2.8630000000000001E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.93</v>
     <v>Index</v>
     <v>7</v>
-    <v>51.62</v>
+    <v>52.13</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.13</v>
+    <v>52.4</v>
+    <v>52.55</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13129,9 +13132,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13724,18 +13727,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="245"/>
-      <c r="E2" s="244" t="s">
+      <c r="C2" s="241"/>
+      <c r="E2" s="240" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="245"/>
-      <c r="H2" s="244" t="s">
+      <c r="F2" s="241"/>
+      <c r="H2" s="240" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="245"/>
+      <c r="I2" s="241"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
@@ -13750,7 +13753,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>182267.19</v>
+        <v>180938.52000000002</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13774,7 +13777,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>181740.19</v>
+        <v>180411.52000000002</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13791,7 +13794,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13815,14 +13818,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>456</v>
+        <v>453.79</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>18.868649318463444</v>
+        <v>18.731102850061959</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13839,22 +13842,22 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>6.5</v>
+        <v>0.25</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>13.551546752844647</v>
-      </c>
-      <c r="H7" s="180" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="208">
-        <f>'AVG target price'!C10</f>
-        <v>136.10678192151076</v>
+        <v>13.452760275563126</v>
+      </c>
+      <c r="H7" s="181" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales price</v>
+      </c>
+      <c r="I7" s="207">
+        <f>'AVG target price'!C9</f>
+        <v>188.16458959229004</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13863,22 +13866,22 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.81</v>
+        <v>0.31</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.7426768361327125E-2</v>
+        <v>2.7628168949320464E-2</v>
       </c>
       <c r="H8" s="180" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="209">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>-0.70204946931654133</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="208">
+        <f>'AVG target price'!C10</f>
+        <v>136.10678192151076</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13887,14 +13890,22 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.4435E-2</v>
+        <v>5.5159999999999996E-4</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>5.2997964142641366E-2</v>
+        <v>5.3387139454882243E-2</v>
+      </c>
+      <c r="H9" s="180" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="209">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.69986155525820148</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13903,21 +13914,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.7730000000000001E-3</v>
+        <v>6.8360000000000003E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.3663063001080994E-2</v>
-      </c>
-      <c r="H10" s="180" t="s">
-        <v>362</v>
-      </c>
-      <c r="I10" s="208">
-        <f>DDM!C26</f>
-        <v>11.111111111111111</v>
+        <v>2.3836825900864004E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13933,7 +13937,14 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.0945469670103544E-3</v>
+        <v>1.1025844579694805E-3</v>
+      </c>
+      <c r="H11" s="180" t="s">
+        <v>362</v>
+      </c>
+      <c r="I11" s="208">
+        <f>DDM!C26</f>
+        <v>11.111111111111111</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13942,7 +13953,7 @@
       </c>
       <c r="C12" s="205" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>105.42</v>
+        <v>111.83</v>
       </c>
       <c r="E12" s="181" t="s">
         <v>101</v>
@@ -13958,7 +13969,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1183000000000001</v>
+        <v>2.1196000000000002</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13967,6 +13978,13 @@
         <f>Statement!AC123</f>
         <v>1.0631768953068592</v>
       </c>
+      <c r="H13" s="180" t="s">
+        <v>434</v>
+      </c>
+      <c r="I13" s="209">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.35499999999999998</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="182" t="s">
@@ -13974,7 +13992,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>6317508</v>
+        <v>6463752</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -13990,7 +14008,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>2.8913596572153221E-3</v>
+        <v>2.9125915255634894E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14003,10 +14021,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="246" t="s">
+      <c r="B17" s="242" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="246"/>
+      <c r="C17" s="242"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -14079,14 +14097,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="246" t="s">
+      <c r="B25" s="242" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="246"/>
-      <c r="E25" s="244" t="s">
+      <c r="C25" s="242"/>
+      <c r="E25" s="240" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="245"/>
+      <c r="F25" s="241"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14100,7 +14118,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.55</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14115,7 +14133,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14135,15 +14153,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="241" t="s">
+      <c r="B33" s="132" t="s">
         <v>332</v>
       </c>
-      <c r="C33" s="241"/>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
+      <c r="C33" s="132"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14210,24 +14228,24 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="241"/>
-      <c r="C46" s="241"/>
-      <c r="D46" s="241"/>
-      <c r="E46" s="241"/>
-      <c r="F46" s="241"/>
-      <c r="G46" s="241"/>
-      <c r="H46" s="241"/>
+      <c r="B46" s="132"/>
+      <c r="C46" s="132"/>
+      <c r="D46" s="132"/>
+      <c r="E46" s="132"/>
+      <c r="F46" s="132"/>
+      <c r="G46" s="132"/>
+      <c r="H46" s="132"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="241" t="s">
+      <c r="B49" s="132" t="s">
         <v>335</v>
       </c>
-      <c r="C49" s="241"/>
-      <c r="D49" s="241"/>
-      <c r="E49" s="241"/>
-      <c r="F49" s="241"/>
-      <c r="G49" s="241"/>
-      <c r="H49" s="241"/>
+      <c r="C49" s="132"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="132"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="41" t="s">
@@ -14322,24 +14340,24 @@
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="241"/>
-      <c r="C66" s="241"/>
-      <c r="D66" s="241"/>
-      <c r="E66" s="241"/>
-      <c r="F66" s="241"/>
-      <c r="G66" s="241"/>
-      <c r="H66" s="241"/>
+      <c r="B66" s="132"/>
+      <c r="C66" s="132"/>
+      <c r="D66" s="132"/>
+      <c r="E66" s="132"/>
+      <c r="F66" s="132"/>
+      <c r="G66" s="132"/>
+      <c r="H66" s="132"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="241" t="s">
+      <c r="B69" s="132" t="s">
         <v>108</v>
       </c>
-      <c r="C69" s="241"/>
-      <c r="D69" s="241"/>
-      <c r="E69" s="241"/>
-      <c r="F69" s="241"/>
-      <c r="G69" s="241"/>
-      <c r="H69" s="241"/>
+      <c r="C69" s="132"/>
+      <c r="D69" s="132"/>
+      <c r="E69" s="132"/>
+      <c r="F69" s="132"/>
+      <c r="G69" s="132"/>
+      <c r="H69" s="132"/>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" s="41" t="s">
@@ -14354,28 +14372,22 @@
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="241"/>
-      <c r="C76" s="241"/>
-      <c r="D76" s="241"/>
-      <c r="E76" s="241"/>
-      <c r="F76" s="241"/>
-      <c r="G76" s="241"/>
-      <c r="H76" s="241"/>
+      <c r="B76" s="132"/>
+      <c r="C76" s="132"/>
+      <c r="D76" s="132"/>
+      <c r="E76" s="132"/>
+      <c r="F76" s="132"/>
+      <c r="G76" s="132"/>
+      <c r="H76" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="B76:H76"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B66:H66"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14445,36 +14457,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="241" t="s">
+      <c r="S2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="241"/>
-      <c r="U2" s="241"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="241"/>
-      <c r="X2" s="241"/>
-      <c r="Y2" s="241"/>
-      <c r="Z2" s="241"/>
-      <c r="AA2" s="241" t="s">
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="241"/>
-      <c r="AC2" s="241"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14485,32 +14497,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="252" t="s">
+      <c r="S4" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
+      <c r="AA4" s="251"/>
+      <c r="AB4" s="251"/>
+      <c r="AC4" s="251"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15000,33 +15012,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="249" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="252" t="s">
+      <c r="S11" s="250" t="s">
         <v>121</v>
       </c>
-      <c r="T11" s="253"/>
-      <c r="U11" s="253"/>
-      <c r="V11" s="253"/>
-      <c r="W11" s="253"/>
-      <c r="X11" s="253"/>
-      <c r="Y11" s="253"/>
-      <c r="Z11" s="253"/>
-      <c r="AA11" s="253"/>
-      <c r="AB11" s="253"/>
-      <c r="AC11" s="253"/>
+      <c r="T11" s="251"/>
+      <c r="U11" s="251"/>
+      <c r="V11" s="251"/>
+      <c r="W11" s="251"/>
+      <c r="X11" s="251"/>
+      <c r="Y11" s="251"/>
+      <c r="Z11" s="251"/>
+      <c r="AA11" s="251"/>
+      <c r="AB11" s="251"/>
+      <c r="AC11" s="251"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15457,32 +15469,32 @@
     <row r="19" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="86"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="240" t="s">
+      <c r="C19" s="249" t="s">
         <v>414</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="E19" s="240"/>
-      <c r="F19" s="240"/>
-      <c r="G19" s="240"/>
-      <c r="H19" s="240"/>
-      <c r="I19" s="240"/>
-      <c r="J19" s="240"/>
-      <c r="K19" s="240"/>
-      <c r="L19" s="240"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="249"/>
+      <c r="F19" s="249"/>
+      <c r="G19" s="249"/>
+      <c r="H19" s="249"/>
+      <c r="I19" s="249"/>
+      <c r="J19" s="249"/>
+      <c r="K19" s="249"/>
+      <c r="L19" s="249"/>
       <c r="O19" s="5"/>
-      <c r="S19" s="252" t="s">
+      <c r="S19" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="T19" s="253"/>
-      <c r="U19" s="253"/>
-      <c r="V19" s="253"/>
-      <c r="W19" s="253"/>
-      <c r="X19" s="253"/>
-      <c r="Y19" s="253"/>
-      <c r="Z19" s="253"/>
-      <c r="AA19" s="253"/>
-      <c r="AB19" s="253"/>
-      <c r="AC19" s="253"/>
+      <c r="T19" s="251"/>
+      <c r="U19" s="251"/>
+      <c r="V19" s="251"/>
+      <c r="W19" s="251"/>
+      <c r="X19" s="251"/>
+      <c r="Y19" s="251"/>
+      <c r="Z19" s="251"/>
+      <c r="AA19" s="251"/>
+      <c r="AB19" s="251"/>
+      <c r="AC19" s="251"/>
       <c r="AE19" s="87"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
@@ -15977,35 +15989,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
-      <c r="P2" s="241" t="s">
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="P2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="241"/>
-      <c r="R2" s="241"/>
-      <c r="S2" s="241"/>
-      <c r="T2" s="241"/>
-      <c r="U2" s="241"/>
-      <c r="V2" s="241"/>
-      <c r="W2" s="241"/>
-      <c r="X2" s="241" t="s">
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="241"/>
-      <c r="Z2" s="241"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16014,31 +16026,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="P4" s="253" t="s">
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
+      <c r="P4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="253"/>
-      <c r="R4" s="253"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
+      <c r="Q4" s="251"/>
+      <c r="R4" s="251"/>
+      <c r="S4" s="251"/>
+      <c r="T4" s="251"/>
+      <c r="U4" s="251"/>
+      <c r="V4" s="251"/>
+      <c r="W4" s="251"/>
+      <c r="X4" s="251"/>
+      <c r="Y4" s="251"/>
+      <c r="Z4" s="251"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -16233,32 +16245,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="249" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="253" t="s">
+      <c r="P9" s="251" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="253"/>
-      <c r="R9" s="253"/>
-      <c r="S9" s="253"/>
-      <c r="T9" s="253"/>
-      <c r="U9" s="253"/>
-      <c r="V9" s="253"/>
-      <c r="W9" s="253"/>
-      <c r="X9" s="253"/>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
+      <c r="Q9" s="251"/>
+      <c r="R9" s="251"/>
+      <c r="S9" s="251"/>
+      <c r="T9" s="251"/>
+      <c r="U9" s="251"/>
+      <c r="V9" s="251"/>
+      <c r="W9" s="251"/>
+      <c r="X9" s="251"/>
+      <c r="Y9" s="251"/>
+      <c r="Z9" s="251"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16735,31 +16747,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="240" t="s">
+      <c r="C17" s="249" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="240"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="240"/>
-      <c r="P17" s="253" t="s">
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="249"/>
+      <c r="L17" s="249"/>
+      <c r="P17" s="251" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="253"/>
-      <c r="R17" s="253"/>
-      <c r="S17" s="253"/>
-      <c r="T17" s="253"/>
-      <c r="U17" s="253"/>
-      <c r="V17" s="253"/>
-      <c r="W17" s="253"/>
-      <c r="X17" s="253"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
+      <c r="Q17" s="251"/>
+      <c r="R17" s="251"/>
+      <c r="S17" s="251"/>
+      <c r="T17" s="251"/>
+      <c r="U17" s="251"/>
+      <c r="V17" s="251"/>
+      <c r="W17" s="251"/>
+      <c r="X17" s="251"/>
+      <c r="Y17" s="251"/>
+      <c r="Z17" s="251"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17237,20 +17249,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -17268,18 +17280,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
       <c r="P5" s="254"/>
       <c r="Q5" s="254"/>
       <c r="R5" s="254"/>
@@ -17476,18 +17488,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="249" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
       <c r="N11" s="91"/>
       <c r="P11" s="254"/>
       <c r="Q11" s="254"/>
@@ -17741,18 +17753,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="249" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="249"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17970,18 +17982,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="249" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="249"/>
+      <c r="H26" s="249"/>
+      <c r="I26" s="249"/>
+      <c r="J26" s="249"/>
+      <c r="K26" s="249"/>
+      <c r="L26" s="249"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18173,18 +18185,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="240" t="s">
+      <c r="C33" s="249" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
-      <c r="I33" s="240"/>
-      <c r="J33" s="240"/>
-      <c r="K33" s="240"/>
-      <c r="L33" s="240"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="249"/>
+      <c r="I33" s="249"/>
+      <c r="J33" s="249"/>
+      <c r="K33" s="249"/>
+      <c r="L33" s="249"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18368,18 +18380,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="240" t="s">
+      <c r="C40" s="249" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
-      <c r="G40" s="240"/>
-      <c r="H40" s="240"/>
-      <c r="I40" s="240"/>
-      <c r="J40" s="240"/>
-      <c r="K40" s="240"/>
-      <c r="L40" s="240"/>
+      <c r="D40" s="249"/>
+      <c r="E40" s="249"/>
+      <c r="F40" s="249"/>
+      <c r="G40" s="249"/>
+      <c r="H40" s="249"/>
+      <c r="I40" s="249"/>
+      <c r="J40" s="249"/>
+      <c r="K40" s="249"/>
+      <c r="L40" s="249"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18693,20 +18705,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
       <c r="S2" s="254"/>
       <c r="T2" s="254"/>
       <c r="U2" s="254"/>
@@ -18724,18 +18736,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="249" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
       <c r="S4" s="254"/>
       <c r="T4" s="254"/>
       <c r="U4" s="254"/>
@@ -19109,18 +19121,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="240" t="s">
+      <c r="C13" s="249" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="E13" s="240"/>
-      <c r="F13" s="240"/>
-      <c r="G13" s="240"/>
-      <c r="H13" s="240"/>
-      <c r="I13" s="240"/>
-      <c r="J13" s="240"/>
-      <c r="K13" s="240"/>
-      <c r="L13" s="240"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="249"/>
+      <c r="J13" s="249"/>
+      <c r="K13" s="249"/>
+      <c r="L13" s="249"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19213,18 +19225,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="249" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="249"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19416,18 +19428,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="240" t="s">
+      <c r="C25" s="249" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="E25" s="240"/>
-      <c r="F25" s="240"/>
-      <c r="G25" s="240"/>
-      <c r="H25" s="240"/>
-      <c r="I25" s="240"/>
-      <c r="J25" s="240"/>
-      <c r="K25" s="240"/>
-      <c r="L25" s="240"/>
+      <c r="D25" s="249"/>
+      <c r="E25" s="249"/>
+      <c r="F25" s="249"/>
+      <c r="G25" s="249"/>
+      <c r="H25" s="249"/>
+      <c r="I25" s="249"/>
+      <c r="J25" s="249"/>
+      <c r="K25" s="249"/>
+      <c r="L25" s="249"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19565,18 +19577,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="240" t="s">
+      <c r="C31" s="249" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="240"/>
-      <c r="G31" s="240"/>
-      <c r="H31" s="240"/>
-      <c r="I31" s="240"/>
-      <c r="J31" s="240"/>
-      <c r="K31" s="240"/>
-      <c r="L31" s="240"/>
+      <c r="D31" s="249"/>
+      <c r="E31" s="249"/>
+      <c r="F31" s="249"/>
+      <c r="G31" s="249"/>
+      <c r="H31" s="249"/>
+      <c r="I31" s="249"/>
+      <c r="J31" s="249"/>
+      <c r="K31" s="249"/>
+      <c r="L31" s="249"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19787,10 +19799,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="243" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="241"/>
+      <c r="C4" s="243"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19807,7 +19819,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19816,7 +19828,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>182267.19</v>
+        <v>180938.52000000002</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19834,7 +19846,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2549999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19843,7 +19855,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1183000000000001</v>
+        <v>2.1196000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19875,10 +19887,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="241" t="s">
+      <c r="B15" s="243" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="241"/>
+      <c r="C15" s="243"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19886,7 +19898,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.7386245269794179E-3</v>
+        <v>5.7805208754829638E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19895,7 +19907,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99426137547302063</v>
+        <v>0.99421947912451702</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19913,7 +19925,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1471635</v>
+        <v>0.14793200000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19922,7 +19934,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14647765689759487</v>
+        <v>0.14723670738805517</v>
       </c>
     </row>
   </sheetData>
@@ -19967,20 +19979,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -19998,18 +20010,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="249" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
       <c r="P5" s="254"/>
       <c r="Q5" s="254"/>
       <c r="R5" s="254"/>
@@ -20266,10 +20278,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="241" t="s">
+      <c r="B13" s="243" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="241"/>
+      <c r="C13" s="243"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20289,10 +20301,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="241" t="s">
+      <c r="B18" s="243" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="241"/>
+      <c r="C18" s="243"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20406,37 +20418,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="249" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20656,18 +20668,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="249" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="249"/>
+      <c r="I11" s="249"/>
+      <c r="J11" s="249"/>
+      <c r="K11" s="249"/>
+      <c r="L11" s="249"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20855,18 +20867,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="240" t="s">
+      <c r="C17" s="249" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="240"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="240"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="249"/>
+      <c r="L17" s="249"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -21000,18 +21012,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="240" t="s">
+      <c r="C22" s="249" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="240"/>
-      <c r="E22" s="240"/>
-      <c r="F22" s="240"/>
-      <c r="G22" s="240"/>
-      <c r="H22" s="240"/>
-      <c r="I22" s="240"/>
-      <c r="J22" s="240"/>
-      <c r="K22" s="240"/>
-      <c r="L22" s="240"/>
+      <c r="D22" s="249"/>
+      <c r="E22" s="249"/>
+      <c r="F22" s="249"/>
+      <c r="G22" s="249"/>
+      <c r="H22" s="249"/>
+      <c r="I22" s="249"/>
+      <c r="J22" s="249"/>
+      <c r="K22" s="249"/>
+      <c r="L22" s="249"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21095,18 +21107,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="240" t="s">
+      <c r="C27" s="249" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="E27" s="240"/>
-      <c r="F27" s="240"/>
-      <c r="G27" s="240"/>
-      <c r="H27" s="240"/>
-      <c r="I27" s="240"/>
-      <c r="J27" s="240"/>
-      <c r="K27" s="240"/>
-      <c r="L27" s="240"/>
+      <c r="D27" s="249"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="249"/>
+      <c r="H27" s="249"/>
+      <c r="I27" s="249"/>
+      <c r="J27" s="249"/>
+      <c r="K27" s="249"/>
+      <c r="L27" s="249"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21407,10 +21419,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="241" t="s">
+      <c r="B39" s="243" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="241"/>
+      <c r="C39" s="243"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21512,10 +21524,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="241" t="s">
+      <c r="B52" s="243" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="241"/>
+      <c r="C52" s="243"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21571,10 +21583,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="241" t="s">
+      <c r="B60" s="243" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="241"/>
+      <c r="C60" s="243"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21675,10 +21687,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="241" t="s">
+      <c r="B73" s="243" t="s">
         <v>430</v>
       </c>
-      <c r="C73" s="241"/>
+      <c r="C73" s="243"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21785,12 +21797,12 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B60:C60"/>
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21828,10 +21840,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="243" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="241"/>
+      <c r="C4" s="243"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21894,7 +21906,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21903,7 +21915,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.70204946931654133</v>
+        <v>-0.69986155525820148</v>
       </c>
     </row>
   </sheetData>
@@ -21959,37 +21971,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="241" t="s">
+      <c r="C2" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="243" t="s">
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="252"/>
+      <c r="H2" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
-      <c r="K2" s="241"/>
-      <c r="L2" s="241"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="249" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="249"/>
+      <c r="H4" s="249"/>
+      <c r="I4" s="249"/>
+      <c r="J4" s="249"/>
+      <c r="K4" s="249"/>
+      <c r="L4" s="249"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22102,18 +22114,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="249" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22234,18 +22246,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="240" t="s">
+      <c r="C14" s="249" t="s">
         <v>365</v>
       </c>
-      <c r="D14" s="240"/>
-      <c r="E14" s="240"/>
-      <c r="F14" s="240"/>
-      <c r="G14" s="240"/>
-      <c r="H14" s="240"/>
-      <c r="I14" s="240"/>
-      <c r="J14" s="240"/>
-      <c r="K14" s="240"/>
-      <c r="L14" s="240"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
+      <c r="K14" s="249"/>
+      <c r="L14" s="249"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22335,10 +22347,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="241" t="s">
+      <c r="B20" s="243" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="241"/>
+      <c r="C20" s="243"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22439,20 +22451,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="243" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
-      <c r="F3" s="241"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="252"/>
+      <c r="H3" s="253" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="241"/>
-      <c r="J3" s="241"/>
-      <c r="K3" s="241"/>
-      <c r="L3" s="241"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
       <c r="P3" s="254"/>
       <c r="Q3" s="254"/>
       <c r="R3" s="254"/>
@@ -22470,18 +22482,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="249" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
+      <c r="D5" s="249"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
+      <c r="H5" s="249"/>
+      <c r="I5" s="249"/>
+      <c r="J5" s="249"/>
+      <c r="K5" s="249"/>
+      <c r="L5" s="249"/>
       <c r="P5" s="254"/>
       <c r="Q5" s="254"/>
       <c r="R5" s="254"/>
@@ -22732,7 +22744,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22798,7 +22810,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>164908.41</v>
+        <v>163706.28</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22825,7 +22837,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>164381.41</v>
+        <v>163179.28</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -29648,7 +29660,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29722,7 +29734,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31091,7 +31103,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>18.868649318463444</v>
+        <v>18.731102850061959</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31132,7 +31144,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>13.551546752844647</v>
+        <v>13.452760275563126</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31197,7 +31209,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>18.604288131768953</v>
+        <v>18.468668772563177</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31262,7 +31274,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>182267.19</v>
+        <v>180938.52000000002</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31327,7 +31339,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>181740.19</v>
+        <v>180411.52000000002</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31368,7 +31380,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>14.067667002089944</v>
+        <v>13.964820806563978</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31409,7 +31421,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>40.812977767796994</v>
+        <v>40.51460139231979</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31556,7 +31568,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>36.460730146029206</v>
+        <v>36.194942988597724</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31597,7 +31609,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="204"/>
-        <v>50.968201509976964</v>
+        <v>50.595582111371399</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31638,7 +31650,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>2.7426768361327125E-2</v>
+        <v>2.7628168949320464E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31679,7 +31691,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>5.2997964142641366E-2</v>
+        <v>5.3387139454882243E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31720,7 +31732,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.0945469670103544E-3</v>
+        <v>1.1025844579694805E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31761,7 +31773,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.3663063001080994E-2</v>
+        <v>2.3836825900864004E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31802,7 +31814,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.5226701525381503E-2</v>
+        <v>2.5411946555106119E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32349,7 +32361,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.8913596572153221E-3</v>
+        <v>2.9125915255634894E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33787,15 +33799,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="243" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="241"/>
-      <c r="E4" s="241" t="s">
+      <c r="C4" s="243"/>
+      <c r="E4" s="243" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33803,7 +33815,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33819,7 +33831,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>182267.19</v>
+        <v>180938.52000000002</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33839,7 +33851,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>181740.19</v>
+        <v>180411.52000000002</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33859,7 +33871,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.868649318463444</v>
+        <v>18.731102850061959</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33879,7 +33891,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.551546752844647</v>
+        <v>13.452760275563126</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33899,7 +33911,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>18.604288131768953</v>
+        <v>18.468668772563177</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33919,7 +33931,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>14.067667002089944</v>
+        <v>13.964820806563978</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33928,18 +33940,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>40.812977767796994</v>
+        <v>40.51460139231979</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="241" t="s">
+      <c r="B15" s="243" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="241"/>
-      <c r="E15" s="241" t="s">
+      <c r="C15" s="243"/>
+      <c r="E15" s="243" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="241"/>
+      <c r="F15" s="243"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33990,14 +34002,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="241" t="s">
+      <c r="B21" s="243" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="241"/>
-      <c r="E21" s="241" t="s">
+      <c r="C21" s="243"/>
+      <c r="E21" s="243" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="241"/>
+      <c r="F21" s="243"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34066,14 +34078,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="241" t="s">
+      <c r="B29" s="243" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="241"/>
-      <c r="E29" s="241" t="s">
+      <c r="C29" s="243"/>
+      <c r="E29" s="243" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="241"/>
+      <c r="F29" s="243"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34149,14 +34161,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="241" t="s">
+      <c r="B37" s="243" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="241"/>
-      <c r="E37" s="241" t="s">
+      <c r="C37" s="243"/>
+      <c r="E37" s="243" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="241"/>
+      <c r="F37" s="243"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34164,7 +34176,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.2997964142641366E-2</v>
+        <v>5.3387139454882243E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34180,7 +34192,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.7426768361327125E-2</v>
+        <v>2.7628168949320464E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34196,7 +34208,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.0945469670103544E-3</v>
+        <v>1.1025844579694805E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34212,7 +34224,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.3663063001080994E-2</v>
+        <v>2.3836825900864004E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34221,18 +34233,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.5226701525381503E-2</v>
+        <v>2.5411946555106119E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="241" t="s">
+      <c r="B45" s="243" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="241"/>
-      <c r="E45" s="241" t="s">
+      <c r="C45" s="243"/>
+      <c r="E45" s="243" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="241"/>
+      <c r="F45" s="243"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34265,18 +34277,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>2.8913596572153221E-3</v>
+        <v>2.9125915255634894E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="241" t="s">
+      <c r="B51" s="243" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="241"/>
-      <c r="E51" s="241" t="s">
+      <c r="C51" s="243"/>
+      <c r="E51" s="243" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="241"/>
+      <c r="F51" s="243"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34444,7 +34456,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>456.81</v>
+        <v>453.48</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34473,7 +34485,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>182267.19</v>
+        <v>180938.52000000002</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34502,7 +34514,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>181740.19</v>
+        <v>180411.52000000002</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34531,7 +34543,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.868649318463444</v>
+        <v>18.731102850061959</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34560,7 +34572,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.551546752844647</v>
+        <v>13.452760275563126</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34589,7 +34601,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>18.604288131768953</v>
+        <v>18.468668772563177</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34618,7 +34630,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>14.067667002089944</v>
+        <v>13.964820806563978</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34647,7 +34659,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>40.812977767796994</v>
+        <v>40.51460139231979</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35420,7 +35432,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.2997964142641366E-2</v>
+        <v>5.3387139454882243E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35449,7 +35461,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.7426768361327125E-2</v>
+        <v>2.7628168949320464E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35478,7 +35490,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.0945469670103544E-3</v>
+        <v>1.1025844579694805E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35507,7 +35519,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.3663063001080994E-2</v>
+        <v>2.3836825900864004E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35536,7 +35548,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.5226701525381503E-2</v>
+        <v>2.5411946555106119E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35772,7 +35784,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.8913596572153221E-3</v>
+        <v>2.9125915255634894E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36261,14 +36273,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="247" t="s">
+      <c r="C3" s="244" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="F3" s="249" t="s">
+      <c r="D3" s="245"/>
+      <c r="F3" s="246" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="248"/>
+      <c r="G3" s="245"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36335,19 +36347,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="250">
+      <c r="C7" s="247">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="F7" s="250">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="251"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36374,19 +36386,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="250">
+      <c r="C9" s="247">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="F9" s="250">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="251"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36413,19 +36425,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="250">
+      <c r="C11" s="247">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="F11" s="250">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="251"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36452,19 +36464,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="250">
+      <c r="C13" s="247">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="F13" s="250">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="251"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36491,19 +36503,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="250">
+      <c r="C15" s="247">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="251"/>
-      <c r="F15" s="250">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="251"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36530,19 +36542,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="250">
+      <c r="C17" s="247">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="F17" s="250">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="251"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36569,22 +36581,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="250">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="F19" s="250">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="251"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36611,22 +36623,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="250">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="251"/>
-      <c r="F21" s="250">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="251"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36675,22 +36687,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="250">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="F25" s="250">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="251"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36718,22 +36730,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="250">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="F27" s="250">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="251"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -36761,22 +36773,22 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="250">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="F29" s="250">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="251"/>
+      <c r="G29" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="24">

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14C1598-FB6A-0545-B168-DA2FD8E4E68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCE9D56-5A71-7A42-93B2-3104DD3C0542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2412,6 +2412,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2419,12 +2425,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2445,14 +2445,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12824,12 +12824,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>111.83</v>
-    <v>2.1196000000000002</v>
-    <v>0.25</v>
-    <v>5.5159999999999996E-4</v>
-    <v>0.31</v>
-    <v>6.8360000000000003E-4</v>
+    <v>112.5201</v>
+    <v>2.2473000000000001</v>
+    <v>26.35</v>
+    <v>6.3449999999999993E-2</v>
+    <v>-0.37</v>
+    <v>-8.3779999999999998E-4</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12837,26 +12837,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>465.9</v>
+    <v>447.71</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46294.96077729141</v>
+    <v>46300.895150786717</v>
     <v>4</v>
-    <v>447.03</v>
-    <v>163498132680</v>
+    <v>429.44</v>
+    <v>159229327240</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>463.15</v>
-    <v>18.679600000000001</v>
-    <v>453.23</v>
-    <v>453.48</v>
-    <v>453.79</v>
+    <v>430.5</v>
+    <v>18.1919</v>
+    <v>415.29</v>
+    <v>441.64</v>
+    <v>441.27</v>
     <v>360541000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>6114581</v>
-    <v>6463752</v>
+    <v>11271953</v>
+    <v>7212332</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12878,19 +12878,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.93</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.15</v>
-    <v>2.8630000000000001E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.93</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>7</v>
-    <v>52.13</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.13</v>
-    <v>52.4</v>
-    <v>52.55</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>180938.52000000002</v>
+        <v>176214.36</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>180411.52000000002</v>
+        <v>175687.36</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13818,14 +13818,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>453.79</v>
+        <v>441.27</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>18.731102850061959</v>
+        <v>18.242048740190004</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13842,14 +13842,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.25</v>
+        <v>26.35</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>13.452760275563126</v>
+        <v>13.101519467451041</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13866,14 +13866,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.31</v>
+        <v>-0.37</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.7628168949320464E-2</v>
+        <v>2.8368857112439645E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13890,14 +13890,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>5.5159999999999996E-4</v>
+        <v>6.3449999999999993E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>5.3387139454882243E-2</v>
+        <v>5.4818404130060686E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.69986155525820148</v>
+        <v>-0.69181509391923102</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13914,14 +13914,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>6.8360000000000003E-4</v>
+        <v>-8.3779999999999998E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.3836825900864004E-2</v>
+        <v>2.4475871319454331E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.1025844579694805E-3</v>
+        <v>1.1321438275518523E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="C12" s="205" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>111.83</v>
+        <v>112.5201</v>
       </c>
       <c r="E12" s="181" t="s">
         <v>101</v>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1196000000000002</v>
+        <v>2.2473000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>6463752</v>
+        <v>7212332</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>2.9125915255634894E-3</v>
+        <v>2.9906756747860959E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.55</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18655,6 +18655,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18662,12 +18668,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19727,16 +19727,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>180938.52000000002</v>
+        <v>176214.36</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2549999999999999E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1196000000000002</v>
+        <v>2.2473000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.7805208754829638E-3</v>
+        <v>5.9345721320164758E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99421947912451702</v>
+        <v>0.99406542786798358</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14793200000000001</v>
+        <v>0.15389849999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14723670738805517</v>
+        <v>0.15314926917019112</v>
       </c>
     </row>
   </sheetData>
@@ -21792,17 +21792,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.69986155525820148</v>
+        <v>-0.69181509391923102</v>
       </c>
     </row>
   </sheetData>
@@ -22733,10 +22733,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="257"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22763,20 +22763,20 @@
       <c r="C17" s="156">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="255" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="256" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="257"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>163706.28</v>
+        <v>159432.04</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22837,15 +22837,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>163179.28</v>
+        <v>158905.04</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="256" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="257"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22921,16 +22921,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29660,7 +29660,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31103,7 +31103,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>18.731102850061959</v>
+        <v>18.242048740190004</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31144,7 +31144,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>13.452760275563126</v>
+        <v>13.101519467451041</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>18.468668772563177</v>
+        <v>17.986466606498194</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31274,7 +31274,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>180938.52000000002</v>
+        <v>176214.36</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31339,7 +31339,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>180411.52000000002</v>
+        <v>175687.36</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31380,7 +31380,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>13.964820806563978</v>
+        <v>13.59914544469386</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31421,7 +31421,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>40.51460139231979</v>
+        <v>39.453707612845271</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31526,8 +31526,8 @@
       <c r="Z156" s="49"/>
       <c r="AA156" s="49"/>
       <c r="AC156" s="64">
-        <f>AC107+AC52+AC108+AC54+AC56+AC57</f>
-        <v>3565.7563856638062</v>
+        <f t="shared" ref="AC156" si="202">AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
+        <v>3191.7563856638062</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31539,23 +31539,23 @@
         <v>37.870115207373274</v>
       </c>
       <c r="M157" s="72">
-        <f t="shared" ref="M157:P157" si="202">M151/M155</f>
+        <f t="shared" ref="M157:P157" si="203">M151/M155</f>
         <v>27.199305555555561</v>
       </c>
       <c r="N157" s="72">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>-8.1301357466063351</v>
       </c>
       <c r="O157" s="72">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>-24.15344795539033</v>
       </c>
       <c r="P157" s="72">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>22.472692307692306</v>
       </c>
       <c r="Q157" s="72">
-        <f t="shared" ref="Q157" si="203">Q151/Q155</f>
+        <f t="shared" ref="Q157" si="204">Q151/Q155</f>
         <v>65.032053220441483</v>
       </c>
       <c r="T157" s="49"/>
@@ -31567,8 +31567,8 @@
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
-        <f t="shared" ref="AC157:AC158" ca="1" si="204">AC151/AC155</f>
-        <v>36.194942988597724</v>
+        <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
+        <v>35.249921984396877</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31580,23 +31580,23 @@
         <v>22.429968797781868</v>
       </c>
       <c r="M158" s="72">
-        <f t="shared" ref="M158:P158" si="205">M152/M156</f>
+        <f t="shared" ref="M158:P158" si="206">M152/M156</f>
         <v>38.981647804001206</v>
       </c>
       <c r="N158" s="72">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>-41.203385300668153</v>
       </c>
       <c r="O158" s="72">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>-50.513688394276627</v>
       </c>
       <c r="P158" s="72">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>19.085923994038748</v>
       </c>
       <c r="Q158" s="72">
-        <f t="shared" ref="Q158" si="206">Q152/Q156</f>
+        <f t="shared" ref="Q158" si="207">Q152/Q156</f>
         <v>60.675560360961683</v>
       </c>
       <c r="T158" s="49"/>
@@ -31608,8 +31608,8 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
-        <f t="shared" ca="1" si="204"/>
-        <v>50.595582111371399</v>
+        <f t="shared" ca="1" si="205"/>
+        <v>55.044100730595503</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31621,23 +31621,23 @@
         <v>2.6406045889327028E-2</v>
       </c>
       <c r="M159" s="74">
-        <f t="shared" ref="M159:P159" si="207">M155/M151</f>
+        <f t="shared" ref="M159:P159" si="208">M155/M151</f>
         <v>3.6765644547705971E-2</v>
       </c>
       <c r="N159" s="74">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>-0.12299917629510898</v>
       </c>
       <c r="O159" s="74">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>-4.1401956434829822E-2</v>
       </c>
       <c r="P159" s="74">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v>4.4498451111605546E-2</v>
       </c>
       <c r="Q159" s="74">
-        <f t="shared" ref="Q159" si="208">Q155/Q151</f>
+        <f t="shared" ref="Q159" si="209">Q155/Q151</f>
         <v>1.537703256285426E-2</v>
       </c>
       <c r="T159" s="49"/>
@@ -31649,8 +31649,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
-        <f t="shared" ref="AC159" ca="1" si="209">AC155/AC151</f>
-        <v>2.7628168949320464E-2</v>
+        <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
+        <v>2.8368857112439645E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31658,27 +31658,27 @@
         <v>265</v>
       </c>
       <c r="L160" s="74">
-        <f t="shared" ref="L160:Q160" si="210">L25/L115</f>
+        <f t="shared" ref="L160:Q160" si="211">L25/L115</f>
         <v>5.065701771091221E-2</v>
       </c>
       <c r="M160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>0.12855209742895804</v>
       </c>
       <c r="N160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>-7.4500768049155147E-2</v>
       </c>
       <c r="O160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>-3.3126567242972152E-2</v>
       </c>
       <c r="P160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>6.9716434278552411E-2</v>
       </c>
       <c r="Q160" s="74">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v>4.5046382189239335E-2</v>
       </c>
       <c r="T160" s="49"/>
@@ -31691,7 +31691,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>5.3387139454882243E-2</v>
+        <v>5.4818404130060686E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31699,27 +31699,27 @@
         <v>266</v>
       </c>
       <c r="L161" s="152">
-        <f t="shared" ref="L161:Q161" si="211">L81/L115</f>
+        <f t="shared" ref="L161:Q161" si="212">L81/L115</f>
         <v>0</v>
       </c>
       <c r="M161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="N161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="O161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="P161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>1.5666614444618519E-3</v>
       </c>
       <c r="Q161" s="152">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v>9.2764378478664194E-4</v>
       </c>
       <c r="T161" s="49"/>
@@ -31732,7 +31732,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.1025844579694805E-3</v>
+        <v>1.1321438275518523E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31740,27 +31740,27 @@
         <v>291</v>
       </c>
       <c r="L162" s="152">
-        <f t="shared" ref="L162:Q162" si="212">-L62/L151</f>
+        <f t="shared" ref="L162:Q162" si="213">-L62/L151</f>
         <v>0</v>
       </c>
       <c r="M162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>0</v>
       </c>
       <c r="N162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>0</v>
       </c>
       <c r="O162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>0</v>
       </c>
       <c r="P162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>6.5387270371096906E-3</v>
       </c>
       <c r="Q162" s="152">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v>1.2052394436927197E-2</v>
       </c>
       <c r="T162" s="49"/>
@@ -31773,7 +31773,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.3836825900864004E-2</v>
+        <v>2.4475871319454331E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31781,27 +31781,27 @@
         <v>293</v>
       </c>
       <c r="L163" s="152">
-        <f t="shared" ref="L163:Q163" si="213">-(L62+L63)/L151</f>
+        <f t="shared" ref="L163:Q163" si="214">-(L62+L63)/L151</f>
         <v>0</v>
       </c>
       <c r="M163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0</v>
       </c>
       <c r="N163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0</v>
       </c>
       <c r="O163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0</v>
       </c>
       <c r="P163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>8.4696262963904045E-3</v>
       </c>
       <c r="Q163" s="152">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>1.2907965646955981E-2</v>
       </c>
       <c r="T163" s="49"/>
@@ -31814,7 +31814,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.5411946555106119E-2</v>
+        <v>2.6093219644528404E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31822,27 +31822,27 @@
         <v>340</v>
       </c>
       <c r="L164" s="152">
-        <f t="shared" ref="L164:Q164" si="214">L156/L5</f>
+        <f t="shared" ref="L164:Q164" si="215">L156/L5</f>
         <v>5.7410248456430654E-2</v>
       </c>
       <c r="M164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>2.2420831520460437E-2</v>
       </c>
       <c r="N164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-7.1782573940847319E-2</v>
       </c>
       <c r="O164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>-9.9572581921798325E-2</v>
       </c>
       <c r="P164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.14096638655462185</v>
       </c>
       <c r="Q164" s="152">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v>0.27368653809612248</v>
       </c>
       <c r="T164" s="49"/>
@@ -31855,7 +31855,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="152">
         <f>AC156/AC5</f>
-        <v>0.27600869925410682</v>
+        <v>0.24705909015123509</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -31863,27 +31863,27 @@
         <v>341</v>
       </c>
       <c r="L165" s="152">
-        <f t="shared" ref="L165:Q165" si="215">L155/L5</f>
+        <f t="shared" ref="L165:Q165" si="216">L155/L5</f>
         <v>2.5647086632785723E-2</v>
       </c>
       <c r="M165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>2.2987282498802747E-2</v>
       </c>
       <c r="N165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>-0.24732214228617105</v>
       </c>
       <c r="O165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>-0.17033401931296502</v>
       </c>
       <c r="P165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>0.1065126050420168</v>
       </c>
       <c r="Q165" s="152">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v>0.25597956498180974</v>
       </c>
       <c r="T165" s="49"/>
@@ -31904,27 +31904,27 @@
         <v>269</v>
       </c>
       <c r="L166" s="152">
-        <f t="shared" ref="L166:Q166" si="216">-L63/L155</f>
+        <f t="shared" ref="L166:Q166" si="217">-L63/L155</f>
         <v>0</v>
       </c>
       <c r="M166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0</v>
       </c>
       <c r="N166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0</v>
       </c>
       <c r="O166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>0</v>
       </c>
       <c r="P166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>4.3392504930966469E-2</v>
       </c>
       <c r="Q166" s="152">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v>5.5639552464469305E-2</v>
       </c>
       <c r="T166" s="49"/>
@@ -31945,27 +31945,27 @@
         <v>271</v>
       </c>
       <c r="L167" s="152">
-        <f t="shared" ref="L167:Q167" si="217">-L62/L155</f>
+        <f t="shared" ref="L167:Q167" si="218">-L62/L155</f>
         <v>0</v>
       </c>
       <c r="M167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0</v>
       </c>
       <c r="N167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0</v>
       </c>
       <c r="O167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0</v>
       </c>
       <c r="P167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0.14694280078895464</v>
       </c>
       <c r="Q167" s="152">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v>0.78379195645600241</v>
       </c>
       <c r="T167" s="49"/>
@@ -31986,27 +31986,27 @@
         <v>282</v>
       </c>
       <c r="L168" s="152">
-        <f t="shared" ref="L168:Q168" si="218">(-L63-L62)/L155</f>
+        <f t="shared" ref="L168:Q168" si="219">(-L63-L62)/L155</f>
         <v>0</v>
       </c>
       <c r="M168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0</v>
       </c>
       <c r="N168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0</v>
       </c>
       <c r="O168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0</v>
       </c>
       <c r="P168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0.19033530571992111</v>
       </c>
       <c r="Q168" s="152">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0.83943150892047169</v>
       </c>
       <c r="T168" s="49"/>
@@ -32027,27 +32027,27 @@
         <v>276</v>
       </c>
       <c r="L169" s="152">
-        <f t="shared" ref="L169:Q169" si="219">L79/L77</f>
+        <f t="shared" ref="L169:Q169" si="220">L79/L77</f>
         <v>3.1948881789137375E-3</v>
       </c>
       <c r="M169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>3.1446540880503142E-3</v>
       </c>
       <c r="N169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>3.105590062111801E-3</v>
       </c>
       <c r="O169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>2.9154518950437317E-3</v>
       </c>
       <c r="P169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>2.8011204481792717E-3</v>
       </c>
       <c r="Q169" s="152">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>2.5062656641604009E-3</v>
       </c>
       <c r="T169" s="49"/>
@@ -32068,59 +32068,59 @@
         <v>277</v>
       </c>
       <c r="L170" s="72">
-        <f t="shared" ref="L170:Q170" si="220">L105/L74</f>
+        <f t="shared" ref="L170:Q170" si="221">L105/L74</f>
         <v>8.6351139091954998</v>
       </c>
       <c r="M170" s="72">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>5.8676389750417313</v>
       </c>
       <c r="N170" s="72">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>4.9743536782677547</v>
       </c>
       <c r="O170" s="72">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>4.3373983458330745</v>
       </c>
       <c r="P170" s="72">
-        <f t="shared" si="220"/>
-        <v>6.1275362318840578</v>
-      </c>
-      <c r="Q170" s="72">
-        <f t="shared" si="220"/>
-        <v>4.3739612188365653</v>
-      </c>
-      <c r="T170" s="72">
-        <f t="shared" ref="T170:Z170" si="221">T105/T74</f>
-        <v>3.9016196870466229</v>
-      </c>
-      <c r="U170" s="72">
-        <f t="shared" si="221"/>
-        <v>5.2124571126946426</v>
-      </c>
-      <c r="V170" s="72">
-        <f t="shared" si="221"/>
-        <v>9.9627507163323781</v>
-      </c>
-      <c r="W170" s="72">
         <f t="shared" si="221"/>
         <v>6.1275362318840578</v>
       </c>
+      <c r="Q170" s="72">
+        <f t="shared" si="221"/>
+        <v>4.3739612188365653</v>
+      </c>
+      <c r="T170" s="72">
+        <f t="shared" ref="T170:Z170" si="222">T105/T74</f>
+        <v>3.9016196870466229</v>
+      </c>
+      <c r="U170" s="72">
+        <f t="shared" si="222"/>
+        <v>5.2124571126946426</v>
+      </c>
+      <c r="V170" s="72">
+        <f t="shared" si="222"/>
+        <v>9.9627507163323781</v>
+      </c>
+      <c r="W170" s="72">
+        <f t="shared" si="222"/>
+        <v>6.1275362318840578</v>
+      </c>
       <c r="X170" s="72">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>5.9883040935672511</v>
       </c>
       <c r="Y170" s="72">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>5.8259587020648969</v>
       </c>
       <c r="Z170" s="72">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>5.9420289855072461</v>
       </c>
       <c r="AA170" s="72">
-        <f t="shared" ref="AA170" si="222">AA105/AA74</f>
+        <f t="shared" ref="AA170" si="223">AA105/AA74</f>
         <v>4.3739612188365653</v>
       </c>
       <c r="AC170" s="72">
@@ -32133,59 +32133,59 @@
         <v>279</v>
       </c>
       <c r="L171" s="152">
-        <f t="shared" ref="L171:Q171" si="223">L53/L58</f>
+        <f t="shared" ref="L171:Q171" si="224">L53/L58</f>
         <v>0.16754478398314016</v>
       </c>
       <c r="M171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.17340425531914894</v>
       </c>
       <c r="N171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-0.77941176470588236</v>
       </c>
       <c r="O171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>-1.0034013605442176</v>
       </c>
       <c r="P171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.15671200473092844</v>
       </c>
       <c r="Q171" s="152">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>5.1921608551794347E-2</v>
       </c>
       <c r="T171" s="152">
-        <f t="shared" ref="T171:Z171" si="224">T53/T58</f>
+        <f t="shared" ref="T171:Z171" si="225">T53/T58</f>
         <v>2.4705882352941178</v>
       </c>
       <c r="U171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0.36842105263157893</v>
       </c>
       <c r="V171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0.23280423280423279</v>
       </c>
       <c r="W171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>6.0321715817694369E-2</v>
       </c>
       <c r="X171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>7.8869047619047616E-2</v>
       </c>
       <c r="Y171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>7.4805928016937195E-2</v>
       </c>
       <c r="Z171" s="152">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>6.2598425196850396E-2</v>
       </c>
       <c r="AA171" s="152">
-        <f t="shared" ref="AA171" si="225">AA53/AA58</f>
+        <f t="shared" ref="AA171" si="226">AA53/AA58</f>
         <v>3.2397408207343416E-2</v>
       </c>
       <c r="AC171" s="152">
@@ -32198,59 +32198,59 @@
         <v>280</v>
       </c>
       <c r="L172" s="152">
-        <f t="shared" ref="L172:Q172" si="226">L53/L5</f>
+        <f t="shared" ref="L172:Q172" si="227">L53/L5</f>
         <v>1.8792104952133317E-2</v>
       </c>
       <c r="M172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>1.7346884478263182E-2</v>
       </c>
       <c r="N172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>5.0839328537170263E-2</v>
       </c>
       <c r="O172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>4.6699382618331488E-2</v>
       </c>
       <c r="P172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>2.7836134453781514E-2</v>
       </c>
       <c r="Q172" s="152">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v>1.5790695874293676E-2</v>
       </c>
       <c r="T172" s="152">
-        <f t="shared" ref="T172:Z172" si="227">T53/T5</f>
+        <f t="shared" ref="T172:Z172" si="228">T53/T5</f>
         <v>3.7974683544303799E-2</v>
       </c>
       <c r="U172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>6.6832710668327105E-2</v>
       </c>
       <c r="V172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>9.5902353966870094E-2</v>
       </c>
       <c r="W172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>1.7274472168905951E-2</v>
       </c>
       <c r="X172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>1.8807665010645847E-2</v>
       </c>
       <c r="Y172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>3.5134239310573419E-2</v>
       </c>
       <c r="Z172" s="152">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v>4.7647587653581062E-2</v>
       </c>
       <c r="AA172" s="152">
-        <f t="shared" ref="AA172" si="228">AA53/AA5</f>
+        <f t="shared" ref="AA172" si="229">AA53/AA5</f>
         <v>1.2009607686148919E-2</v>
       </c>
       <c r="AC172" s="152">
@@ -32263,59 +32263,59 @@
         <v>285</v>
       </c>
       <c r="L173" s="72">
-        <f t="shared" ref="L173:Q173" si="229">(L105-L106)/L74</f>
+        <f t="shared" ref="L173:Q173" si="230">(L105-L106)/L74</f>
         <v>-13.72137536609552</v>
       </c>
       <c r="M173" s="72">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-11.788230429015941</v>
       </c>
       <c r="N173" s="72">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-12.410065750972496</v>
       </c>
       <c r="O173" s="72">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v>-12.822909958011032</v>
       </c>
       <c r="P173" s="72">
-        <f t="shared" si="229"/>
-        <v>-7.5275362318840582</v>
-      </c>
-      <c r="Q173" s="72">
-        <f t="shared" si="229"/>
-        <v>1.4598337950138505</v>
-      </c>
-      <c r="T173" s="72">
-        <f t="shared" ref="T173:Z173" si="230">(T105-T106)/T74</f>
-        <v>-13.032096256733441</v>
-      </c>
-      <c r="U173" s="72">
-        <f t="shared" si="230"/>
-        <v>-11.546582211665349</v>
-      </c>
-      <c r="V173" s="72">
-        <f t="shared" si="230"/>
-        <v>-11.048710601719197</v>
-      </c>
-      <c r="W173" s="72">
         <f t="shared" si="230"/>
         <v>-7.5275362318840582</v>
       </c>
+      <c r="Q173" s="72">
+        <f t="shared" si="230"/>
+        <v>1.4598337950138505</v>
+      </c>
+      <c r="T173" s="72">
+        <f t="shared" ref="T173:Z173" si="231">(T105-T106)/T74</f>
+        <v>-13.032096256733441</v>
+      </c>
+      <c r="U173" s="72">
+        <f t="shared" si="231"/>
+        <v>-11.546582211665349</v>
+      </c>
+      <c r="V173" s="72">
+        <f t="shared" si="231"/>
+        <v>-11.048710601719197</v>
+      </c>
+      <c r="W173" s="72">
+        <f t="shared" si="231"/>
+        <v>-7.5275362318840582</v>
+      </c>
       <c r="X173" s="72">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>-7.704678362573099</v>
       </c>
       <c r="Y173" s="72">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>-7.9056047197640114</v>
       </c>
       <c r="Z173" s="72">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v>1.3594202898550725</v>
       </c>
       <c r="AA173" s="72">
-        <f t="shared" ref="AA173" si="231">(AA105-AA106)/AA74</f>
+        <f t="shared" ref="AA173" si="232">(AA105-AA106)/AA74</f>
         <v>1.4598337950138505</v>
       </c>
       <c r="AC173" s="72">
@@ -32328,27 +32328,27 @@
         <v>290</v>
       </c>
       <c r="L174" s="152">
-        <f t="shared" ref="L174:Q174" si="232">(L105-L106)/L151</f>
+        <f t="shared" ref="L174:Q174" si="233">(L105-L106)/L151</f>
         <v>-0.32581653395701898</v>
       </c>
       <c r="M174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.39786895430677177</v>
       </c>
       <c r="N174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.40127785569580804</v>
       </c>
       <c r="O174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.21374337174301083</v>
       </c>
       <c r="P174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>-0.11396694037163668</v>
       </c>
       <c r="Q174" s="152">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v>2.4504675417672196E-3</v>
       </c>
       <c r="T174" s="49"/>
@@ -32361,7 +32361,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.9125915255634894E-3</v>
+        <v>2.9906756747860959E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -32369,59 +32369,59 @@
         <v>299</v>
       </c>
       <c r="L175" s="152">
-        <f t="shared" ref="L175:Q175" si="233">-L108/L5</f>
+        <f t="shared" ref="L175:Q175" si="234">-L108/L5</f>
         <v>6.7722491431272902E-2</v>
       </c>
       <c r="M175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>5.9703080934390466E-2</v>
       </c>
       <c r="N175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>0.13125499600319745</v>
       </c>
       <c r="O175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>7.7093557068228596E-2</v>
       </c>
       <c r="P175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>4.3277310924369747E-2</v>
       </c>
       <c r="Q175" s="152">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v>3.2355445467915474E-2</v>
       </c>
       <c r="T175" s="152">
-        <f t="shared" ref="T175:Z175" si="234">-T108/T5</f>
+        <f t="shared" ref="T175:Z175" si="235">-T108/T5</f>
         <v>4.3399638336347197E-2</v>
       </c>
       <c r="U175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>8.8003320880033209E-2</v>
       </c>
       <c r="V175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>0.14864864864864866</v>
       </c>
       <c r="W175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>2.72552783109405E-2</v>
       </c>
       <c r="X175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>2.5904897090134847E-2</v>
       </c>
       <c r="Y175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>5.4690089492873718E-2</v>
       </c>
       <c r="Z175" s="152">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v>9.2897812406353017E-2</v>
       </c>
       <c r="AA175" s="152">
-        <f t="shared" ref="AA175" si="235">-AA108/AA5</f>
+        <f t="shared" ref="AA175" si="236">-AA108/AA5</f>
         <v>2.8823058446757407E-2</v>
       </c>
       <c r="AC175" s="152">
@@ -32434,59 +32434,59 @@
         <v>300</v>
       </c>
       <c r="L176" s="152">
-        <f t="shared" ref="L176:Q176" si="236">-(L108/L58)</f>
+        <f t="shared" ref="L176:Q176" si="237">-(L108/L58)</f>
         <v>0.60379346680716539</v>
       </c>
       <c r="M176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.59680851063829787</v>
       </c>
       <c r="N176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>-2.0122549019607843</v>
       </c>
       <c r="O176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>-1.6564625850340136</v>
       </c>
       <c r="P176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.24364281490242459</v>
       </c>
       <c r="Q176" s="152">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v>0.10638839399338254</v>
       </c>
       <c r="T176" s="152">
-        <f t="shared" ref="T176:Z176" si="237">-(T108/T58)</f>
+        <f t="shared" ref="T176:Z176" si="238">-(T108/T58)</f>
         <v>2.8235294117647061</v>
       </c>
       <c r="U176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.48512585812356979</v>
       </c>
       <c r="V176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.36084656084656086</v>
       </c>
       <c r="W176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>9.5174262734584444E-2</v>
       </c>
       <c r="X176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.10863095238095238</v>
       </c>
       <c r="Y176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.11644318983768526</v>
       </c>
       <c r="Z176" s="152">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v>0.12204724409448819</v>
       </c>
       <c r="AA176" s="152">
-        <f t="shared" ref="AA176" si="238">-(AA108/AA58)</f>
+        <f t="shared" ref="AA176" si="239">-(AA108/AA58)</f>
         <v>7.775377969762419E-2</v>
       </c>
       <c r="AC176" s="152">
@@ -32499,59 +32499,59 @@
         <v>301</v>
       </c>
       <c r="L177" s="152">
-        <f t="shared" ref="L177:Q177" si="239">-L108/L52</f>
+        <f t="shared" ref="L177:Q177" si="240">-L108/L52</f>
         <v>0.9455445544554455</v>
       </c>
       <c r="M177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>1.2077502691065662</v>
       </c>
       <c r="N177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0.99154589371980673</v>
       </c>
       <c r="O177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0.85739436619718312</v>
       </c>
       <c r="P177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>0.91352549889135259</v>
       </c>
       <c r="Q177" s="152">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v>1.1146666666666667</v>
       </c>
       <c r="T177" s="152">
-        <f t="shared" ref="T177:Z177" si="240">-T108/T52</f>
+        <f t="shared" ref="T177:Z177" si="241">-T108/T52</f>
         <v>0.71111111111111114</v>
       </c>
       <c r="U177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>0.83137254901960789</v>
       </c>
       <c r="V177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>0.9342465753424658</v>
       </c>
       <c r="W177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>0.82558139534883723</v>
       </c>
       <c r="X177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>0.82954545454545459</v>
       </c>
       <c r="Y177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="Z177" s="152">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v>1.1231884057971016</v>
       </c>
       <c r="AA177" s="152">
-        <f t="shared" ref="AA177" si="241">-AA108/AA52</f>
+        <f t="shared" ref="AA177" si="242">-AA108/AA52</f>
         <v>1.0909090909090908</v>
       </c>
       <c r="AC177" s="152">
@@ -32564,27 +32564,27 @@
         <v>353</v>
       </c>
       <c r="L178" s="220">
-        <f t="shared" ref="L178:Q178" si="242">L5/L36</f>
+        <f t="shared" ref="L178:Q178" si="243">L5/L36</f>
         <v>0.64755854890555642</v>
       </c>
       <c r="M178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.71567843406070297</v>
       </c>
       <c r="N178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.25604813950632443</v>
       </c>
       <c r="O178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.26116255994708121</v>
       </c>
       <c r="P178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.67990287101842595</v>
       </c>
       <c r="Q178" s="220">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.93203953538705719</v>
       </c>
       <c r="T178" s="49"/>
@@ -32605,27 +32605,27 @@
         <v>350</v>
       </c>
       <c r="L179" s="222">
-        <f t="shared" ref="L179:Q179" si="243">IF(AND(L11&gt;0,L106&gt;0),L106/L11,"N/A")</f>
+        <f t="shared" ref="L179:Q179" si="244">IF(AND(L11&gt;0,L106&gt;0),L106/L11,"N/A")</f>
         <v>7.1516393442622954</v>
       </c>
       <c r="M179" s="222">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>2.9284818067754079</v>
       </c>
       <c r="N179" s="222" t="str">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>N/A</v>
       </c>
       <c r="O179" s="222" t="str">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>N/A</v>
       </c>
       <c r="P179" s="222">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>2.0184233076263927</v>
       </c>
       <c r="Q179" s="222">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v>0.23624522793622277</v>
       </c>
       <c r="T179" s="49"/>
@@ -32646,27 +32646,27 @@
         <v>351</v>
       </c>
       <c r="L180" s="222">
-        <f t="shared" ref="L180:Q180" si="244">IF(AND(L11&gt;0,L106&gt;0),(L106-L105)/L11,"N/A")</f>
+        <f t="shared" ref="L180:Q180" si="245">IF(AND(L11&gt;0,L106&gt;0),(L106-L105)/L11,"N/A")</f>
         <v>4.389344262295082</v>
       </c>
       <c r="M180" s="222">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>1.9552488498536178</v>
       </c>
       <c r="N180" s="222" t="str">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>N/A</v>
       </c>
       <c r="O180" s="222" t="str">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>N/A</v>
       </c>
       <c r="P180" s="222">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>1.1126820908311912</v>
       </c>
       <c r="Q180" s="222">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v>-0.1183471816752751</v>
       </c>
       <c r="T180" s="49"/>
@@ -32687,27 +32687,27 @@
         <v>352</v>
       </c>
       <c r="L181" s="222">
-        <f t="shared" ref="L181:Q181" si="245">L5/(L106+L110-L105)</f>
+        <f t="shared" ref="L181:Q181" si="246">L5/(L106+L110-L105)</f>
         <v>1.0526250311022642</v>
       </c>
       <c r="M181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>1.1122750946969697</v>
       </c>
       <c r="N181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0.39354473386183464</v>
       </c>
       <c r="O181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>0.38581811518964149</v>
       </c>
       <c r="P181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>1.2038442083965604</v>
       </c>
       <c r="Q181" s="222">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v>1.5495981768022071</v>
       </c>
       <c r="T181" s="49"/>
@@ -32853,7 +32853,7 @@
         <v>225</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" ref="AC186:AC187" si="246">SUM(X186:AA186)</f>
+        <f t="shared" ref="AC186:AC187" si="247">SUM(X186:AA186)</f>
         <v>726</v>
       </c>
     </row>
@@ -32913,7 +32913,7 @@
         <v>187</v>
       </c>
       <c r="AC187" s="62">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v>703</v>
       </c>
     </row>
@@ -32977,98 +32977,98 @@
       <c r="J191" s="81"/>
       <c r="K191" s="81"/>
       <c r="L191" s="81">
-        <f t="shared" ref="L191:L193" si="247">IF(K185=0,
+        <f t="shared" ref="L191:L193" si="248">IF(K185=0,
 IF(L185=0,0,IF(L185&gt;0,1,-1)),
 (L185-K185)/ABS(K185)
 )</f>
         <v>1</v>
       </c>
       <c r="M191" s="81">
-        <f t="shared" ref="M191:M193" si="248">IF(L185=0,
+        <f t="shared" ref="M191:M193" si="249">IF(L185=0,
 IF(M185=0,0,IF(M185&gt;0,1,-1)),
 (M185-L185)/ABS(L185)
 )</f>
         <v>0.4008387209505504</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" ref="N191:N193" si="249">IF(M185=0,
+        <f t="shared" ref="N191:N193" si="250">IF(M185=0,
 IF(N185=0,0,IF(N185&gt;0,1,-1)),
 (N185-M185)/ABS(M185)
 )</f>
         <v>-0.40713483846825493</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" ref="O191:O193" si="250">IF(N185=0,
+        <f t="shared" ref="O191:O193" si="251">IF(N185=0,
 IF(O185=0,0,IF(O185&gt;0,1,-1)),
 (O185-N185)/ABS(N185)
 )</f>
         <v>6.2907637281716805E-2</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" ref="P191:P193" si="251">IF(O185=0,
+        <f t="shared" ref="P191:P193" si="252">IF(O185=0,
 IF(P185=0,0,IF(P185&gt;0,1,-1)),
 (P185-O185)/ABS(O185)
 )</f>
         <v>0.65102929532858278</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" ref="Q191:Q193" si="252">IF(P185=0,
+        <f t="shared" ref="Q191:Q193" si="253">IF(P185=0,
 IF(Q185=0,0,IF(Q185&gt;0,1,-1)),
 (Q185-P185)/ABS(P185)
 )</f>
         <v>0.37753266994365187</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" ref="T191:T193" si="253">IF(S185=0,
+        <f t="shared" ref="T191:T193" si="254">IF(S185=0,
 IF(T185=0,0,IF(T185&gt;0,1,-1)),
 (T185-S185)/ABS(S185)
 )</f>
         <v>1</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" ref="U191:U193" si="254">IF(T185=0,
+        <f t="shared" ref="U191:U193" si="255">IF(T185=0,
 IF(U185=0,0,IF(U185&gt;0,1,-1)),
 (U185-T185)/ABS(T185)
 )</f>
         <v>9.7957045573598744E-2</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" ref="V191:V193" si="255">IF(U185=0,
+        <f t="shared" ref="V191:V193" si="256">IF(U185=0,
 IF(V185=0,0,IF(V185&gt;0,1,-1)),
 (V185-U185)/ABS(U185)
 )</f>
         <v>-4.2461832061068704E-2</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" ref="W191:W193" si="256">IF(V185=0,
+        <f t="shared" ref="W191:W193" si="257">IF(V185=0,
 IF(W185=0,0,IF(W185&gt;0,1,-1)),
 (W185-V185)/ABS(V185)
 )</f>
         <v>0.16043846537120079</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" ref="X191:X193" si="257">IF(W185=0,
+        <f t="shared" ref="X191:X193" si="258">IF(W185=0,
 IF(X185=0,0,IF(X185&gt;0,1,-1)),
 (X185-W185)/ABS(W185)
 )</f>
         <v>7.7715757835981114E-2</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" ref="Y191:Y193" si="258">IF(X185=0,
+        <f t="shared" ref="Y191:Y193" si="259">IF(X185=0,
 IF(Y185=0,0,IF(Y185&gt;0,1,-1)),
 (Y185-X185)/ABS(X185)
 )</f>
         <v>6.4940239043824705E-2</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" ref="Z191:Z193" si="259">IF(Y185=0,
+        <f t="shared" ref="Z191:Z193" si="260">IF(Y185=0,
 IF(Z185=0,0,IF(Z185&gt;0,1,-1)),
 (Z185-Y185)/ABS(Y185)
 )</f>
         <v>0.11185933408155631</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" ref="AA191:AA193" si="260">IF(Z185=0,
+        <f t="shared" ref="AA191:AA193" si="261">IF(Z185=0,
 IF(AA185=0,0,IF(AA185&gt;0,1,-1)),
 (AA185-Z185)/ABS(Z185)
 )</f>
@@ -33082,59 +33082,59 @@
         <v>Client</v>
       </c>
       <c r="L192" s="81">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>1</v>
       </c>
       <c r="M192" s="81">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>-2.8155473149292679E-2</v>
       </c>
       <c r="N192" s="81">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v>-0.90234595816845675</v>
       </c>
       <c r="O192" s="81">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v>-0.16497829232995659</v>
       </c>
       <c r="P192" s="81">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>-3.6395147313691506E-2</v>
       </c>
       <c r="Q192" s="81">
-        <f t="shared" si="252"/>
+        <f t="shared" si="253"/>
         <v>0.30575539568345322</v>
       </c>
       <c r="T192" s="81">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>1</v>
       </c>
       <c r="U192" s="81">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>7.1942446043165471E-3</v>
       </c>
       <c r="V192" s="81">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>-2.1428571428571429E-2</v>
       </c>
       <c r="W192" s="81">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>2.1897810218978103E-2</v>
       </c>
       <c r="X192" s="81">
-        <f t="shared" si="257"/>
+        <f t="shared" si="258"/>
         <v>4.2857142857142858E-2</v>
       </c>
       <c r="Y192" s="81">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.20547945205479451</v>
       </c>
       <c r="Z192" s="81">
-        <f t="shared" si="259"/>
+        <f t="shared" si="260"/>
         <v>1.7045454545454544E-2</v>
       </c>
       <c r="AA192" s="81">
-        <f t="shared" si="260"/>
+        <f t="shared" si="261"/>
         <v>0.25698324022346369</v>
       </c>
       <c r="AC192" s="49"/>
@@ -33145,59 +33145,59 @@
         <v>Consumer</v>
       </c>
       <c r="L193" s="81">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>1</v>
       </c>
       <c r="M193" s="81">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>-5.5640632976008166E-2</v>
       </c>
       <c r="N193" s="81">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v>-0.78081081081081083</v>
       </c>
       <c r="O193" s="81">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v>-0.15166461159062886</v>
       </c>
       <c r="P193" s="81">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>-9.4476744186046513E-2</v>
       </c>
       <c r="Q193" s="81">
-        <f t="shared" si="252"/>
+        <f t="shared" si="253"/>
         <v>0.12841091492776885</v>
       </c>
       <c r="T193" s="81">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>1</v>
       </c>
       <c r="U193" s="81">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>5.4878048780487805E-2</v>
       </c>
       <c r="V193" s="81">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>-0.13294797687861271</v>
       </c>
       <c r="W193" s="81">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>-9.3333333333333338E-2</v>
       </c>
       <c r="X193" s="81">
-        <f t="shared" si="257"/>
+        <f t="shared" si="258"/>
         <v>0.19117647058823528</v>
       </c>
       <c r="Y193" s="81">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>3.7037037037037035E-2</v>
       </c>
       <c r="Z193" s="81">
-        <f t="shared" si="259"/>
+        <f t="shared" si="260"/>
         <v>0.10714285714285714</v>
       </c>
       <c r="AA193" s="81">
-        <f t="shared" si="260"/>
+        <f t="shared" si="261"/>
         <v>5.3763440860215058E-3</v>
       </c>
       <c r="AC193" s="49"/>
@@ -33248,30 +33248,30 @@
       <c r="J197" s="81"/>
       <c r="K197" s="81"/>
       <c r="L197" s="81">
-        <f t="shared" ref="L197:Q197" si="261">IF(K63=0,
+        <f t="shared" ref="L197:Q197" si="262">IF(K63=0,
 IF(L63=0,0,IF(L63&gt;0,1,-1)),
 (L63-K63)/K63
 )</f>
         <v>0</v>
       </c>
       <c r="M197" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>0</v>
       </c>
       <c r="N197" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>0</v>
       </c>
       <c r="O197" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>0</v>
       </c>
       <c r="P197" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>-1</v>
       </c>
       <c r="Q197" s="81">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v>3.1818181818181817</v>
       </c>
       <c r="T197" s="49"/>
@@ -33328,19 +33328,19 @@
         <v>100</v>
       </c>
       <c r="N201" s="141">
-        <f t="shared" ref="N201:P201" si="262">100*(1+((N115-$M115)/ABS($M115)))</f>
+        <f t="shared" ref="N201:P201" si="263">100*(1+((N115-$M115)/ABS($M115)))</f>
         <v>105.7104194857916</v>
       </c>
       <c r="O201" s="141">
-        <f t="shared" si="262"/>
+        <f t="shared" si="263"/>
         <v>205.06089309878212</v>
       </c>
       <c r="P201" s="141">
-        <f t="shared" si="262"/>
+        <f t="shared" si="263"/>
         <v>218.17940460081186</v>
       </c>
       <c r="Q201" s="141">
-        <f t="shared" ref="Q201" si="263">100*(1+((Q115-$M115)/ABS($M115)))</f>
+        <f t="shared" ref="Q201" si="264">100*(1+((Q115-$M115)/ABS($M115)))</f>
         <v>1842.37347767253</v>
       </c>
       <c r="T201" s="49"/>
@@ -33402,19 +33402,19 @@
         <v>100</v>
       </c>
       <c r="N203" s="141">
-        <f t="shared" ref="N203:P203" si="264">100*(1+((N25-$M25)/ABS($M25)))</f>
+        <f t="shared" ref="N203:P203" si="265">100*(1+((N25-$M25)/ABS($M25)))</f>
         <v>-61.263157894736842</v>
       </c>
       <c r="O203" s="141">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>-52.84210526315789</v>
       </c>
       <c r="P203" s="141">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v>118.32315789473684</v>
       </c>
       <c r="Q203" s="141">
-        <f t="shared" ref="Q203" si="265">100*(1+((Q25-$M25)/ABS($M25)))</f>
+        <f t="shared" ref="Q203" si="266">100*(1+((Q25-$M25)/ABS($M25)))</f>
         <v>645.59242105263149</v>
       </c>
       <c r="T203" s="49"/>
@@ -33557,7 +33557,7 @@
         <v>209</v>
       </c>
       <c r="AC208" s="62">
-        <f t="shared" ref="AC208:AC209" si="266">SUM(X208:AA208)</f>
+        <f t="shared" ref="AC208:AC209" si="267">SUM(X208:AA208)</f>
         <v>783</v>
       </c>
     </row>
@@ -33617,7 +33617,7 @@
         <v>22</v>
       </c>
       <c r="AC209" s="62">
-        <f t="shared" si="266"/>
+        <f t="shared" si="267"/>
         <v>89</v>
       </c>
     </row>
@@ -33682,39 +33682,39 @@
         <v>14.674329501915709</v>
       </c>
       <c r="T211" s="63">
-        <f t="shared" ref="T211:AA211" si="267">T185/T208</f>
+        <f t="shared" ref="T211:AA211" si="268">T185/T208</f>
         <v>13.539007092198581</v>
       </c>
       <c r="U211" s="63">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>13.61038961038961</v>
       </c>
       <c r="V211" s="63">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>13.841379310344827</v>
       </c>
       <c r="W211" s="63">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>13.7</v>
       </c>
       <c r="X211" s="63">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>13.71584699453552</v>
       </c>
       <c r="Y211" s="63">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>13.921875</v>
       </c>
       <c r="Z211" s="63">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>14.93467336683417</v>
       </c>
       <c r="AA211" s="63">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v>15.956937799043063</v>
       </c>
       <c r="AC211" s="63">
-        <f t="shared" ref="AC211" si="268">AC185/AC208</f>
+        <f t="shared" ref="AC211" si="269">AC185/AC208</f>
         <v>14.674329501915709</v>
       </c>
     </row>
@@ -33815,7 +33815,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33831,7 +33831,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>180938.52000000002</v>
+        <v>176214.36</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33851,7 +33851,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>180411.52000000002</v>
+        <v>175687.36</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33871,7 +33871,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.731102850061959</v>
+        <v>18.242048740190004</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33891,7 +33891,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.452760275563126</v>
+        <v>13.101519467451041</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>18.468668772563177</v>
+        <v>17.986466606498194</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33931,7 +33931,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.964820806563978</v>
+        <v>13.59914544469386</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>40.51460139231979</v>
+        <v>39.453707612845271</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.3387139454882243E-2</v>
+        <v>5.4818404130060686E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34192,7 +34192,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.7628168949320464E-2</v>
+        <v>2.8368857112439645E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.1025844579694805E-3</v>
+        <v>1.1321438275518523E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34224,7 +34224,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.3836825900864004E-2</v>
+        <v>2.4475871319454331E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.5411946555106119E-2</v>
+        <v>2.6093219644528404E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34277,7 +34277,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>2.9125915255634894E-3</v>
+        <v>2.9906756747860959E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>453.48</v>
+        <v>441.64</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34485,7 +34485,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>180938.52000000002</v>
+        <v>176214.36</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>180411.52000000002</v>
+        <v>175687.36</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34543,7 +34543,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.731102850061959</v>
+        <v>18.242048740190004</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34572,7 +34572,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.452760275563126</v>
+        <v>13.101519467451041</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>18.468668772563177</v>
+        <v>17.986466606498194</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34630,7 +34630,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.964820806563978</v>
+        <v>13.59914544469386</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34659,7 +34659,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>40.51460139231979</v>
+        <v>39.453707612845271</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35432,7 +35432,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.3387139454882243E-2</v>
+        <v>5.4818404130060686E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.7628168949320464E-2</v>
+        <v>2.8368857112439645E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.1025844579694805E-3</v>
+        <v>1.1321438275518523E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.3836825900864004E-2</v>
+        <v>2.4475871319454331E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35548,7 +35548,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.5411946555106119E-2</v>
+        <v>2.6093219644528404E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.9125915255634894E-3</v>
+        <v>2.9906756747860959E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36273,14 +36273,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="244" t="s">
+      <c r="C3" s="246" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="F3" s="246" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="245"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36347,19 +36347,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="244">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="245"/>
+      <c r="F7" s="244">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="245"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36386,19 +36386,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="244">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="245"/>
+      <c r="F9" s="244">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="245"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36425,19 +36425,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="244">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="245"/>
+      <c r="F11" s="244">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="245"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36464,19 +36464,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="244">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="245"/>
+      <c r="F13" s="244">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="245"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36503,19 +36503,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="244">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="245"/>
+      <c r="F15" s="244">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36542,19 +36542,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="244">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="245"/>
+      <c r="F17" s="244">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="245"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36581,22 +36581,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="244">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="245"/>
+      <c r="F19" s="244">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="245"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36623,22 +36623,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="244">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="245"/>
+      <c r="F21" s="244">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="245"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36687,22 +36687,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="244">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="245"/>
+      <c r="F25" s="244">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="245"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36730,22 +36730,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="244">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="245"/>
+      <c r="F27" s="244">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="245"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -36773,49 +36773,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="244">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="245"/>
+      <c r="F29" s="244">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="245"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCE9D56-5A71-7A42-93B2-3104DD3C0542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86130E5-FE51-144F-A63B-8BE8EBD4FB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2412,12 +2412,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2425,6 +2419,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2445,14 +2445,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12825,11 +12825,11 @@
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
     <v>112.5201</v>
-    <v>2.2473000000000001</v>
-    <v>26.35</v>
-    <v>6.3449999999999993E-2</v>
-    <v>-0.37</v>
-    <v>-8.3779999999999998E-4</v>
+    <v>2.2273000000000001</v>
+    <v>3.97</v>
+    <v>1.0094000000000001E-2</v>
+    <v>-1.38</v>
+    <v>-3.4739999999999997E-3</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12837,26 +12837,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>447.71</v>
+    <v>398.28</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46300.895150786717</v>
+    <v>46304.999991284378</v>
     <v>4</v>
-    <v>429.44</v>
-    <v>159229327240</v>
+    <v>386.01</v>
+    <v>148411095040</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>430.5</v>
-    <v>18.1919</v>
-    <v>415.29</v>
-    <v>441.64</v>
-    <v>441.27</v>
-    <v>360541000</v>
+    <v>397.35</v>
+    <v>16.2011</v>
+    <v>393.31</v>
+    <v>397.28</v>
+    <v>395.9</v>
+    <v>373568000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>11271953</v>
-    <v>7212332</v>
+    <v>7046643</v>
+    <v>8102798</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12878,19 +12878,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>7</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13132,9 +13132,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>176214.36</v>
+        <v>158514.72</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>175687.36</v>
+        <v>157987.72</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13818,14 +13818,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>441.27</v>
+        <v>395.9</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>18.242048740190004</v>
+        <v>16.409748038000824</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13842,14 +13842,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>26.35</v>
+        <v>3.97</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>13.101519467451041</v>
+        <v>11.78555306138246</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13866,14 +13866,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.37</v>
+        <v>-1.38</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.8368857112439645E-2</v>
+        <v>3.1536503360697354E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13890,14 +13890,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.3449999999999993E-2</v>
+        <v>1.0094000000000001E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>5.4818404130060686E-2</v>
+        <v>6.09393878372936E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.69181509391923102</v>
+        <v>-0.65740338823622935</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13914,14 +13914,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-8.3779999999999998E-4</v>
+        <v>-3.4739999999999997E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.4475871319454331E-2</v>
+        <v>2.7208829564850507E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.1321438275518523E-3</v>
+        <v>1.2585581957309706E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2473000000000001</v>
+        <v>2.2273000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="I13" s="209">
         <f>'Reverse DCF'!C17</f>
-        <v>0.35499999999999998</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>7212332</v>
+        <v>8102798</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>2.9906756747860959E-3</v>
+        <v>3.3246123766928395E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18655,12 +18655,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18668,6 +18662,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19727,16 +19727,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>176214.36</v>
+        <v>158514.72</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.2473000000000001</v>
+        <v>2.2273000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.9345721320164758E-3</v>
+        <v>6.5928534471348414E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99406542786798358</v>
+        <v>0.99340714655286511</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15389849999999999</v>
+        <v>0.15266849999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15314926917019112</v>
+        <v>0.15184427135131937</v>
       </c>
     </row>
   </sheetData>
@@ -21792,17 +21792,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.69181509391923102</v>
+        <v>-0.65740338823622935</v>
       </c>
     </row>
   </sheetData>
@@ -22591,23 +22591,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>4790.9499025744572</v>
+        <v>4667.1984290762248</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>6491.7371179883894</v>
+        <v>6160.7019263806169</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>8796.3037948742676</v>
+        <v>8132.1265428224151</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>11918.991642054632</v>
+        <v>10734.407036525588</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>16150.233674984027</v>
+        <v>14169.417288213777</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22639,7 +22639,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>205915.47935604636</v>
+        <v>180660.07042472565</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22693,23 +22693,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f>H7/(1+$C$21)^H9</f>
-        <v>4355.4090023404151</v>
+        <v>4242.9076627965678</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>5365.0719983375111</v>
+        <v>5091.4891953558808</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" si="1"/>
-        <v>6608.7932343157509</v>
+        <v>6109.7870344270568</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" si="1"/>
-        <v>8140.8316659071297</v>
+        <v>7331.7444413124686</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>10028.0244611856</v>
+        <v>8798.0933295749619</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22728,15 +22728,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f>L8/(1+C21)^L9</f>
-        <v>127857.31188011641</v>
+        <v>112175.68995208076</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="256" t="s">
+      <c r="B14" s="255" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="257"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="C16" s="154">
         <f>C36</f>
-        <v>451.19790094793024</v>
+        <v>399.65848092949506</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22761,22 +22761,22 @@
         <v>323</v>
       </c>
       <c r="C17" s="156">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="E17" s="255" t="s">
+        <v>0.32</v>
+      </c>
+      <c r="E17" s="257" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="255"/>
-      <c r="G17" s="255"/>
-      <c r="H17" s="255"/>
-      <c r="I17" s="255"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="256" t="s">
+      <c r="B19" s="255" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="257"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>159432.04</v>
+        <v>143418.07999999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22837,15 +22837,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>158905.04</v>
+        <v>142891.07999999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="256" t="s">
+      <c r="B28" s="255" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="257"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22853,7 +22853,7 @@
       </c>
       <c r="C29" s="159">
         <f>SUM(H10:L10)</f>
-        <v>34498.130362086406</v>
+        <v>31574.021663466934</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22862,7 +22862,7 @@
       </c>
       <c r="C30" s="159">
         <f>L11</f>
-        <v>127857.31188011641</v>
+        <v>112175.68995208076</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22871,7 +22871,7 @@
       </c>
       <c r="C31" s="162">
         <f>C29+C30</f>
-        <v>162355.44224220281</v>
+        <v>143749.71161554771</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="C34" s="162">
         <f>C31+C32-C33</f>
-        <v>162882.44224220281</v>
+        <v>144276.71161554771</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22916,21 +22916,21 @@
       </c>
       <c r="C36" s="165">
         <f>C34/C35</f>
-        <v>451.19790094793024</v>
+        <v>399.65848092949506</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29660,7 +29660,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31103,7 +31103,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>18.242048740190004</v>
+        <v>16.409748038000824</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31144,7 +31144,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>13.101519467451041</v>
+        <v>11.78555306138246</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>17.986466606498194</v>
+        <v>16.179837545126354</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31274,7 +31274,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>176214.36</v>
+        <v>158514.72</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31339,7 +31339,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>175687.36</v>
+        <v>157987.72</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31380,7 +31380,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>13.59914544469386</v>
+        <v>12.229098227416983</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31421,7 +31421,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>39.453707612845271</v>
+        <v>35.478940040422188</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31568,7 +31568,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>35.249921984396877</v>
+        <v>31.709285857171434</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31609,7 +31609,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>55.044100730595503</v>
+        <v>49.498677502337785</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31650,7 +31650,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>2.8368857112439645E-2</v>
+        <v>3.1536503360697354E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31691,7 +31691,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>5.4818404130060686E-2</v>
+        <v>6.09393878372936E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31732,7 +31732,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.1321438275518523E-3</v>
+        <v>1.2585581957309706E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31773,7 +31773,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.4475871319454331E-2</v>
+        <v>2.7208829564850507E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31814,7 +31814,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.6093219644528404E-2</v>
+        <v>2.9006769844466179E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32361,7 +32361,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.9906756747860959E-3</v>
+        <v>3.3246123766928395E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33831,7 +33831,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>176214.36</v>
+        <v>158514.72</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33851,7 +33851,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>175687.36</v>
+        <v>157987.72</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33871,7 +33871,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.242048740190004</v>
+        <v>16.409748038000824</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33891,7 +33891,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.101519467451041</v>
+        <v>11.78555306138246</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33911,7 +33911,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>17.986466606498194</v>
+        <v>16.179837545126354</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33931,7 +33931,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.59914544469386</v>
+        <v>12.229098227416983</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>39.453707612845271</v>
+        <v>35.478940040422188</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.4818404130060686E-2</v>
+        <v>6.09393878372936E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34192,7 +34192,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.8368857112439645E-2</v>
+        <v>3.1536503360697354E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.1321438275518523E-3</v>
+        <v>1.2585581957309706E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34224,7 +34224,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.4475871319454331E-2</v>
+        <v>2.7208829564850507E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.6093219644528404E-2</v>
+        <v>2.9006769844466179E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34277,7 +34277,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>2.9906756747860959E-3</v>
+        <v>3.3246123766928395E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>441.64</v>
+        <v>397.28</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34485,7 +34485,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>176214.36</v>
+        <v>158514.72</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>175687.36</v>
+        <v>157987.72</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34543,7 +34543,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>18.242048740190004</v>
+        <v>16.409748038000824</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34572,7 +34572,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>13.101519467451041</v>
+        <v>11.78555306138246</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>17.986466606498194</v>
+        <v>16.179837545126354</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34630,7 +34630,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>13.59914544469386</v>
+        <v>12.229098227416983</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34659,7 +34659,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>39.453707612845271</v>
+        <v>35.478940040422188</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35432,7 +35432,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>5.4818404130060686E-2</v>
+        <v>6.09393878372936E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35461,7 +35461,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.8368857112439645E-2</v>
+        <v>3.1536503360697354E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.1321438275518523E-3</v>
+        <v>1.2585581957309706E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.4475871319454331E-2</v>
+        <v>2.7208829564850507E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35548,7 +35548,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.6093219644528404E-2</v>
+        <v>2.9006769844466179E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.9906756747860959E-3</v>
+        <v>3.3246123766928395E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36273,14 +36273,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="244" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="247"/>
-      <c r="F3" s="248" t="s">
+      <c r="D3" s="245"/>
+      <c r="F3" s="246" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="247"/>
+      <c r="G3" s="245"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36347,19 +36347,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="244">
+      <c r="C7" s="247">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="245"/>
-      <c r="F7" s="244">
+      <c r="D7" s="248"/>
+      <c r="F7" s="247">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="245"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36386,19 +36386,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="244">
+      <c r="C9" s="247">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="F9" s="244">
+      <c r="D9" s="248"/>
+      <c r="F9" s="247">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="245"/>
+      <c r="G9" s="248"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36425,19 +36425,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="244">
+      <c r="C11" s="247">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="F11" s="244">
+      <c r="D11" s="248"/>
+      <c r="F11" s="247">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="245"/>
+      <c r="G11" s="248"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36464,19 +36464,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="244">
+      <c r="C13" s="247">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="F13" s="244">
+      <c r="D13" s="248"/>
+      <c r="F13" s="247">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="245"/>
+      <c r="G13" s="248"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36503,19 +36503,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="244">
+      <c r="C15" s="247">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="245"/>
-      <c r="F15" s="244">
+      <c r="D15" s="248"/>
+      <c r="F15" s="247">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="248"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36542,19 +36542,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="244">
+      <c r="C17" s="247">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="F17" s="244">
+      <c r="D17" s="248"/>
+      <c r="F17" s="247">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="245"/>
+      <c r="G17" s="248"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36581,22 +36581,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="244">
+      <c r="C19" s="247">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="245"/>
-      <c r="F19" s="244">
+      <c r="D19" s="248"/>
+      <c r="F19" s="247">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="245"/>
+      <c r="G19" s="248"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36623,22 +36623,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="244">
+      <c r="C21" s="247">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="F21" s="244">
+      <c r="D21" s="248"/>
+      <c r="F21" s="247">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="245"/>
+      <c r="G21" s="248"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36687,22 +36687,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="244">
+      <c r="C25" s="247">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="F25" s="244">
+      <c r="D25" s="248"/>
+      <c r="F25" s="247">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="245"/>
+      <c r="G25" s="248"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36730,22 +36730,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="244">
+      <c r="C27" s="247">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="F27" s="244">
+      <c r="D27" s="248"/>
+      <c r="F27" s="247">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="245"/>
+      <c r="G27" s="248"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -36773,49 +36773,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="244">
+      <c r="C29" s="247">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="245"/>
-      <c r="F29" s="244">
+      <c r="D29" s="248"/>
+      <c r="F29" s="247">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="245"/>
+      <c r="G29" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86130E5-FE51-144F-A63B-8BE8EBD4FB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6161CB7A-05E3-3B4C-8AFB-052C7A6D8E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="443">
   <si>
     <t>Ticker</t>
   </si>
@@ -1475,6 +1475,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1516,7 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1658,6 +1682,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2075,11 +2107,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="258">
+  <cellXfs count="262">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2400,6 +2433,14 @@
     <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2412,6 +2453,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2419,12 +2466,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2445,17 +2486,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12826,10 +12868,10 @@
     <v>799.87</v>
     <v>112.5201</v>
     <v>2.2273000000000001</v>
-    <v>3.97</v>
-    <v>1.0094000000000001E-2</v>
-    <v>-1.38</v>
-    <v>-3.4739999999999997E-3</v>
+    <v>-10.34</v>
+    <v>-2.6027000000000002E-2</v>
+    <v>0.26</v>
+    <v>6.7190000000000001E-4</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12837,26 +12879,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>398.28</v>
+    <v>392.59500000000003</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46304.999991284378</v>
+    <v>46307.865252441406</v>
     <v>4</v>
-    <v>386.01</v>
-    <v>148411095040</v>
+    <v>385.89</v>
+    <v>144548401920</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>397.35</v>
-    <v>16.2011</v>
-    <v>393.31</v>
+    <v>391.76</v>
+    <v>15.938700000000001</v>
     <v>397.28</v>
-    <v>395.9</v>
+    <v>386.94</v>
+    <v>387.2</v>
     <v>373568000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>7046643</v>
-    <v>8102798</v>
+    <v>5354872</v>
+    <v>8163872</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -13132,9 +13174,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13710,7 +13752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I76"/>
+  <dimension ref="B1:K76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13722,25 +13764,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="240" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="244" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="241"/>
-      <c r="E2" s="240" t="s">
+      <c r="C2" s="245"/>
+      <c r="E2" s="244" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="241"/>
-      <c r="H2" s="240" t="s">
+      <c r="F2" s="245"/>
+      <c r="H2" s="244" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="241"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="245"/>
+      <c r="K2" s="132" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="181" t="s">
         <v>11</v>
       </c>
@@ -13753,7 +13800,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>158514.72</v>
+        <v>154389.06</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13763,8 +13810,11 @@
         <f>'AVG target price'!C5</f>
         <v>100.93902416944954</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K3" s="242" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="181" t="s">
         <v>0</v>
       </c>
@@ -13777,7 +13827,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>157987.72</v>
+        <v>153862.06</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13787,14 +13837,17 @@
         <f>'AVG target price'!C6</f>
         <v>126.97405835620837</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K4" s="242" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="181" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13811,21 +13864,24 @@
         <f>'AVG target price'!C7</f>
         <v>122.57242020457076</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="242" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>395.9</v>
+        <v>387.2</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>16.409748038000824</v>
+        <v>15.982651796778191</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13835,21 +13891,24 @@
         <f>'AVG target price'!C8</f>
         <v>141.88381728503509</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K6" s="243" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="181" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>3.97</v>
+        <v>-10.34</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>11.78555306138246</v>
+        <v>11.478810666460253</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13860,20 +13919,20 @@
         <v>188.16458959229004</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.38</v>
+        <v>0.26</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>3.1536503360697354E-2</v>
+        <v>3.2379237233519008E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13884,20 +13943,20 @@
         <v>136.10678192151076</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="181" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.0094000000000001E-2</v>
+        <v>-2.6027000000000002E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>6.09393878372936E-2</v>
+        <v>6.2567839975189957E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13905,26 +13964,26 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.65740338823622935</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-0.64824835395278146</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-3.4739999999999997E-3</v>
+        <v>6.7190000000000001E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.7208829564850507E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>2.7935917221077713E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="181" t="s">
         <v>7</v>
       </c>
@@ -13937,7 +13996,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.2585581957309706E-3</v>
+        <v>1.292190003618132E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
@@ -13947,7 +14006,7 @@
         <v>11.111111111111111</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="181" t="s">
         <v>8</v>
       </c>
@@ -13963,7 +14022,7 @@
         <v>0.67989322559699872</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="181" t="s">
         <v>9</v>
       </c>
@@ -13986,13 +14045,13 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="182" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8102798</v>
+        <v>8163872</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -14002,16 +14061,16 @@
         <v>0.50818716392752861</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="181" t="s">
         <v>289</v>
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>3.3246123766928395E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>3.4134542952719577E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="182" t="s">
         <v>294</v>
       </c>
@@ -14019,12 +14078,16 @@
         <f>Statement!AC173</f>
         <v>1.4598337950138505</v>
       </c>
+      <c r="H16" s="244" t="s">
+        <v>435</v>
+      </c>
+      <c r="I16" s="245"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="242" t="s">
+      <c r="B17" s="246" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="242"/>
+      <c r="C17" s="246"/>
       <c r="E17" s="180" t="s">
         <v>295</v>
       </c>
@@ -14032,6 +14095,13 @@
         <f>Statement!AC169</f>
         <v>2.5062656641604009E-3</v>
       </c>
+      <c r="H17" s="181" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="240">
+        <f>DCF!C15</f>
+        <v>0.1</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="180" t="s">
@@ -14047,7 +14117,13 @@
         <f>Statement!AC142</f>
         <v>42.713410112871273</v>
       </c>
-      <c r="I18" s="50"/>
+      <c r="H18" s="182" t="s">
+        <v>436</v>
+      </c>
+      <c r="I18" s="241">
+        <f>Multiples!C54</f>
+        <v>0.11</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="180" t="s">
@@ -14097,14 +14173,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="242" t="s">
+      <c r="B25" s="246" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="242"/>
-      <c r="E25" s="240" t="s">
+      <c r="C25" s="246"/>
+      <c r="E25" s="244" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="241"/>
+      <c r="F25" s="245"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="180" t="s">
@@ -14381,13 +14457,14 @@
       <c r="H76" s="132"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14400,6 +14477,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{97C5DCB1-C0CF-FF4C-8285-F7DB5D75D42E}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{63821515-D738-4040-AB04-396F28815092}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{8247D464-1495-3C4F-A5CC-EE072FBF19E6}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{D81AE3AF-07A7-A648-AC3B-0BCD30FBC706}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14409,18 +14492,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="242" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="242" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="242" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="242" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="243" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{362694D2-AFDA-9F4A-926F-AA5A7AFDDDFF}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{C8CCBCB2-2015-AB45-8787-7673AC13CBCE}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{F92DCF8F-0248-A94A-810F-67B4645D60A3}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{838F657B-8B64-114B-A41C-28E594BE17B4}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{8FF6F303-2BC9-674B-A1B7-583445F4F518}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14457,36 +14579,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="247"/>
+      <c r="U2" s="247"/>
+      <c r="V2" s="247"/>
+      <c r="W2" s="247"/>
+      <c r="X2" s="247"/>
+      <c r="Y2" s="247"/>
+      <c r="Z2" s="247"/>
+      <c r="AA2" s="247" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="247"/>
+      <c r="AC2" s="247"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14497,32 +14619,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="249" t="s">
+      <c r="C4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="250" t="s">
+      <c r="S4" s="254" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="251"/>
-      <c r="U4" s="251"/>
-      <c r="V4" s="251"/>
-      <c r="W4" s="251"/>
-      <c r="X4" s="251"/>
-      <c r="Y4" s="251"/>
-      <c r="Z4" s="251"/>
-      <c r="AA4" s="251"/>
-      <c r="AB4" s="251"/>
-      <c r="AC4" s="251"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
+      <c r="AA4" s="255"/>
+      <c r="AB4" s="255"/>
+      <c r="AC4" s="255"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15012,33 +15134,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="249" t="s">
+      <c r="C11" s="253" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="253"/>
+      <c r="I11" s="253"/>
+      <c r="J11" s="253"/>
+      <c r="K11" s="253"/>
+      <c r="L11" s="253"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="250" t="s">
+      <c r="S11" s="254" t="s">
         <v>121</v>
       </c>
-      <c r="T11" s="251"/>
-      <c r="U11" s="251"/>
-      <c r="V11" s="251"/>
-      <c r="W11" s="251"/>
-      <c r="X11" s="251"/>
-      <c r="Y11" s="251"/>
-      <c r="Z11" s="251"/>
-      <c r="AA11" s="251"/>
-      <c r="AB11" s="251"/>
-      <c r="AC11" s="251"/>
+      <c r="T11" s="255"/>
+      <c r="U11" s="255"/>
+      <c r="V11" s="255"/>
+      <c r="W11" s="255"/>
+      <c r="X11" s="255"/>
+      <c r="Y11" s="255"/>
+      <c r="Z11" s="255"/>
+      <c r="AA11" s="255"/>
+      <c r="AB11" s="255"/>
+      <c r="AC11" s="255"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15469,32 +15591,32 @@
     <row r="19" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="86"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="249" t="s">
+      <c r="C19" s="253" t="s">
         <v>414</v>
       </c>
-      <c r="D19" s="249"/>
-      <c r="E19" s="249"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="249"/>
-      <c r="H19" s="249"/>
-      <c r="I19" s="249"/>
-      <c r="J19" s="249"/>
-      <c r="K19" s="249"/>
-      <c r="L19" s="249"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
+      <c r="F19" s="253"/>
+      <c r="G19" s="253"/>
+      <c r="H19" s="253"/>
+      <c r="I19" s="253"/>
+      <c r="J19" s="253"/>
+      <c r="K19" s="253"/>
+      <c r="L19" s="253"/>
       <c r="O19" s="5"/>
-      <c r="S19" s="250" t="s">
+      <c r="S19" s="254" t="s">
         <v>115</v>
       </c>
-      <c r="T19" s="251"/>
-      <c r="U19" s="251"/>
-      <c r="V19" s="251"/>
-      <c r="W19" s="251"/>
-      <c r="X19" s="251"/>
-      <c r="Y19" s="251"/>
-      <c r="Z19" s="251"/>
-      <c r="AA19" s="251"/>
-      <c r="AB19" s="251"/>
-      <c r="AC19" s="251"/>
+      <c r="T19" s="255"/>
+      <c r="U19" s="255"/>
+      <c r="V19" s="255"/>
+      <c r="W19" s="255"/>
+      <c r="X19" s="255"/>
+      <c r="Y19" s="255"/>
+      <c r="Z19" s="255"/>
+      <c r="AA19" s="255"/>
+      <c r="AB19" s="255"/>
+      <c r="AC19" s="255"/>
       <c r="AE19" s="87"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
@@ -15989,35 +16111,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="P2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="247"/>
+      <c r="R2" s="247"/>
+      <c r="S2" s="247"/>
+      <c r="T2" s="247"/>
+      <c r="U2" s="247"/>
+      <c r="V2" s="247"/>
+      <c r="W2" s="247"/>
+      <c r="X2" s="247" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="247"/>
+      <c r="Z2" s="247"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16026,31 +16148,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="249" t="s">
+      <c r="C4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
-      <c r="P4" s="251" t="s">
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
+      <c r="P4" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="251"/>
-      <c r="R4" s="251"/>
-      <c r="S4" s="251"/>
-      <c r="T4" s="251"/>
-      <c r="U4" s="251"/>
-      <c r="V4" s="251"/>
-      <c r="W4" s="251"/>
-      <c r="X4" s="251"/>
-      <c r="Y4" s="251"/>
-      <c r="Z4" s="251"/>
+      <c r="Q4" s="255"/>
+      <c r="R4" s="255"/>
+      <c r="S4" s="255"/>
+      <c r="T4" s="255"/>
+      <c r="U4" s="255"/>
+      <c r="V4" s="255"/>
+      <c r="W4" s="255"/>
+      <c r="X4" s="255"/>
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="255"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -16245,32 +16367,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="249" t="s">
+      <c r="C9" s="253" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="251" t="s">
+      <c r="P9" s="255" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="251"/>
-      <c r="R9" s="251"/>
-      <c r="S9" s="251"/>
-      <c r="T9" s="251"/>
-      <c r="U9" s="251"/>
-      <c r="V9" s="251"/>
-      <c r="W9" s="251"/>
-      <c r="X9" s="251"/>
-      <c r="Y9" s="251"/>
-      <c r="Z9" s="251"/>
+      <c r="Q9" s="255"/>
+      <c r="R9" s="255"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="255"/>
+      <c r="U9" s="255"/>
+      <c r="V9" s="255"/>
+      <c r="W9" s="255"/>
+      <c r="X9" s="255"/>
+      <c r="Y9" s="255"/>
+      <c r="Z9" s="255"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16747,31 +16869,31 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="249" t="s">
+      <c r="C17" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
-      <c r="J17" s="249"/>
-      <c r="K17" s="249"/>
-      <c r="L17" s="249"/>
-      <c r="P17" s="251" t="s">
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="253"/>
+      <c r="I17" s="253"/>
+      <c r="J17" s="253"/>
+      <c r="K17" s="253"/>
+      <c r="L17" s="253"/>
+      <c r="P17" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="251"/>
-      <c r="R17" s="251"/>
-      <c r="S17" s="251"/>
-      <c r="T17" s="251"/>
-      <c r="U17" s="251"/>
-      <c r="V17" s="251"/>
-      <c r="W17" s="251"/>
-      <c r="X17" s="251"/>
-      <c r="Y17" s="251"/>
-      <c r="Z17" s="251"/>
+      <c r="Q17" s="255"/>
+      <c r="R17" s="255"/>
+      <c r="S17" s="255"/>
+      <c r="T17" s="255"/>
+      <c r="U17" s="255"/>
+      <c r="V17" s="255"/>
+      <c r="W17" s="255"/>
+      <c r="X17" s="255"/>
+      <c r="Y17" s="255"/>
+      <c r="Z17" s="255"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
@@ -17249,60 +17371,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="252"/>
-      <c r="H3" s="253" t="s">
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
-      <c r="S3" s="254"/>
-      <c r="T3" s="254"/>
-      <c r="U3" s="254"/>
-      <c r="V3" s="254"/>
-      <c r="W3" s="254"/>
-      <c r="X3" s="254"/>
-      <c r="Y3" s="254"/>
-      <c r="Z3" s="254"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="249" t="s">
+      <c r="C5" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
-      <c r="I5" s="249"/>
-      <c r="J5" s="249"/>
-      <c r="K5" s="249"/>
-      <c r="L5" s="249"/>
-      <c r="P5" s="254"/>
-      <c r="Q5" s="254"/>
-      <c r="R5" s="254"/>
-      <c r="S5" s="254"/>
-      <c r="T5" s="254"/>
-      <c r="U5" s="254"/>
-      <c r="V5" s="254"/>
-      <c r="W5" s="254"/>
-      <c r="X5" s="254"/>
-      <c r="Y5" s="254"/>
-      <c r="Z5" s="254"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17488,30 +17610,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="249" t="s">
+      <c r="C11" s="253" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="253"/>
+      <c r="I11" s="253"/>
+      <c r="J11" s="253"/>
+      <c r="K11" s="253"/>
+      <c r="L11" s="253"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="254"/>
-      <c r="Q11" s="254"/>
-      <c r="R11" s="254"/>
-      <c r="S11" s="254"/>
-      <c r="T11" s="254"/>
-      <c r="U11" s="254"/>
-      <c r="V11" s="254"/>
-      <c r="W11" s="254"/>
-      <c r="X11" s="254"/>
-      <c r="Y11" s="254"/>
-      <c r="Z11" s="254"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="258"/>
+      <c r="S11" s="258"/>
+      <c r="T11" s="258"/>
+      <c r="U11" s="258"/>
+      <c r="V11" s="258"/>
+      <c r="W11" s="258"/>
+      <c r="X11" s="258"/>
+      <c r="Y11" s="258"/>
+      <c r="Z11" s="258"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17753,18 +17875,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="249" t="s">
+      <c r="C18" s="253" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="249"/>
-      <c r="E18" s="249"/>
-      <c r="F18" s="249"/>
-      <c r="G18" s="249"/>
-      <c r="H18" s="249"/>
-      <c r="I18" s="249"/>
-      <c r="J18" s="249"/>
-      <c r="K18" s="249"/>
-      <c r="L18" s="249"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
+      <c r="F18" s="253"/>
+      <c r="G18" s="253"/>
+      <c r="H18" s="253"/>
+      <c r="I18" s="253"/>
+      <c r="J18" s="253"/>
+      <c r="K18" s="253"/>
+      <c r="L18" s="253"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17977,23 +18099,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="254"/>
-      <c r="C25" s="254"/>
+      <c r="B25" s="258"/>
+      <c r="C25" s="258"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="249" t="s">
+      <c r="C26" s="253" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="249"/>
-      <c r="E26" s="249"/>
-      <c r="F26" s="249"/>
-      <c r="G26" s="249"/>
-      <c r="H26" s="249"/>
-      <c r="I26" s="249"/>
-      <c r="J26" s="249"/>
-      <c r="K26" s="249"/>
-      <c r="L26" s="249"/>
+      <c r="D26" s="253"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="253"/>
+      <c r="G26" s="253"/>
+      <c r="H26" s="253"/>
+      <c r="I26" s="253"/>
+      <c r="J26" s="253"/>
+      <c r="K26" s="253"/>
+      <c r="L26" s="253"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18185,18 +18307,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="249" t="s">
+      <c r="C33" s="253" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="249"/>
-      <c r="I33" s="249"/>
-      <c r="J33" s="249"/>
-      <c r="K33" s="249"/>
-      <c r="L33" s="249"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="253"/>
+      <c r="I33" s="253"/>
+      <c r="J33" s="253"/>
+      <c r="K33" s="253"/>
+      <c r="L33" s="253"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18380,18 +18502,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="249" t="s">
+      <c r="C40" s="253" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="249"/>
-      <c r="E40" s="249"/>
-      <c r="F40" s="249"/>
-      <c r="G40" s="249"/>
-      <c r="H40" s="249"/>
-      <c r="I40" s="249"/>
-      <c r="J40" s="249"/>
-      <c r="K40" s="249"/>
-      <c r="L40" s="249"/>
+      <c r="D40" s="253"/>
+      <c r="E40" s="253"/>
+      <c r="F40" s="253"/>
+      <c r="G40" s="253"/>
+      <c r="H40" s="253"/>
+      <c r="I40" s="253"/>
+      <c r="J40" s="253"/>
+      <c r="K40" s="253"/>
+      <c r="L40" s="253"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18655,6 +18777,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18662,12 +18790,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18705,60 +18827,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254"/>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
+      <c r="S2" s="258"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="258"/>
+      <c r="W2" s="258"/>
+      <c r="X2" s="258"/>
+      <c r="Y2" s="258"/>
+      <c r="Z2" s="258"/>
+      <c r="AA2" s="258"/>
+      <c r="AB2" s="258"/>
+      <c r="AC2" s="258"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="249" t="s">
+      <c r="C4" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
-      <c r="S4" s="254"/>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
-      <c r="AA4" s="254"/>
-      <c r="AB4" s="254"/>
-      <c r="AC4" s="254"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
+      <c r="S4" s="258"/>
+      <c r="T4" s="258"/>
+      <c r="U4" s="258"/>
+      <c r="V4" s="258"/>
+      <c r="W4" s="258"/>
+      <c r="X4" s="258"/>
+      <c r="Y4" s="258"/>
+      <c r="Z4" s="258"/>
+      <c r="AA4" s="258"/>
+      <c r="AB4" s="258"/>
+      <c r="AC4" s="258"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19121,18 +19243,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="249" t="s">
+      <c r="C13" s="253" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="249"/>
-      <c r="H13" s="249"/>
-      <c r="I13" s="249"/>
-      <c r="J13" s="249"/>
-      <c r="K13" s="249"/>
-      <c r="L13" s="249"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="253"/>
+      <c r="I13" s="253"/>
+      <c r="J13" s="253"/>
+      <c r="K13" s="253"/>
+      <c r="L13" s="253"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19225,18 +19347,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="249" t="s">
+      <c r="C18" s="253" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="249"/>
-      <c r="E18" s="249"/>
-      <c r="F18" s="249"/>
-      <c r="G18" s="249"/>
-      <c r="H18" s="249"/>
-      <c r="I18" s="249"/>
-      <c r="J18" s="249"/>
-      <c r="K18" s="249"/>
-      <c r="L18" s="249"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
+      <c r="F18" s="253"/>
+      <c r="G18" s="253"/>
+      <c r="H18" s="253"/>
+      <c r="I18" s="253"/>
+      <c r="J18" s="253"/>
+      <c r="K18" s="253"/>
+      <c r="L18" s="253"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19428,18 +19550,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="249" t="s">
+      <c r="C25" s="253" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="249"/>
-      <c r="I25" s="249"/>
-      <c r="J25" s="249"/>
-      <c r="K25" s="249"/>
-      <c r="L25" s="249"/>
+      <c r="D25" s="253"/>
+      <c r="E25" s="253"/>
+      <c r="F25" s="253"/>
+      <c r="G25" s="253"/>
+      <c r="H25" s="253"/>
+      <c r="I25" s="253"/>
+      <c r="J25" s="253"/>
+      <c r="K25" s="253"/>
+      <c r="L25" s="253"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19577,18 +19699,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="249" t="s">
+      <c r="C31" s="253" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="249"/>
-      <c r="E31" s="249"/>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="249"/>
-      <c r="I31" s="249"/>
-      <c r="J31" s="249"/>
-      <c r="K31" s="249"/>
-      <c r="L31" s="249"/>
+      <c r="D31" s="253"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
+      <c r="I31" s="253"/>
+      <c r="J31" s="253"/>
+      <c r="K31" s="253"/>
+      <c r="L31" s="253"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19727,16 +19849,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19750,18 +19872,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="242" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="242" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="242" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="242" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="243" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>163</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{DB312C7A-0D5C-B045-855D-0DFAAE55DE7B}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{1675E99D-55F9-8344-835E-4202655857A3}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{4AB041E1-211D-F148-B10E-421B68D20C76}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{8AF14AB8-3EF3-DD47-B946-928A30DD7A37}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{628E7204-2493-5B4B-8D7B-2A7FC45DB5AD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19799,10 +19960,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="247" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="247"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19819,7 +19980,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19828,7 +19989,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>158514.72</v>
+        <v>154389.06</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19887,10 +20048,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="247" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="247"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19898,7 +20059,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.5928534471348414E-3</v>
+        <v>6.7678385620890645E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19907,7 +20068,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99340714655286511</v>
+        <v>0.99323216143791093</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19934,7 +20095,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15184427135131937</v>
+        <v>0.15182239497472547</v>
       </c>
     </row>
   </sheetData>
@@ -19979,60 +20140,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="252"/>
-      <c r="H3" s="253" t="s">
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
-      <c r="S3" s="254"/>
-      <c r="T3" s="254"/>
-      <c r="U3" s="254"/>
-      <c r="V3" s="254"/>
-      <c r="W3" s="254"/>
-      <c r="X3" s="254"/>
-      <c r="Y3" s="254"/>
-      <c r="Z3" s="254"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="249" t="s">
+      <c r="C5" s="253" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
-      <c r="I5" s="249"/>
-      <c r="J5" s="249"/>
-      <c r="K5" s="249"/>
-      <c r="L5" s="249"/>
-      <c r="P5" s="254"/>
-      <c r="Q5" s="254"/>
-      <c r="R5" s="254"/>
-      <c r="S5" s="254"/>
-      <c r="T5" s="254"/>
-      <c r="U5" s="254"/>
-      <c r="V5" s="254"/>
-      <c r="W5" s="254"/>
-      <c r="X5" s="254"/>
-      <c r="Y5" s="254"/>
-      <c r="Z5" s="254"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20278,10 +20439,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="247" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="247"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20301,10 +20462,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="247" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="247"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20418,37 +20579,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="249" t="s">
+      <c r="C4" s="253" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20668,18 +20829,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="249" t="s">
+      <c r="C11" s="253" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="253"/>
+      <c r="I11" s="253"/>
+      <c r="J11" s="253"/>
+      <c r="K11" s="253"/>
+      <c r="L11" s="253"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20867,18 +21028,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="249" t="s">
+      <c r="C17" s="253" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
-      <c r="J17" s="249"/>
-      <c r="K17" s="249"/>
-      <c r="L17" s="249"/>
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="253"/>
+      <c r="I17" s="253"/>
+      <c r="J17" s="253"/>
+      <c r="K17" s="253"/>
+      <c r="L17" s="253"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -21012,18 +21173,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="249" t="s">
+      <c r="C22" s="253" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="249"/>
-      <c r="E22" s="249"/>
-      <c r="F22" s="249"/>
-      <c r="G22" s="249"/>
-      <c r="H22" s="249"/>
-      <c r="I22" s="249"/>
-      <c r="J22" s="249"/>
-      <c r="K22" s="249"/>
-      <c r="L22" s="249"/>
+      <c r="D22" s="253"/>
+      <c r="E22" s="253"/>
+      <c r="F22" s="253"/>
+      <c r="G22" s="253"/>
+      <c r="H22" s="253"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="253"/>
+      <c r="K22" s="253"/>
+      <c r="L22" s="253"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21107,18 +21268,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="249" t="s">
+      <c r="C27" s="253" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="249"/>
-      <c r="E27" s="249"/>
-      <c r="F27" s="249"/>
-      <c r="G27" s="249"/>
-      <c r="H27" s="249"/>
-      <c r="I27" s="249"/>
-      <c r="J27" s="249"/>
-      <c r="K27" s="249"/>
-      <c r="L27" s="249"/>
+      <c r="D27" s="253"/>
+      <c r="E27" s="253"/>
+      <c r="F27" s="253"/>
+      <c r="G27" s="253"/>
+      <c r="H27" s="253"/>
+      <c r="I27" s="253"/>
+      <c r="J27" s="253"/>
+      <c r="K27" s="253"/>
+      <c r="L27" s="253"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21419,10 +21580,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="243" t="s">
+      <c r="B39" s="247" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="243"/>
+      <c r="C39" s="247"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21524,10 +21685,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="243" t="s">
+      <c r="B52" s="247" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="243"/>
+      <c r="C52" s="247"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21583,10 +21744,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="243" t="s">
+      <c r="B60" s="247" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="243"/>
+      <c r="C60" s="247"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21687,10 +21848,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="243" t="s">
+      <c r="B73" s="247" t="s">
         <v>430</v>
       </c>
-      <c r="C73" s="243"/>
+      <c r="C73" s="247"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21792,17 +21953,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21840,10 +22001,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="247" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="247"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21906,7 +22067,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21915,7 +22076,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.65740338823622935</v>
+        <v>-0.64824835395278146</v>
       </c>
     </row>
   </sheetData>
@@ -21931,18 +22092,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="242" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="242" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="242" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="242" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="243" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{511BC83D-D66E-5D4E-BA12-F2E14E111040}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{B3A21CE9-0E9E-CF46-B24D-3D195DF243C6}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{5422C205-1F62-6847-BA27-D0939E27CCF7}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{A736BBCD-B90B-E14E-80AC-DB9FDC60692A}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{406439E8-8BF7-3D43-BB78-45BB8CDF05C1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21971,37 +22171,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253" t="s">
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="247"/>
+      <c r="J2" s="247"/>
+      <c r="K2" s="247"/>
+      <c r="L2" s="247"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="249" t="s">
+      <c r="C4" s="253" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="253"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22114,18 +22314,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="249" t="s">
+      <c r="C9" s="253" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22246,18 +22446,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="249" t="s">
+      <c r="C14" s="253" t="s">
         <v>365</v>
       </c>
-      <c r="D14" s="249"/>
-      <c r="E14" s="249"/>
-      <c r="F14" s="249"/>
-      <c r="G14" s="249"/>
-      <c r="H14" s="249"/>
-      <c r="I14" s="249"/>
-      <c r="J14" s="249"/>
-      <c r="K14" s="249"/>
-      <c r="L14" s="249"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="253"/>
+      <c r="F14" s="253"/>
+      <c r="G14" s="253"/>
+      <c r="H14" s="253"/>
+      <c r="I14" s="253"/>
+      <c r="J14" s="253"/>
+      <c r="K14" s="253"/>
+      <c r="L14" s="253"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22347,10 +22547,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="247" t="s">
         <v>367</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="247"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22451,60 +22651,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="252"/>
-      <c r="H3" s="253" t="s">
+      <c r="D3" s="247"/>
+      <c r="E3" s="247"/>
+      <c r="F3" s="247"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
-      <c r="S3" s="254"/>
-      <c r="T3" s="254"/>
-      <c r="U3" s="254"/>
-      <c r="V3" s="254"/>
-      <c r="W3" s="254"/>
-      <c r="X3" s="254"/>
-      <c r="Y3" s="254"/>
-      <c r="Z3" s="254"/>
+      <c r="I3" s="247"/>
+      <c r="J3" s="247"/>
+      <c r="K3" s="247"/>
+      <c r="L3" s="247"/>
+      <c r="P3" s="258"/>
+      <c r="Q3" s="258"/>
+      <c r="R3" s="258"/>
+      <c r="S3" s="258"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="258"/>
+      <c r="W3" s="258"/>
+      <c r="X3" s="258"/>
+      <c r="Y3" s="258"/>
+      <c r="Z3" s="258"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="249" t="s">
+      <c r="C5" s="253" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
-      <c r="I5" s="249"/>
-      <c r="J5" s="249"/>
-      <c r="K5" s="249"/>
-      <c r="L5" s="249"/>
-      <c r="P5" s="254"/>
-      <c r="Q5" s="254"/>
-      <c r="R5" s="254"/>
-      <c r="S5" s="254"/>
-      <c r="T5" s="254"/>
-      <c r="U5" s="254"/>
-      <c r="V5" s="254"/>
-      <c r="W5" s="254"/>
-      <c r="X5" s="254"/>
-      <c r="Y5" s="254"/>
-      <c r="Z5" s="254"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="258"/>
+      <c r="R5" s="258"/>
+      <c r="S5" s="258"/>
+      <c r="T5" s="258"/>
+      <c r="U5" s="258"/>
+      <c r="V5" s="258"/>
+      <c r="W5" s="258"/>
+      <c r="X5" s="258"/>
+      <c r="Y5" s="258"/>
+      <c r="Z5" s="258"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22733,10 +22933,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="261"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22744,7 +22944,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22763,20 +22963,20 @@
       <c r="C17" s="156">
         <v>0.32</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="259" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="260" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="261"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -22810,7 +23010,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>143418.07999999999</v>
+        <v>139685.34</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22837,15 +23037,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>142891.07999999999</v>
+        <v>139158.34</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="260" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="261"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -22921,16 +23121,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29660,7 +29860,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29734,7 +29934,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31103,7 +31303,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>16.409748038000824</v>
+        <v>15.982651796778191</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31144,7 +31344,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>11.78555306138246</v>
+        <v>11.478810666460253</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31209,7 +31409,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>16.179837545126354</v>
+        <v>15.758725180505415</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31274,7 +31474,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>158514.72</v>
+        <v>154389.06</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31339,7 +31539,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>157987.72</v>
+        <v>153862.06</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31380,7 +31580,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>12.229098227416983</v>
+        <v>11.909749980648657</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31421,7 +31621,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>35.478940040422188</v>
+        <v>34.552450033685155</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31568,7 +31768,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>31.709285857171434</v>
+        <v>30.883988797759553</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31609,7 +31809,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>49.498677502337785</v>
+        <v>48.206078850845785</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31650,7 +31850,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>3.1536503360697354E-2</v>
+        <v>3.2379237233519008E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31691,7 +31891,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>6.09393878372936E-2</v>
+        <v>6.2567839975189957E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31732,7 +31932,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.2585581957309706E-3</v>
+        <v>1.292190003618132E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31773,7 +31973,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.7208829564850507E-2</v>
+        <v>2.7935917221077713E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31814,7 +32014,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.9006769844466179E-2</v>
+        <v>2.9781902940532186E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32361,7 +32561,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>3.3246123766928395E-3</v>
+        <v>3.4134542952719577E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33764,18 +33964,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="132" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="242" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="242" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="242" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="242" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="243" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>231</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{C5D045C0-3DD6-B247-9C3A-A6CA2C8D018B}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{B7375BC8-9874-2844-A331-F5A79BAE8D30}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{B80B889B-2231-D145-A045-CE32A59A6A5C}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{28A00C51-1261-6E45-AE17-05875871B452}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{94CD6498-EF25-0F48-85A2-AB9ACD91683E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -33799,15 +34038,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="247" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="247"/>
+      <c r="E4" s="247" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33815,7 +34054,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33831,7 +34070,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>158514.72</v>
+        <v>154389.06</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33851,7 +34090,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>157987.72</v>
+        <v>153862.06</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33871,7 +34110,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>16.409748038000824</v>
+        <v>15.982651796778191</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -33891,7 +34130,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.78555306138246</v>
+        <v>11.478810666460253</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -33911,7 +34150,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>16.179837545126354</v>
+        <v>15.758725180505415</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33931,7 +34170,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.229098227416983</v>
+        <v>11.909749980648657</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33940,18 +34179,18 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>35.478940040422188</v>
+        <v>34.552450033685155</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="247" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="247"/>
+      <c r="E15" s="247" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34002,14 +34241,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="247" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="247"/>
+      <c r="E21" s="247" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="247"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34078,14 +34317,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="247" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="247"/>
+      <c r="E29" s="247" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="247"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34161,14 +34400,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="247" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="247"/>
+      <c r="E37" s="247" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="247"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34176,7 +34415,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>6.09393878372936E-2</v>
+        <v>6.2567839975189957E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34192,7 +34431,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>3.1536503360697354E-2</v>
+        <v>3.2379237233519008E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34208,7 +34447,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.2585581957309706E-3</v>
+        <v>1.292190003618132E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34224,7 +34463,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.7208829564850507E-2</v>
+        <v>2.7935917221077713E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34233,18 +34472,18 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.9006769844466179E-2</v>
+        <v>2.9781902940532186E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="247" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="247"/>
+      <c r="E45" s="247" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="247"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34277,18 +34516,18 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>3.3246123766928395E-3</v>
+        <v>3.4134542952719577E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="247" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="247"/>
+      <c r="E51" s="247" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="247"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34456,7 +34695,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>397.28</v>
+        <v>386.94</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34485,7 +34724,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>158514.72</v>
+        <v>154389.06</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34514,7 +34753,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>157987.72</v>
+        <v>153862.06</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34543,7 +34782,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>16.409748038000824</v>
+        <v>15.982651796778191</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34572,7 +34811,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.78555306138246</v>
+        <v>11.478810666460253</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34601,7 +34840,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>16.179837545126354</v>
+        <v>15.758725180505415</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34630,7 +34869,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>12.229098227416983</v>
+        <v>11.909749980648657</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34659,7 +34898,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>35.478940040422188</v>
+        <v>34.552450033685155</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35432,7 +35671,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>6.09393878372936E-2</v>
+        <v>6.2567839975189957E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35461,7 +35700,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>3.1536503360697354E-2</v>
+        <v>3.2379237233519008E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35490,7 +35729,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.2585581957309706E-3</v>
+        <v>1.292190003618132E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35519,7 +35758,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.7208829564850507E-2</v>
+        <v>2.7935917221077713E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35548,7 +35787,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.9006769844466179E-2</v>
+        <v>2.9781902940532186E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35784,7 +36023,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>3.3246123766928395E-3</v>
+        <v>3.4134542952719577E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36273,14 +36512,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="244" t="s">
+      <c r="C3" s="250" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="245"/>
-      <c r="F3" s="246" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="245"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36347,19 +36586,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="247">
+      <c r="C7" s="248">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="F7" s="247">
+      <c r="D7" s="249"/>
+      <c r="F7" s="248">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="248"/>
+      <c r="G7" s="249"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36386,19 +36625,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="247">
+      <c r="C9" s="248">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="F9" s="247">
+      <c r="D9" s="249"/>
+      <c r="F9" s="248">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="248"/>
+      <c r="G9" s="249"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36425,19 +36664,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="247">
+      <c r="C11" s="248">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="F11" s="247">
+      <c r="D11" s="249"/>
+      <c r="F11" s="248">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="248"/>
+      <c r="G11" s="249"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36464,19 +36703,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="247">
+      <c r="C13" s="248">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="F13" s="247">
+      <c r="D13" s="249"/>
+      <c r="F13" s="248">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="248"/>
+      <c r="G13" s="249"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36503,19 +36742,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="247">
+      <c r="C15" s="248">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="F15" s="247">
+      <c r="D15" s="249"/>
+      <c r="F15" s="248">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="248"/>
+      <c r="G15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36542,19 +36781,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="247">
+      <c r="C17" s="248">
         <f>Statement!AA96</f>
         <v>-3.1201248049921998E-3</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="F17" s="247">
+      <c r="D17" s="249"/>
+      <c r="F17" s="248">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>11.678571428571429</v>
       </c>
-      <c r="G17" s="248"/>
+      <c r="G17" s="249"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36581,22 +36820,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="247">
+      <c r="C19" s="248">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="F19" s="247">
+      <c r="D19" s="249"/>
+      <c r="F19" s="248">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="248"/>
+      <c r="G19" s="249"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36623,22 +36862,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="247">
+      <c r="C21" s="248">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>1.219512195122142E-3</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="F21" s="247">
+      <c r="D21" s="249"/>
+      <c r="F21" s="248">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>11.253731343283583</v>
       </c>
-      <c r="G21" s="248"/>
+      <c r="G21" s="249"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36687,22 +36926,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="247">
+      <c r="C25" s="248">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="F25" s="247">
+      <c r="D25" s="249"/>
+      <c r="F25" s="248">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="248"/>
+      <c r="G25" s="249"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36730,22 +36969,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="247">
+      <c r="C27" s="248">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="F27" s="247">
+      <c r="D27" s="249"/>
+      <c r="F27" s="248">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="248"/>
+      <c r="G27" s="249"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -36773,49 +37012,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="247">
+      <c r="C29" s="248">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="248"/>
-      <c r="F29" s="247">
+      <c r="D29" s="249"/>
+      <c r="F29" s="248">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="248"/>
+      <c r="G29" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6161CB7A-05E3-3B4C-8AFB-052C7A6D8E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCE2823-07E8-504D-9F62-A1E06C8108B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -12866,12 +12866,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>112.5201</v>
-    <v>2.2273000000000001</v>
-    <v>-10.34</v>
-    <v>-2.6027000000000002E-2</v>
-    <v>0.26</v>
-    <v>6.7190000000000001E-4</v>
+    <v>117.23</v>
+    <v>2.2690999999999999</v>
+    <v>20.21</v>
+    <v>6.0872999999999997E-2</v>
+    <v>-0.61</v>
+    <v>-1.732E-3</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12879,26 +12879,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>392.59500000000003</v>
+    <v>356.25</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46307.865252441406</v>
+    <v>46314.919424733591</v>
     <v>4</v>
-    <v>385.89</v>
-    <v>144548401920</v>
+    <v>341.14</v>
+    <v>131574385279</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>391.76</v>
-    <v>15.938700000000001</v>
-    <v>397.28</v>
-    <v>386.94</v>
-    <v>387.2</v>
+    <v>341.96</v>
+    <v>13.675599999999999</v>
+    <v>332</v>
+    <v>352.21</v>
+    <v>351.6</v>
     <v>373568000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>5354872</v>
-    <v>8163872</v>
+    <v>7797630</v>
+    <v>8923335</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12922,17 +12922,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>0.09</v>
+    <v>1.769E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>51.33</v>
     <v>Index</v>
     <v>7</v>
-    <v>52.34</v>
+    <v>50.67</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.14</v>
+    <v>50.89</v>
+    <v>50.98</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13752,6 +13752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:K76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -13800,7 +13801,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>154389.06</v>
+        <v>140531.78999999998</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13827,7 +13828,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>153862.06</v>
+        <v>140004.78999999998</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13847,7 +13848,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13874,14 +13875,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>387.2</v>
+        <v>351.6</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>15.982651796778191</v>
+        <v>14.548120611317636</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13901,14 +13902,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-10.34</v>
+        <v>20.21</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>11.478810666460253</v>
+        <v>10.44852407307067</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13925,14 +13926,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.26</v>
+        <v>-0.61</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>3.2379237233519008E-2</v>
+        <v>3.5572022529564311E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13949,14 +13950,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.6027000000000002E-2</v>
+        <v>6.0872999999999997E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>6.2567839975189957E-2</v>
+        <v>6.8737400982368482E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13964,7 +13965,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.64824835395278146</v>
+        <v>-0.61356355037758503</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13973,14 +13974,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>6.7190000000000001E-4</v>
+        <v>-1.732E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.7935917221077713E-2</v>
+        <v>3.0690564746951567E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13996,7 +13997,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.292190003618132E-3</v>
+        <v>1.4196076204537067E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>362</v>
@@ -14012,7 +14013,7 @@
       </c>
       <c r="C12" s="205" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>112.5201</v>
+        <v>117.23</v>
       </c>
       <c r="E12" s="181" t="s">
         <v>101</v>
@@ -14028,7 +14029,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2273000000000001</v>
+        <v>2.2690999999999999</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -14051,7 +14052,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8163872</v>
+        <v>8923335</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -14067,7 +14068,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>3.4134542952719577E-3</v>
+        <v>3.7500411828526492E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14194,7 +14195,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14209,7 +14210,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.0979999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14489,7 +14490,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B54B610-4F16-C34E-B8D9-992F7812B5AD}">
-  <sheetPr>
+  <sheetPr codeName="Sheet10">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -14549,6 +14550,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66282D1-ADA2-D843-8696-3FC058E17FA6}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:AE25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16085,6 +16087,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABDC400-6556-6848-BEEB-E2541EF30223}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -17340,6 +17343,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECA4AF9-34CA-DC41-86C9-B346AEC194A1}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:AB46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -18798,6 +18802,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297D0CC1-03C8-8940-8079-159588699646}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:AE34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19869,7 +19874,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C2FB80D-D3C0-DD46-8304-4441946EF9E3}">
-  <sheetPr>
+  <sheetPr codeName="Sheet15">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -19929,6 +19934,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9236FE7C-2B1B-7C49-B055-001352253955}">
+  <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19980,7 +19986,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19989,7 +19995,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>154389.06</v>
+        <v>140531.78999999998</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20007,7 +20013,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.0979999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20016,7 +20022,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.2273000000000001</v>
+        <v>2.2690999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20059,7 +20065,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.7678385620890645E-3</v>
+        <v>7.4302291243934079E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20068,7 +20074,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99323216143791093</v>
+        <v>0.99256977087560661</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20086,7 +20092,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15266849999999998</v>
+        <v>0.15308949999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20095,7 +20101,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15182239497472547</v>
+        <v>0.15215745577375064</v>
       </c>
     </row>
   </sheetData>
@@ -20109,6 +20115,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE76C87-6799-634E-8DEB-EF0E693AF74F}">
+  <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -20557,6 +20564,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -21974,6 +21982,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -22067,7 +22076,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22076,7 +22085,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.64824835395278146</v>
+        <v>-0.61356355037758503</v>
       </c>
     </row>
   </sheetData>
@@ -22089,7 +22098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03335612-A5F6-ED42-8E7B-33A97D1D2D90}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -22149,6 +22158,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B6E4A1-F7CC-5043-8E79-210959816CC1}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -22620,6 +22630,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0116CE1A-CCEC-514B-9208-A0DCC7740441}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -22944,7 +22955,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23010,7 +23021,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>139685.34</v>
+        <v>127147.81</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23037,7 +23048,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>139158.34</v>
+        <v>126620.81</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23140,6 +23151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0548B83C-60BF-4548-84AB-1D4A73B251A4}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AE213"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -29860,7 +29872,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29934,7 +29946,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31303,7 +31315,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>15.982651796778191</v>
+        <v>14.548120611317636</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31344,7 +31356,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>11.478810666460253</v>
+        <v>10.44852407307067</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31409,7 +31421,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>15.758725180505415</v>
+        <v>14.344292644404332</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31474,7 +31486,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>154389.06</v>
+        <v>140531.78999999998</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31539,7 +31551,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>153862.06</v>
+        <v>140004.78999999998</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31580,7 +31592,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>11.909749980648657</v>
+        <v>10.837122842325256</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31621,7 +31633,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>34.552450033685155</v>
+        <v>31.440554682236691</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31768,7 +31780,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>30.883988797759553</v>
+        <v>28.111980396079211</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31809,7 +31821,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>48.206078850845785</v>
+        <v>43.864497500138143</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31850,7 +31862,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>3.2379237233519008E-2</v>
+        <v>3.5572022529564311E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31891,7 +31903,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>6.2567839975189957E-2</v>
+        <v>6.8737400982368482E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31932,7 +31944,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.292190003618132E-3</v>
+        <v>1.4196076204537067E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31973,7 +31985,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.7935917221077713E-2</v>
+        <v>3.0690564746951567E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32014,7 +32026,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.9781902940532186E-2</v>
+        <v>3.2718575633314005E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32561,7 +32573,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>3.4134542952719577E-3</v>
+        <v>3.7500411828526492E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33961,7 +33973,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{757210FB-34E3-D04A-8896-321D81878D88}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B5:H13"/>
@@ -34021,6 +34033,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="B1:G54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -34054,7 +34067,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34070,7 +34083,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>154389.06</v>
+        <v>140531.78999999998</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34090,7 +34103,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>153862.06</v>
+        <v>140004.78999999998</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -34110,7 +34123,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>15.982651796778191</v>
+        <v>14.548120611317636</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -34130,7 +34143,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.478810666460253</v>
+        <v>10.44852407307067</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -34150,7 +34163,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>15.758725180505415</v>
+        <v>14.344292644404332</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34170,7 +34183,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>11.909749980648657</v>
+        <v>10.837122842325256</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34179,7 +34192,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>34.552450033685155</v>
+        <v>31.440554682236691</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34415,7 +34428,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>6.2567839975189957E-2</v>
+        <v>6.8737400982368482E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34431,7 +34444,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>3.2379237233519008E-2</v>
+        <v>3.5572022529564311E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34447,7 +34460,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.292190003618132E-3</v>
+        <v>1.4196076204537067E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34463,7 +34476,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.7935917221077713E-2</v>
+        <v>3.0690564746951567E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34472,7 +34485,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.9781902940532186E-2</v>
+        <v>3.2718575633314005E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34516,7 +34529,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>3.4134542952719577E-3</v>
+        <v>3.7500411828526492E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34596,6 +34609,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="B1:I94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -34695,7 +34709,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>386.94</v>
+        <v>352.21</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34724,7 +34738,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>154389.06</v>
+        <v>140531.78999999998</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34753,7 +34767,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>153862.06</v>
+        <v>140004.78999999998</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34782,7 +34796,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>15.982651796778191</v>
+        <v>14.548120611317636</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34811,7 +34825,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>11.478810666460253</v>
+        <v>10.44852407307067</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34840,7 +34854,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>15.758725180505415</v>
+        <v>14.344292644404332</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34869,7 +34883,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>11.909749980648657</v>
+        <v>10.837122842325256</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34898,7 +34912,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>34.552450033685155</v>
+        <v>31.440554682236691</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35671,7 +35685,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>6.2567839975189957E-2</v>
+        <v>6.8737400982368482E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35700,7 +35714,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>3.2379237233519008E-2</v>
+        <v>3.5572022529564311E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35729,7 +35743,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.292190003618132E-3</v>
+        <v>1.4196076204537067E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35758,7 +35772,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.7935917221077713E-2</v>
+        <v>3.0690564746951567E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35787,7 +35801,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.9781902940532186E-2</v>
+        <v>3.2718575633314005E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36023,7 +36037,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>3.4134542952719577E-3</v>
+        <v>3.7500411828526492E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36496,6 +36510,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A593F86-70CC-F54A-91FC-45975067BFCE}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="B1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -37065,6 +37080,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59D4CD5-3D15-DF4B-A135-ED758F2E1A8D}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="B55:L73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -37935,6 +37951,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0C9119-3B3B-094C-BA34-9489CF595CBC}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="B55:J66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCE2823-07E8-504D-9F62-A1E06C8108B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587EAAFF-9FB0-6A45-879B-DC975DF0E066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -158,19 +179,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="443">
   <si>
     <t>Ticker</t>
   </si>
@@ -1237,9 +1267,6 @@
     <t>M</t>
   </si>
   <si>
-    <t>29.11.2024</t>
-  </si>
-  <si>
     <t>Q1 2025</t>
   </si>
   <si>
@@ -1252,9 +1279,6 @@
     <t>Actual EPS</t>
   </si>
   <si>
-    <t>FY 2024</t>
-  </si>
-  <si>
     <t>Manual Cost of Equity</t>
   </si>
   <si>
@@ -1499,6 +1523,12 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>FY 2026</t>
+  </si>
+  <si>
+    <t>Removed 5591 form Net Income to take out the one time gain from selling Sandisk and adjusted EPS and also the Quarterly values</t>
   </si>
 </sst>
 </file>
@@ -2453,12 +2483,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2466,6 +2490,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2486,14 +2516,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2840,7 +2870,7 @@
                   <c:v>1643</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9424</c:v>
+                  <c:v>3833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3160,10 +3190,10 @@
                   <c:v>546</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1146</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2071</c:v>
+                  <c:v>925</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1236</c:v>
@@ -3485,7 +3515,7 @@
                   <c:v>1342</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3535.7563856638062</c:v>
+                  <c:v>3255.5018544274453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3919,7 +3949,7 @@
                   <c:v>0.17258403361344538</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.72946822509482157</c:v>
+                  <c:v>0.29669479061846893</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4684,7 +4714,7 @@
                   <c:v>0.11734037994572204</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.67989322559699872</c:v>
+                  <c:v>0.276531274799798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4759,7 +4789,7 @@
                   <c:v>0.30935793635850123</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0631768953068592</c:v>
+                  <c:v>0.432423285198556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4834,7 +4864,7 @@
                   <c:v>0.29514415781487102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.50818716392752861</c:v>
+                  <c:v>0.47457141111040485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5196,7 +5226,7 @@
                   <c:v>118.32315789473684</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>645.59242105263149</c:v>
+                  <c:v>262.58019417388977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5638,16 +5668,16 @@
                   <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1182</c:v>
+                  <c:v>571</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1842</c:v>
+                  <c:v>739</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3205</c:v>
+                  <c:v>1016</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3195</c:v>
+                  <c:v>1507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6089,16 +6119,16 @@
                   <c:v>9.6737044145873322E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.41944641589779985</c:v>
+                  <c:v>0.20262597586941092</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.61054027179317205</c:v>
+                  <c:v>0.24494530991050711</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.96044351213664969</c:v>
+                  <c:v>0.30446508840275699</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8526821457165733</c:v>
+                  <c:v>0.40218841740058714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12828,7 +12858,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12867,11 +12897,9 @@
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
     <v>117.23</v>
-    <v>2.2690999999999999</v>
-    <v>20.21</v>
-    <v>6.0872999999999997E-2</v>
-    <v>-0.61</v>
-    <v>-1.732E-3</v>
+    <v>2.2572000000000001</v>
+    <v>9.2200000000000006</v>
+    <v>2.6178E-2</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12879,36 +12907,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>356.25</v>
+    <v>361.78500000000003</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46314.919424733591</v>
+    <v>46315.693459166403</v>
     <v>4</v>
-    <v>341.14</v>
-    <v>131574385279</v>
+    <v>342.59</v>
+    <v>135018682240</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>341.96</v>
-    <v>13.675599999999999</v>
-    <v>332</v>
+    <v>349.5</v>
+    <v>14.8879</v>
     <v>352.21</v>
-    <v>351.6</v>
+    <v>361.43</v>
     <v>373568000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>7797630</v>
-    <v>8923335</v>
+    <v>3912645</v>
+    <v>8943779</v>
     <v>2000</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12922,28 +12964,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.09</v>
-    <v>1.769E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>51.33</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>7</v>
-    <v>50.67</v>
+    <v>10</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.14</v>
-    <v>50.89</v>
+    <v>50.9</v>
     <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12977,8 +13019,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13000,7 +13040,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13010,6 +13049,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13045,7 +13089,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13056,16 +13100,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13166,19 +13207,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13259,9 +13294,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13269,9 +13301,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13785,7 +13814,7 @@
       </c>
       <c r="I2" s="245"/>
       <c r="K2" s="132" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
@@ -13801,7 +13830,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>140531.78999999998</v>
+        <v>144210.57</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13812,7 +13841,7 @@
         <v>100.93902416944954</v>
       </c>
       <c r="K3" s="242" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
@@ -13828,7 +13857,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>140004.78999999998</v>
+        <v>143683.57</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13839,7 +13868,7 @@
         <v>126.97405835620837</v>
       </c>
       <c r="K4" s="242" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
@@ -13848,14 +13877,14 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="185">
+      <c r="F5" s="186">
         <f>Statement!AC25</f>
-        <v>24.21</v>
+        <v>9.9576085543415989</v>
       </c>
       <c r="H5" s="181" t="str">
         <f>'AVG target price'!B7</f>
@@ -13866,23 +13895,23 @@
         <v>122.57242020457076</v>
       </c>
       <c r="K5" s="242" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="204" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>351.6</v>
+      <c r="C6" s="204" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>14.548120611317636</v>
+        <v>36.296867669337487</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13893,7 +13922,7 @@
         <v>141.88381728503509</v>
       </c>
       <c r="K6" s="243" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
@@ -13902,14 +13931,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>20.21</v>
+        <v>9.2200000000000006</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>10.44852407307067</v>
+        <v>10.722040986144439</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13924,16 +13953,16 @@
       <c r="B8" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.61</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>3.5572022529564311E-2</v>
+        <v>2.2931744878340054E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13950,14 +13979,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.0872999999999997E-2</v>
+        <v>2.6178E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>6.8737400982368482E-2</v>
+        <v>2.7550586709298063E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13965,23 +13994,23 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.61356355037758503</v>
+        <v>-0.62342145942088167</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.732E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>3.0690564746951567E-2</v>
+        <v>1.7973717183144063E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13997,10 +14026,10 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.4196076204537067E-3</v>
+        <v>1.3833937415267132E-3</v>
       </c>
       <c r="H11" s="180" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I11" s="208">
         <f>DDM!C26</f>
@@ -14020,7 +14049,7 @@
       </c>
       <c r="F12" s="188">
         <f>Statement!AC121</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
@@ -14029,17 +14058,17 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2690999999999999</v>
+        <v>2.2572000000000001</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
       </c>
       <c r="F13" s="188">
         <f>Statement!AC123</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
       <c r="H13" s="180" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I13" s="209">
         <f>'Reverse DCF'!C17</f>
@@ -14052,7 +14081,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8923335</v>
+        <v>8943779</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -14068,7 +14097,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>3.7500411828526492E-3</v>
+        <v>3.6543784550605407E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14080,7 +14109,7 @@
         <v>1.4598337950138505</v>
       </c>
       <c r="H16" s="244" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I16" s="245"/>
     </row>
@@ -14119,7 +14148,7 @@
         <v>42.713410112871273</v>
       </c>
       <c r="H18" s="182" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I18" s="241">
         <f>Multiples!C54</f>
@@ -14190,12 +14219,12 @@
       <c r="C26" s="166">
         <v>0.21</v>
       </c>
-      <c r="E26" s="181" t="e" vm="2">
+      <c r="E26" s="181" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>50.98</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14210,7 +14239,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>5.0979999999999998E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14223,7 +14252,7 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="180" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C29" s="217">
         <v>0.11</v>
@@ -14245,7 +14274,7 @@
         <v>333</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -14253,52 +14282,52 @@
         <v>334</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="16" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="16"/>
       <c r="C38" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="16"/>
       <c r="C39" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="16"/>
       <c r="C41" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="16"/>
       <c r="C42" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="16" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C43" s="90">
         <v>4500</v>
@@ -14329,35 +14358,35 @@
         <v>336</v>
       </c>
       <c r="C51" s="41" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D51" s="41"/>
       <c r="E51" s="41" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
@@ -14365,35 +14394,35 @@
         <v>336</v>
       </c>
       <c r="C56" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D56" s="41"/>
       <c r="E56" s="41" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
@@ -14401,19 +14430,19 @@
         <v>336</v>
       </c>
       <c r="C61" s="41" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D61" s="41"/>
       <c r="E61" s="41" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
@@ -14441,11 +14470,19 @@
         <v>336</v>
       </c>
       <c r="C71" s="41" t="s">
-        <v>355</v>
+        <v>417</v>
       </c>
       <c r="D71" s="41"/>
       <c r="E71" s="41" t="s">
-        <v>360</v>
+        <v>441</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B72" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
@@ -14503,32 +14540,32 @@
   <sheetData>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H5" s="132" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H6" s="242" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H7" s="242" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H8" s="242" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H9" s="242" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H10" s="243" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
@@ -14789,11 +14826,11 @@
         <v>14385.825339544892</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="O6" s="5"/>
       <c r="Q6" s="90" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="R6" s="1" t="str">
         <f>B6</f>
@@ -14888,11 +14925,11 @@
         <v>1122.9593760000002</v>
       </c>
       <c r="N7" s="90" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="O7" s="5"/>
       <c r="Q7" s="90" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="R7" s="1" t="str">
         <f t="shared" ref="R7:R8" si="3">B7</f>
@@ -14987,11 +15024,11 @@
         <v>874.81404359999988</v>
       </c>
       <c r="N8" s="90" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="O8" s="5"/>
       <c r="Q8" s="90" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R8" s="1" t="str">
         <f t="shared" si="3"/>
@@ -15594,7 +15631,7 @@
       <c r="A19" s="86"/>
       <c r="B19" s="60"/>
       <c r="C19" s="253" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D19" s="253"/>
       <c r="E19" s="253"/>
@@ -15760,11 +15797,11 @@
         <v>972.29573100000027</v>
       </c>
       <c r="N21" s="90" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O21" s="5"/>
       <c r="Q21" s="90" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="R21" s="1" t="str">
         <f>B21</f>
@@ -15859,11 +15896,11 @@
         <v>14.795730229885056</v>
       </c>
       <c r="N22" s="90" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="O22" s="5"/>
       <c r="Q22" s="90" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R22" s="1" t="str">
         <f t="shared" ref="R22" si="24">B22</f>
@@ -18781,12 +18818,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18794,6 +18825,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19325,7 +19362,7 @@
       </c>
       <c r="G15" s="130">
         <f>Statement!Q82</f>
-        <v>4.8561332660272592E-2</v>
+        <v>0.1114974501622624</v>
       </c>
       <c r="H15" s="129">
         <f>Overview!$C$26</f>
@@ -19635,7 +19672,7 @@
       </c>
       <c r="G27" s="131">
         <f t="shared" si="6"/>
-        <v>4236.7563856638062</v>
+        <v>3956.5018544274453</v>
       </c>
       <c r="H27" s="126">
         <f t="shared" si="6"/>
@@ -19680,7 +19717,7 @@
       </c>
       <c r="G28" s="127">
         <f t="shared" si="7"/>
-        <v>3535.7563856638062</v>
+        <v>3255.5018544274453</v>
       </c>
       <c r="H28" s="94">
         <f t="shared" si="7"/>
@@ -19854,16 +19891,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19887,32 +19924,32 @@
   <sheetData>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H5" s="132" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H6" s="242" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H7" s="242" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H8" s="242" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H9" s="242" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H10" s="243" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
@@ -19986,7 +20023,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19995,7 +20032,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>140531.78999999998</v>
+        <v>144210.57</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20013,7 +20050,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>5.0979999999999998E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20022,7 +20059,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.2690999999999999</v>
+        <v>2.2572000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20065,7 +20102,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.4302291243934079E-3</v>
+        <v>7.2420582948518669E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20074,7 +20111,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99256977087560661</v>
+        <v>0.99275794170514808</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20092,7 +20129,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15308949999999999</v>
+        <v>0.15293400000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20101,7 +20138,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15215745577375064</v>
+        <v>0.15202668596858779</v>
       </c>
     </row>
   </sheetData>
@@ -20283,7 +20320,7 @@
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3535.7563856638062</v>
+        <v>3255.5018544274453</v>
       </c>
       <c r="H7" s="112">
         <f>'FCF &amp; Other'!H28</f>
@@ -20778,7 +20815,7 @@
       </c>
       <c r="G8" s="93">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3535.7563856638062</v>
+        <v>3255.5018544274453</v>
       </c>
       <c r="H8" s="92">
         <f>'FCF &amp; Other'!H28</f>
@@ -21008,11 +21045,11 @@
       </c>
       <c r="G15" s="96">
         <f t="shared" si="3"/>
-        <v>1.6346917925959807</v>
+        <v>1.4258583117939234</v>
       </c>
       <c r="H15" s="95">
         <f t="shared" si="3"/>
-        <v>0.10395959867775496</v>
+        <v>0.19899553896160058</v>
       </c>
       <c r="I15" s="95">
         <f t="shared" si="3"/>
@@ -21541,7 +21578,7 @@
       </c>
       <c r="G35" s="148">
         <f>G33/G8</f>
-        <v>59.019787288499579</v>
+        <v>64.100590052507599</v>
       </c>
       <c r="H35" s="137"/>
       <c r="I35" s="137"/>
@@ -21552,7 +21589,7 @@
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B36" s="16" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C36" s="147">
         <f>C33/C6</f>
@@ -21622,7 +21659,7 @@
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C43" s="24">
         <f>(C40*C42)</f>
@@ -21631,7 +21668,7 @@
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C44" s="24">
         <f>C43/(1+C41)^5</f>
@@ -21640,7 +21677,7 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B45" s="16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C45" s="108">
         <f>SUM(H9:K9)+C44</f>
@@ -21759,7 +21796,7 @@
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C61" s="64">
         <f>L8</f>
@@ -21785,7 +21822,7 @@
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C64" s="24">
         <f>(C61*C63)</f>
@@ -21794,7 +21831,7 @@
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C65" s="24">
         <f>C64/(1+C62)^5</f>
@@ -21803,7 +21840,7 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" s="16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C66" s="108">
         <f>SUM(H9:K9)+C65</f>
@@ -21857,13 +21894,13 @@
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B73" s="247" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C73" s="247"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C74" s="64">
         <f>L6</f>
@@ -21881,7 +21918,7 @@
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B76" s="39" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C76" s="105">
         <v>6</v>
@@ -21889,7 +21926,7 @@
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C77" s="24">
         <f>(C74*C76)</f>
@@ -21898,7 +21935,7 @@
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C78" s="24">
         <f>C77/(1+C75)^5</f>
@@ -21907,7 +21944,7 @@
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79" s="16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C79" s="108">
         <f>SUM(H9:K9)+C78</f>
@@ -21961,17 +21998,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22054,7 +22091,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C9" s="133">
         <f>Multiples!C84</f>
@@ -22076,7 +22113,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22085,7 +22122,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.61356355037758503</v>
+        <v>-0.62342145942088167</v>
       </c>
     </row>
   </sheetData>
@@ -22111,32 +22148,32 @@
   <sheetData>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H5" s="132" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H6" s="242" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H7" s="242" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H8" s="242" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H9" s="242" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H10" s="243" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
@@ -22176,7 +22213,7 @@
     <row r="1" spans="1:14" s="83" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4"/>
       <c r="B1" s="82" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -22280,7 +22317,7 @@
       </c>
       <c r="G6" s="227">
         <f>Statement!Q25</f>
-        <v>24.28</v>
+        <v>9.8753438030560279</v>
       </c>
       <c r="H6" s="137"/>
       <c r="I6" s="137"/>
@@ -22291,7 +22328,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C7" s="226">
         <f>Statement!M81</f>
@@ -22403,7 +22440,7 @@
       </c>
       <c r="G11" s="96">
         <f>(G6-F6)/F6</f>
-        <v>4.4561797752808987</v>
+        <v>1.2191783827092197</v>
       </c>
       <c r="H11" s="137"/>
       <c r="I11" s="137"/>
@@ -22457,7 +22494,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="253" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D14" s="253"/>
       <c r="E14" s="253"/>
@@ -22518,7 +22555,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C16" s="95">
         <f>C7/C6</f>
@@ -22538,7 +22575,7 @@
       </c>
       <c r="G16" s="96">
         <f t="shared" si="2"/>
-        <v>2.059308072487644E-2</v>
+        <v>5.0631148643682643E-2</v>
       </c>
       <c r="H16" s="137"/>
       <c r="I16" s="137"/>
@@ -22558,14 +22595,14 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B20" s="247" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C20" s="247"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C21" s="228">
         <f>G7</f>
@@ -22574,7 +22611,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C22" s="229">
         <v>1</v>
@@ -22582,7 +22619,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23" s="39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C23" s="230">
         <f>C21*(1+C22)</f>
@@ -22600,7 +22637,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B25" s="39" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C25" s="229">
         <v>0.02</v>
@@ -22798,27 +22835,27 @@
       </c>
       <c r="G7" s="113">
         <f>'FCF &amp; Other'!G28</f>
-        <v>3535.7563856638062</v>
+        <v>3255.5018544274453</v>
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>4667.1984290762248</v>
+        <v>4297.2624478442276</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>6160.7019263806169</v>
+        <v>5672.3864311543803</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>8132.1265428224151</v>
+        <v>7487.5500891237825</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>10734.407036525588</v>
+        <v>9883.5661176433932</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>14169.417288213777</v>
+        <v>13046.30727528928</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22850,7 +22887,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>180660.07042472565</v>
+        <v>166340.41775993831</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22904,23 +22941,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f>H7/(1+$C$21)^H9</f>
-        <v>4242.9076627965678</v>
+        <v>3906.602225312934</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>5091.4891953558808</v>
+        <v>4687.9226703755203</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" si="1"/>
-        <v>6109.7870344270568</v>
+        <v>5625.5072044506242</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" si="1"/>
-        <v>7331.7444413124686</v>
+        <v>6750.6086453407488</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>8798.0933295749619</v>
+        <v>8100.7303744088986</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22939,15 +22976,15 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f>L8/(1+C21)^L9</f>
-        <v>112175.68995208076</v>
+        <v>103284.31227371345</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="260" t="s">
+      <c r="B14" s="259" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="261"/>
+      <c r="C14" s="260"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22955,7 +22992,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22964,7 +23001,7 @@
       </c>
       <c r="C16" s="154">
         <f>C36</f>
-        <v>399.65848092949506</v>
+        <v>368.09607588255449</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22974,20 +23011,20 @@
       <c r="C17" s="156">
         <v>0.32</v>
       </c>
-      <c r="E17" s="259" t="s">
+      <c r="E17" s="261" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="260" t="s">
+      <c r="B19" s="259" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="261"/>
+      <c r="C19" s="260"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -23021,7 +23058,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>127147.81</v>
+        <v>130476.23</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23048,15 +23085,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>126620.81</v>
+        <v>129949.22999999998</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="260" t="s">
+      <c r="B28" s="259" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="261"/>
+      <c r="C28" s="260"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23064,7 +23101,7 @@
       </c>
       <c r="C29" s="159">
         <f>SUM(H10:L10)</f>
-        <v>31574.021663466934</v>
+        <v>29071.371119888725</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23073,7 +23110,7 @@
       </c>
       <c r="C30" s="159">
         <f>L11</f>
-        <v>112175.68995208076</v>
+        <v>103284.31227371345</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23082,7 +23119,7 @@
       </c>
       <c r="C31" s="162">
         <f>C29+C30</f>
-        <v>143749.71161554771</v>
+        <v>132355.68339360217</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23109,7 +23146,7 @@
       </c>
       <c r="C34" s="162">
         <f>C31+C32-C33</f>
-        <v>144276.71161554771</v>
+        <v>132882.68339360217</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23127,21 +23164,21 @@
       </c>
       <c r="C36" s="165">
         <f>C34/C35</f>
-        <v>399.65848092949506</v>
+        <v>368.09607588255449</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23188,48 +23225,48 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="X2" s="199" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Y2" s="199" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Z2" s="199" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AA2" s="199" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AB2" s="7"/>
       <c r="AD2" s="7"/>
@@ -23261,7 +23298,7 @@
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U3" s="10" t="s">
         <v>87</v>
@@ -23279,10 +23316,10 @@
         <v>86</v>
       </c>
       <c r="Z3" s="199" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AA3" s="199" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="59" t="s">
@@ -23597,7 +23634,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B9" s="20" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
@@ -23657,7 +23694,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B10" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
@@ -23838,11 +23875,11 @@
         <v>-26</v>
       </c>
       <c r="AA12" s="62">
-        <v>1684</v>
+        <v>-4</v>
       </c>
       <c r="AC12" s="62">
         <f t="shared" si="0"/>
-        <v>1574</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
@@ -23935,7 +23972,7 @@
         <v>1130</v>
       </c>
       <c r="Q14" s="18">
-        <v>9905</v>
+        <v>4314</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -24121,7 +24158,7 @@
         <v>1643</v>
       </c>
       <c r="Q17" s="18">
-        <v>9424</v>
+        <v>3833</v>
       </c>
       <c r="R17" s="60"/>
       <c r="S17" s="60"/>
@@ -24138,21 +24175,21 @@
         <v>252</v>
       </c>
       <c r="X17" s="18">
-        <v>1182</v>
+        <v>571</v>
       </c>
       <c r="Y17" s="18">
-        <v>1842</v>
+        <v>739</v>
       </c>
       <c r="Z17" s="18">
-        <v>3205</v>
+        <v>1016</v>
       </c>
       <c r="AA17" s="18">
-        <v>3195</v>
+        <v>1507</v>
       </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="61">
         <f t="shared" si="0"/>
-        <v>9424</v>
+        <v>3833</v>
       </c>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
@@ -24510,7 +24547,7 @@
         <v>4.6100000000000003</v>
       </c>
       <c r="Q22" s="26">
-        <v>26.92</v>
+        <v>10.949104414261461</v>
       </c>
       <c r="T22" s="26">
         <v>0.43</v>
@@ -24525,20 +24562,20 @@
         <v>0.7</v>
       </c>
       <c r="X22" s="26">
-        <v>3.34</v>
+        <v>1.655072463768116</v>
       </c>
       <c r="Y22" s="26">
-        <v>5.27</v>
+        <v>2.1671554252199412</v>
       </c>
       <c r="Z22" s="26">
-        <v>9.26</v>
+        <v>2.9707602339181287</v>
       </c>
       <c r="AA22" s="26">
-        <v>9.1300000000000008</v>
+        <v>4.305714285714286</v>
       </c>
       <c r="AC22" s="26">
         <f>SUM(X22:AA22)</f>
-        <v>27</v>
+        <v>11.098702408620472</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
@@ -24576,7 +24613,7 @@
       </c>
       <c r="Q23" s="65">
         <f t="shared" si="13"/>
-        <v>26.92</v>
+        <v>10.949104414261461</v>
       </c>
       <c r="T23" s="65">
         <f t="shared" ref="T23:Z23" si="14">T22/T$84</f>
@@ -24596,23 +24633,23 @@
       </c>
       <c r="X23" s="65">
         <f t="shared" si="14"/>
-        <v>3.34</v>
+        <v>1.655072463768116</v>
       </c>
       <c r="Y23" s="65">
         <f t="shared" si="14"/>
-        <v>5.27</v>
+        <v>2.1671554252199412</v>
       </c>
       <c r="Z23" s="65">
         <f t="shared" si="14"/>
-        <v>9.26</v>
+        <v>2.9707602339181287</v>
       </c>
       <c r="AA23" s="65">
         <f t="shared" ref="AA23" si="15">AA22/AA$84</f>
-        <v>9.1300000000000008</v>
+        <v>4.305714285714286</v>
       </c>
       <c r="AC23" s="65">
         <f>AC22/AC$84</f>
-        <v>27</v>
+        <v>11.098702408620472</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
@@ -24644,7 +24681,7 @@
         <v>4.45</v>
       </c>
       <c r="Q24" s="26">
-        <v>24.28</v>
+        <v>9.8753438030560279</v>
       </c>
       <c r="T24" s="63">
         <v>0.42</v>
@@ -24659,20 +24696,20 @@
         <v>0.67</v>
       </c>
       <c r="X24" s="26">
-        <v>3.07</v>
+        <v>1.5186170212765957</v>
       </c>
       <c r="Y24" s="26">
-        <v>4.7300000000000004</v>
+        <v>1.9396325459317585</v>
       </c>
       <c r="Z24" s="26">
-        <v>8.1999999999999993</v>
+        <v>2.6253229974160206</v>
       </c>
       <c r="AA24" s="26">
-        <v>8.2100000000000009</v>
+        <v>3.8740359897172238</v>
       </c>
       <c r="AC24" s="26">
         <f>SUM(X24:AA24)</f>
-        <v>24.21</v>
+        <v>9.9576085543415989</v>
       </c>
     </row>
     <row r="25" spans="1:31" s="30" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24711,7 +24748,7 @@
       </c>
       <c r="Q25" s="66">
         <f t="shared" si="16"/>
-        <v>24.28</v>
+        <v>9.8753438030560279</v>
       </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -24733,24 +24770,24 @@
       </c>
       <c r="X25" s="66">
         <f t="shared" si="17"/>
-        <v>3.07</v>
+        <v>1.5186170212765957</v>
       </c>
       <c r="Y25" s="66">
         <f t="shared" si="17"/>
-        <v>4.7300000000000004</v>
+        <v>1.9396325459317585</v>
       </c>
       <c r="Z25" s="66">
         <f t="shared" si="17"/>
-        <v>8.1999999999999993</v>
+        <v>2.6253229974160206</v>
       </c>
       <c r="AA25" s="66">
         <f t="shared" ref="AA25" si="18">AA24/AA$84</f>
-        <v>8.2100000000000009</v>
+        <v>3.8740359897172238</v>
       </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="66">
         <f>AC24/AC$84</f>
-        <v>24.21</v>
+        <v>9.9576085543415989</v>
       </c>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
@@ -26238,17 +26275,17 @@
         <v>88</v>
       </c>
       <c r="Y52" s="21">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="Z52" s="21">
-        <v>276</v>
+        <v>96</v>
       </c>
       <c r="AA52" s="21">
         <v>99</v>
       </c>
       <c r="AC52" s="62">
         <f>SUM(X52:AA52)</f>
-        <v>643</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.2">
@@ -26298,17 +26335,17 @@
         <v>53</v>
       </c>
       <c r="Y53" s="21">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="Z53" s="21">
-        <v>159</v>
+        <v>53</v>
       </c>
       <c r="AA53" s="21">
         <v>45</v>
       </c>
       <c r="AC53" s="62">
         <f t="shared" ref="AC53:AC57" si="26">SUM(X53:AA53)</f>
-        <v>363</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.2">
@@ -26358,17 +26395,17 @@
         <v>131</v>
       </c>
       <c r="Y54" s="62">
-        <v>-199</v>
+        <v>-330</v>
       </c>
       <c r="Z54" s="62">
-        <v>-408</v>
+        <v>-209</v>
       </c>
       <c r="AA54" s="62">
         <v>-133</v>
       </c>
       <c r="AC54" s="62">
         <f t="shared" si="26"/>
-        <v>-609</v>
+        <v>-541</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.2">
@@ -26418,17 +26455,17 @@
         <v>-101</v>
       </c>
       <c r="Y55" s="62">
-        <v>-55</v>
+        <v>46</v>
       </c>
       <c r="Z55" s="62">
-        <v>-64</v>
+        <v>-9</v>
       </c>
       <c r="AA55" s="62">
         <v>-154</v>
       </c>
       <c r="AC55" s="62">
         <f>SUM(X55:AA55)</f>
-        <v>-374</v>
+        <v>-218</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
@@ -26477,18 +26514,18 @@
       <c r="X56" s="21">
         <v>248</v>
       </c>
-      <c r="Y56" s="21">
-        <v>219</v>
+      <c r="Y56" s="62">
+        <v>-29</v>
       </c>
       <c r="Z56" s="62">
-        <v>289</v>
+        <v>70</v>
       </c>
       <c r="AA56" s="62">
         <v>96</v>
       </c>
       <c r="AC56" s="62">
         <f t="shared" si="26"/>
-        <v>852</v>
+        <v>385</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.2">
@@ -26549,19 +26586,17 @@
         <v>-377</v>
       </c>
       <c r="Y57" s="62">
-        <f>42+51-577+244</f>
-        <v>-240</v>
+        <v>137</v>
       </c>
       <c r="Z57" s="62">
-        <f>29+94-598+290</f>
-        <v>-185</v>
+        <v>55</v>
       </c>
       <c r="AA57" s="62">
         <v>-99</v>
       </c>
       <c r="AC57" s="62">
         <f t="shared" si="26"/>
-        <v>-901</v>
+        <v>-284</v>
       </c>
     </row>
     <row r="58" spans="1:31" s="19" customFormat="1" x14ac:dyDescent="0.2">
@@ -26614,10 +26649,10 @@
         <v>672</v>
       </c>
       <c r="Y58" s="18">
-        <v>1417</v>
+        <v>745</v>
       </c>
       <c r="Z58" s="18">
-        <v>2540</v>
+        <v>1123</v>
       </c>
       <c r="AA58" s="18">
         <v>1389</v>
@@ -26625,7 +26660,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="61">
         <f>SUM(X58:AA58)</f>
-        <v>6018</v>
+        <v>3929</v>
       </c>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1"/>
@@ -26677,17 +26712,17 @@
         <v>-73</v>
       </c>
       <c r="Y59" s="62">
-        <v>-165</v>
+        <v>-92</v>
       </c>
       <c r="Z59" s="62">
-        <v>-310</v>
+        <v>-145</v>
       </c>
       <c r="AA59" s="62">
         <v>-108</v>
       </c>
       <c r="AC59" s="62">
         <f>SUM(X59:AA59)</f>
-        <v>-656</v>
+        <v>-418</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.2">
@@ -26800,10 +26835,10 @@
         <v>-57</v>
       </c>
       <c r="Y61" s="61">
-        <v>-173</v>
+        <v>-116</v>
       </c>
       <c r="Z61" s="61">
-        <v>-318</v>
+        <v>-145</v>
       </c>
       <c r="AA61" s="61">
         <v>-111</v>
@@ -26811,7 +26846,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="61">
         <f t="shared" si="27"/>
-        <v>-659</v>
+        <v>-429</v>
       </c>
       <c r="AD61" s="1"/>
       <c r="AE61" s="1"/>
@@ -26863,17 +26898,17 @@
         <v>-553</v>
       </c>
       <c r="Y62" s="62">
-        <v>-1168</v>
+        <v>-615</v>
       </c>
       <c r="Z62" s="62">
-        <v>-1920</v>
+        <v>-752</v>
       </c>
       <c r="AA62" s="62">
         <v>-672</v>
       </c>
       <c r="AC62" s="62">
         <f t="shared" si="27"/>
-        <v>-4313</v>
+        <v>-2592</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
@@ -26924,17 +26959,17 @@
         <v>-34</v>
       </c>
       <c r="Y63" s="62">
-        <v>-77</v>
+        <v>-48</v>
       </c>
       <c r="Z63" s="62">
-        <v>-120</v>
+        <v>-43</v>
       </c>
       <c r="AA63" s="62">
         <v>-54</v>
       </c>
       <c r="AC63" s="62">
         <f>SUM(X63:AA63)</f>
-        <v>-285</v>
+        <v>-179</v>
       </c>
     </row>
     <row r="64" spans="1:31" x14ac:dyDescent="0.2">
@@ -27047,10 +27082,10 @@
         <v>-678</v>
       </c>
       <c r="Y65" s="71">
-        <v>-1381</v>
+        <v>-703</v>
       </c>
       <c r="Z65" s="71">
-        <v>-2283</v>
+        <v>-902</v>
       </c>
       <c r="AA65" s="71">
         <v>-1749</v>
@@ -27058,7 +27093,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="71">
         <f t="shared" si="27"/>
-        <v>-6091</v>
+        <v>-4032</v>
       </c>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
@@ -27171,11 +27206,11 @@
       </c>
       <c r="AA68" s="64">
         <f t="shared" ref="AA68:AC68" si="32">AA5-AA6-AA10+AA12+AA13+AA15-AA16</f>
-        <v>3195</v>
+        <v>1507</v>
       </c>
       <c r="AC68" s="64">
         <f t="shared" si="32"/>
-        <v>5521</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="69" spans="1:31" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -27241,7 +27276,7 @@
       </c>
       <c r="Q69" s="40">
         <f t="shared" si="33"/>
-        <v>5591</v>
+        <v>0</v>
       </c>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -27263,15 +27298,15 @@
       </c>
       <c r="X69" s="40">
         <f t="shared" si="35"/>
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="Y69" s="40">
         <f t="shared" si="35"/>
-        <v>1103</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="40">
         <f t="shared" ref="Z69:AA69" si="36">Z17-Z68</f>
-        <v>2189</v>
+        <v>0</v>
       </c>
       <c r="AA69" s="40">
         <f t="shared" si="36"/>
@@ -27280,7 +27315,7 @@
       <c r="AB69" s="16"/>
       <c r="AC69" s="40">
         <f>AC17-AC68</f>
-        <v>3903</v>
+        <v>0</v>
       </c>
       <c r="AD69" s="1"/>
       <c r="AE69" s="1"/>
@@ -28044,7 +28079,7 @@
       </c>
       <c r="Q82" s="46">
         <f t="shared" si="64"/>
-        <v>4.8561332660272592E-2</v>
+        <v>0.1114974501622624</v>
       </c>
       <c r="T82" s="46">
         <f t="shared" ref="T82:Z82" si="66">IF(AND(T14&gt;0,T15&lt;0),-(T15)/T14,0)</f>
@@ -28826,7 +28861,7 @@
       </c>
       <c r="Q95" s="52">
         <f t="shared" si="85"/>
-        <v>7.7654867256637168</v>
+        <v>2.8176991150442476</v>
       </c>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
@@ -28930,7 +28965,7 @@
       </c>
       <c r="Q96" s="52">
         <f t="shared" si="94"/>
-        <v>4.7358490566037732</v>
+        <v>1.3329275715155204</v>
       </c>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
@@ -28967,28 +29002,28 @@
 IF(X17=0,0,IF(X17&gt;0,1,-1)),
 (X17-W17)/ABS(W17)
 )</f>
-        <v>3.6904761904761907</v>
+        <v>1.2658730158730158</v>
       </c>
       <c r="Y96" s="52">
         <f t="shared" ref="Y96" si="100">IF(X17=0,
 IF(Y17=0,0,IF(Y17&gt;0,1,-1)),
 (Y17-X17)/ABS(X17)
 )</f>
-        <v>0.55837563451776651</v>
+        <v>0.29422066549912435</v>
       </c>
       <c r="Z96" s="52">
         <f t="shared" ref="Z96" si="101">IF(Y17=0,
 IF(Z17=0,0,IF(Z17&gt;0,1,-1)),
 (Z17-Y17)/ABS(Y17)
 )</f>
-        <v>0.73995656894679696</v>
+        <v>0.37483085250338294</v>
       </c>
       <c r="AA96" s="52">
         <f t="shared" ref="AA96" si="102">IF(Z17=0,
 IF(AA17=0,0,IF(AA17&gt;0,1,-1)),
 (AA17-Z17)/ABS(Z17)
 )</f>
-        <v>-3.1201248049921998E-3</v>
+        <v>0.48326771653543305</v>
       </c>
       <c r="AB96" s="1"/>
       <c r="AC96" s="67"/>
@@ -29193,7 +29228,7 @@
       </c>
       <c r="Q101" s="55">
         <f t="shared" si="109"/>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
@@ -29215,24 +29250,24 @@
       </c>
       <c r="X101" s="55">
         <f t="shared" si="110"/>
-        <v>0.41944641589779985</v>
+        <v>0.20262597586941092</v>
       </c>
       <c r="Y101" s="55">
         <f t="shared" si="110"/>
-        <v>0.61054027179317205</v>
+        <v>0.24494530991050711</v>
       </c>
       <c r="Z101" s="55">
         <f t="shared" si="110"/>
-        <v>0.96044351213664969</v>
+        <v>0.30446508840275699</v>
       </c>
       <c r="AA101" s="55">
         <f t="shared" ref="AA101" si="111">AA109/AA5</f>
-        <v>0.8526821457165733</v>
+        <v>0.40218841740058714</v>
       </c>
       <c r="AB101" s="1"/>
       <c r="AC101" s="55">
         <f>AC109/AC5</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
       <c r="AD101" s="1"/>
       <c r="AE101" s="1"/>
@@ -29313,7 +29348,7 @@
       </c>
       <c r="Q104" s="81">
         <f t="shared" si="112"/>
-        <v>4.8561332660272592E-2</v>
+        <v>0.1114974501622624</v>
       </c>
       <c r="T104" s="81">
         <f t="shared" ref="T104:Z104" si="114">IF(AND(T82&gt;=0,T11&gt;=0),T82,0)</f>
@@ -29553,7 +29588,7 @@
       </c>
       <c r="Q107" s="25">
         <f t="shared" si="122"/>
-        <v>4236.7563856638062</v>
+        <v>3956.5018544274453</v>
       </c>
       <c r="T107" s="67"/>
       <c r="U107" s="67"/>
@@ -29627,11 +29662,11 @@
       </c>
       <c r="Y108" s="126">
         <f t="shared" si="124"/>
-        <v>-165</v>
+        <v>-92</v>
       </c>
       <c r="Z108" s="126">
         <f t="shared" si="124"/>
-        <v>-310</v>
+        <v>-145</v>
       </c>
       <c r="AA108" s="126">
         <f t="shared" ref="AA108" si="125">AA59+AA60</f>
@@ -29639,7 +29674,7 @@
       </c>
       <c r="AC108" s="126">
         <f>AC59+AC60</f>
-        <v>-656</v>
+        <v>-418</v>
       </c>
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.2">
@@ -29677,7 +29712,7 @@
       </c>
       <c r="Q109" s="126">
         <f t="shared" si="126"/>
-        <v>9424</v>
+        <v>3833</v>
       </c>
       <c r="T109" s="126">
         <f t="shared" ref="T109:Z109" si="127">T16+T17</f>
@@ -29697,23 +29732,23 @@
       </c>
       <c r="X109" s="126">
         <f t="shared" si="127"/>
-        <v>1182</v>
+        <v>571</v>
       </c>
       <c r="Y109" s="126">
         <f t="shared" si="127"/>
-        <v>1842</v>
+        <v>739</v>
       </c>
       <c r="Z109" s="126">
         <f t="shared" si="127"/>
-        <v>3205</v>
+        <v>1016</v>
       </c>
       <c r="AA109" s="126">
         <f t="shared" ref="AA109" si="128">AA16+AA17</f>
-        <v>3195</v>
+        <v>1507</v>
       </c>
       <c r="AC109" s="126">
         <f>AC16+AC17</f>
-        <v>9424</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
@@ -29872,7 +29907,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29946,7 +29981,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30007,7 +30042,7 @@
       </c>
       <c r="Q119" s="74">
         <f t="shared" si="135"/>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
       <c r="T119" s="77"/>
       <c r="U119" s="77"/>
@@ -30019,7 +30054,7 @@
       <c r="AA119" s="77"/>
       <c r="AC119" s="74">
         <f>AC109/AC5</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -30089,7 +30124,7 @@
       </c>
       <c r="Q121" s="76">
         <f>Q119*Q120</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
       <c r="T121" s="79"/>
       <c r="U121" s="79"/>
@@ -30101,7 +30136,7 @@
       <c r="AA121" s="79"/>
       <c r="AC121" s="76">
         <f>AC119*AC120</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
     </row>
     <row r="122" spans="1:31" x14ac:dyDescent="0.2">
@@ -30171,7 +30206,7 @@
       </c>
       <c r="Q123" s="76">
         <f>Q121*Q122</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
       <c r="T123" s="79"/>
       <c r="U123" s="79"/>
@@ -30183,7 +30218,7 @@
       <c r="AA123" s="79"/>
       <c r="AC123" s="76">
         <f>AC121*AC122</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
     </row>
     <row r="125" spans="1:31" x14ac:dyDescent="0.2">
@@ -30416,7 +30451,7 @@
     </row>
     <row r="131" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B131" s="20" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C131" s="49"/>
       <c r="D131" s="49"/>
@@ -30461,7 +30496,7 @@
     </row>
     <row r="132" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B132" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C132" s="49"/>
       <c r="D132" s="49"/>
@@ -30506,7 +30541,7 @@
     </row>
     <row r="133" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B133" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C133" s="49"/>
       <c r="D133" s="49"/>
@@ -30537,19 +30572,19 @@
       </c>
       <c r="W133" s="225">
         <f t="shared" ref="W133" si="152">X24</f>
-        <v>3.07</v>
+        <v>1.5186170212765957</v>
       </c>
       <c r="X133" s="225">
         <f t="shared" ref="X133" si="153">Y24</f>
-        <v>4.7300000000000004</v>
+        <v>1.9396325459317585</v>
       </c>
       <c r="Y133" s="225">
         <f t="shared" ref="Y133" si="154">Z24</f>
-        <v>8.1999999999999993</v>
+        <v>2.6253229974160206</v>
       </c>
       <c r="Z133" s="225">
         <f t="shared" ref="Z133" si="155">AA24</f>
-        <v>8.2100000000000009</v>
+        <v>3.8740359897172238</v>
       </c>
       <c r="AA133" s="225">
         <f t="shared" ref="AA133" si="156">AB24</f>
@@ -30590,11 +30625,11 @@
       </c>
       <c r="W134" s="221" t="str">
         <f t="shared" si="157"/>
-        <v>BEAT</v>
+        <v>MET</v>
       </c>
       <c r="X134" s="221" t="str">
         <f t="shared" si="157"/>
-        <v>BEAT</v>
+        <v>MET</v>
       </c>
       <c r="Y134" s="221" t="str">
         <f t="shared" si="157"/>
@@ -30677,7 +30712,7 @@
       </c>
       <c r="Q138" s="81">
         <f t="shared" si="158"/>
-        <v>0.50818716392752861</v>
+        <v>0.47457141111040485</v>
       </c>
       <c r="T138" s="49"/>
       <c r="U138" s="49"/>
@@ -31268,13 +31303,13 @@
         <f t="shared" si="191"/>
         <v>45.769230769230766</v>
       </c>
-      <c r="AA147" s="177" t="str">
+      <c r="AA147" s="177">
         <f t="shared" ref="AA147" si="192">IF(AA12&gt;=0,"N/A",IF(AA11&lt;=0,"N/A",AA11/-AA12))</f>
-        <v>N/A</v>
-      </c>
-      <c r="AC147" s="177" t="str">
+        <v>390.75</v>
+      </c>
+      <c r="AC147" s="177">
         <f>IF(AC12&gt;=0,"N/A",IF(AC11&lt;=0,"N/A",AC11/-AC12))</f>
-        <v>N/A</v>
+        <v>39.061403508771932</v>
       </c>
     </row>
     <row r="148" spans="2:29" x14ac:dyDescent="0.2">
@@ -31303,7 +31338,7 @@
       </c>
       <c r="Q148" s="72">
         <f>Q115/Statement!Q25</f>
-        <v>22.199341021416803</v>
+        <v>54.580378237889889</v>
       </c>
       <c r="T148" s="49"/>
       <c r="U148" s="49"/>
@@ -31315,7 +31350,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>14.548120611317636</v>
+        <v>36.296867669337487</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31356,7 +31391,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>10.44852407307067</v>
+        <v>10.722040986144439</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31421,7 +31456,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>14.344292644404332</v>
+        <v>14.719791290613719</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31486,7 +31521,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>140531.78999999998</v>
+        <v>144210.57</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31551,7 +31586,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>140004.78999999998</v>
+        <v>143683.57</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31592,7 +31627,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>10.837122842325256</v>
+        <v>11.121880176484249</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31633,7 +31668,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>31.440554682236691</v>
+        <v>32.266689871996405</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31686,11 +31721,11 @@
       </c>
       <c r="Y155" s="64">
         <f t="shared" si="199"/>
-        <v>1146</v>
+        <v>600</v>
       </c>
       <c r="Z155" s="64">
         <f t="shared" si="199"/>
-        <v>2071</v>
+        <v>925</v>
       </c>
       <c r="AA155" s="64">
         <f t="shared" ref="AA155" si="200">AA58-AA53+AA108+AA64</f>
@@ -31698,7 +31733,7 @@
       </c>
       <c r="AC155" s="64">
         <f>AC58-AC53+AC108+AC64</f>
-        <v>4999</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31727,7 +31762,7 @@
       </c>
       <c r="Q156" s="64">
         <f t="shared" si="201"/>
-        <v>3535.7563856638062</v>
+        <v>3255.5018544274453</v>
       </c>
       <c r="T156" s="49"/>
       <c r="U156" s="49"/>
@@ -31739,7 +31774,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="64">
         <f t="shared" ref="AC156" si="202">AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
-        <v>3191.7563856638062</v>
+        <v>3535.7563856638062</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31780,7 +31815,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>28.111980396079211</v>
+        <v>43.607671605684914</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31809,7 +31844,7 @@
       </c>
       <c r="Q158" s="72">
         <f t="shared" ref="Q158" si="207">Q152/Q156</f>
-        <v>60.675560360961683</v>
+        <v>65.898902717022324</v>
       </c>
       <c r="T158" s="49"/>
       <c r="U158" s="49"/>
@@ -31821,7 +31856,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>43.864497500138143</v>
+        <v>40.63729350319047</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31862,7 +31897,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>3.5572022529564311E-2</v>
+        <v>2.2931744878340054E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31891,7 +31926,7 @@
       </c>
       <c r="Q160" s="74">
         <f t="shared" si="211"/>
-        <v>4.5046382189239335E-2</v>
+        <v>1.8321602603072407E-2</v>
       </c>
       <c r="T160" s="49"/>
       <c r="U160" s="49"/>
@@ -31903,7 +31938,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>6.8737400982368482E-2</v>
+        <v>2.7550586709298063E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31944,7 +31979,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.4196076204537067E-3</v>
+        <v>1.3833937415267132E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31985,7 +32020,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>3.0690564746951567E-2</v>
+        <v>1.7973717183144063E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32026,7 +32061,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>3.2718575633314005E-2</v>
+        <v>1.9214957683060262E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32055,7 +32090,7 @@
       </c>
       <c r="Q164" s="152">
         <f t="shared" si="215"/>
-        <v>0.27368653809612248</v>
+        <v>0.25199333186991602</v>
       </c>
       <c r="T164" s="49"/>
       <c r="U164" s="49"/>
@@ -32067,7 +32102,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="152">
         <f>AC156/AC5</f>
-        <v>0.24705909015123509</v>
+        <v>0.27368653809612248</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -32108,7 +32143,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="152">
         <f>AC155/AC5</f>
-        <v>0.38694945429212785</v>
+        <v>0.25597956498180974</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32149,7 +32184,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="152">
         <f>-AC63/AC155</f>
-        <v>5.7011402280456092E-2</v>
+        <v>5.4127608104021771E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -32190,7 +32225,7 @@
       <c r="AA167" s="49"/>
       <c r="AC167" s="152">
         <f>-AC62/AC155</f>
-        <v>0.86277255451090218</v>
+        <v>0.78379195645600241</v>
       </c>
     </row>
     <row r="168" spans="2:29" x14ac:dyDescent="0.2">
@@ -32231,7 +32266,7 @@
       <c r="AA168" s="49"/>
       <c r="AC168" s="152">
         <f>(-AC63-AC62)/AC155</f>
-        <v>0.91978395679135827</v>
+        <v>0.83791956456002414</v>
       </c>
     </row>
     <row r="169" spans="2:29" x14ac:dyDescent="0.2">
@@ -32390,11 +32425,11 @@
       </c>
       <c r="Y171" s="152">
         <f t="shared" si="225"/>
-        <v>7.4805928016937195E-2</v>
+        <v>7.1140939597315433E-2</v>
       </c>
       <c r="Z171" s="152">
         <f t="shared" si="225"/>
-        <v>6.2598425196850396E-2</v>
+        <v>4.7195013357079249E-2</v>
       </c>
       <c r="AA171" s="152">
         <f t="shared" ref="AA171" si="226">AA53/AA58</f>
@@ -32402,7 +32437,7 @@
       </c>
       <c r="AC171" s="152">
         <f>AC53/AC58</f>
-        <v>6.0319042871385842E-2</v>
+        <v>5.1921608551794347E-2</v>
       </c>
     </row>
     <row r="172" spans="2:29" x14ac:dyDescent="0.2">
@@ -32455,11 +32490,11 @@
       </c>
       <c r="Y172" s="152">
         <f t="shared" si="228"/>
-        <v>3.5134239310573419E-2</v>
+        <v>1.7567119655286709E-2</v>
       </c>
       <c r="Z172" s="152">
         <f t="shared" si="228"/>
-        <v>4.7647587653581062E-2</v>
+        <v>1.5882529217860354E-2</v>
       </c>
       <c r="AA172" s="152">
         <f t="shared" ref="AA172" si="229">AA53/AA5</f>
@@ -32467,7 +32502,7 @@
       </c>
       <c r="AC172" s="152">
         <f>AC53/AC5</f>
-        <v>2.8098150011610805E-2</v>
+        <v>1.5790695874293676E-2</v>
       </c>
     </row>
     <row r="173" spans="2:29" x14ac:dyDescent="0.2">
@@ -32573,7 +32608,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>3.7500411828526492E-3</v>
+        <v>3.6543784550605407E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -32626,11 +32661,11 @@
       </c>
       <c r="Y175" s="152">
         <f t="shared" si="235"/>
-        <v>5.4690089492873718E-2</v>
+        <v>3.0493868080875043E-2</v>
       </c>
       <c r="Z175" s="152">
         <f t="shared" si="235"/>
-        <v>9.2897812406353017E-2</v>
+        <v>4.3452202577165117E-2</v>
       </c>
       <c r="AA175" s="152">
         <f t="shared" ref="AA175" si="236">-AA108/AA5</f>
@@ -32638,7 +32673,7 @@
       </c>
       <c r="AC175" s="152">
         <f>-AC108/AC5</f>
-        <v>5.0777923987924765E-2</v>
+        <v>3.2355445467915474E-2</v>
       </c>
     </row>
     <row r="176" spans="2:29" x14ac:dyDescent="0.2">
@@ -32691,11 +32726,11 @@
       </c>
       <c r="Y176" s="152">
         <f t="shared" si="238"/>
-        <v>0.11644318983768526</v>
+        <v>0.12348993288590604</v>
       </c>
       <c r="Z176" s="152">
         <f t="shared" si="238"/>
-        <v>0.12204724409448819</v>
+        <v>0.12911843276936777</v>
       </c>
       <c r="AA176" s="152">
         <f t="shared" ref="AA176" si="239">-(AA108/AA58)</f>
@@ -32703,7 +32738,7 @@
       </c>
       <c r="AC176" s="152">
         <f>-(AC108/AC58)</f>
-        <v>0.10900631439016284</v>
+        <v>0.10638839399338254</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32756,11 +32791,11 @@
       </c>
       <c r="Y177" s="152">
         <f t="shared" si="241"/>
-        <v>0.91666666666666663</v>
+        <v>1</v>
       </c>
       <c r="Z177" s="152">
         <f t="shared" si="241"/>
-        <v>1.1231884057971016</v>
+        <v>1.5104166666666667</v>
       </c>
       <c r="AA177" s="152">
         <f t="shared" ref="AA177" si="242">-AA108/AA52</f>
@@ -32768,7 +32803,7 @@
       </c>
       <c r="AC177" s="152">
         <f>-AC108/AC52</f>
-        <v>1.0202177293934682</v>
+        <v>1.1146666666666667</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -32951,7 +32986,7 @@
     </row>
     <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B185" s="20" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C185" s="62"/>
       <c r="D185" s="62"/>
@@ -33011,7 +33046,7 @@
     </row>
     <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B186" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C186" s="62"/>
       <c r="D186" s="62"/>
@@ -33071,7 +33106,7 @@
     </row>
     <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B187" s="20" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C187" s="62"/>
       <c r="D187" s="62"/>
@@ -33627,7 +33662,7 @@
       </c>
       <c r="Q203" s="141">
         <f t="shared" ref="Q203" si="266">100*(1+((Q25-$M25)/ABS($M25)))</f>
-        <v>645.59242105263149</v>
+        <v>262.58019417388977</v>
       </c>
       <c r="T203" s="49"/>
       <c r="U203" s="49"/>
@@ -33655,7 +33690,7 @@
     </row>
     <row r="207" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B207" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C207" s="62"/>
       <c r="D207" s="62"/>
@@ -33715,7 +33750,7 @@
     </row>
     <row r="208" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B208" s="231" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C208" s="62"/>
       <c r="D208" s="62"/>
@@ -33775,7 +33810,7 @@
     </row>
     <row r="209" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B209" s="231" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C209" s="62"/>
       <c r="D209" s="62"/>
@@ -33862,7 +33897,7 @@
     </row>
     <row r="211" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B211" s="232" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C211" s="62"/>
       <c r="D211" s="62"/>
@@ -33986,32 +34021,32 @@
   <sheetData>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H5" s="132" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H6" s="242" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H7" s="242" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H8" s="242" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H9" s="242" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="H10" s="243" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
@@ -34067,7 +34102,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34083,7 +34118,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>140531.78999999998</v>
+        <v>144210.57</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34103,14 +34138,14 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>140004.78999999998</v>
+        <v>143683.57</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="174">
         <f>IF(OR(Statement!M17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(4, Statement!M17, Statement!Q17))</f>
-        <v>0.58320081438886584</v>
+        <v>0.26433421272034763</v>
       </c>
       <c r="G7" s="174" t="str">
         <f>IF(OR(Statement!H17&lt;=0, Statement!Q17&lt;=0), "N/A", _xlfn.RRI(9, Statement!H17, Statement!Q17))</f>
@@ -34123,14 +34158,14 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>14.548120611317636</v>
+        <v>36.296867669337487</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
       </c>
       <c r="F8" s="174">
         <f>IF(OR(Statement!M25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(4, Statement!M25, Statement!Q25))</f>
-        <v>0.59400473021836042</v>
+        <v>0.27296215194980888</v>
       </c>
       <c r="G8" s="174" t="str">
         <f>IF(OR(Statement!H25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(9, Statement!H25, Statement!Q25))</f>
@@ -34143,7 +34178,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>10.44852407307067</v>
+        <v>10.722040986144439</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -34163,7 +34198,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>14.344292644404332</v>
+        <v>14.719791290613719</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34183,7 +34218,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>10.837122842325256</v>
+        <v>11.121880176484249</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34192,7 +34227,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>31.440554682236691</v>
+        <v>32.266689871996405</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34218,7 +34253,7 @@
       </c>
       <c r="F16" s="169">
         <f>Statement!AC17</f>
-        <v>9424</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -34234,7 +34269,7 @@
       </c>
       <c r="F17" s="169">
         <f>Statement!AC58</f>
-        <v>6018</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -34243,14 +34278,14 @@
       </c>
       <c r="C18" s="171">
         <f>Statement!AC101</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>253</v>
       </c>
       <c r="F18" s="173">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
-        <v>3406</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -34269,14 +34304,14 @@
       </c>
       <c r="C22" s="171">
         <f>Statement!AC119</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>101</v>
       </c>
       <c r="F22" s="171">
         <f>C24</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
@@ -34292,7 +34327,7 @@
       </c>
       <c r="F23" s="171">
         <f>C26</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
@@ -34301,7 +34336,7 @@
       </c>
       <c r="C24" s="172">
         <f>Statement!AC121</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>104</v>
@@ -34326,7 +34361,7 @@
       </c>
       <c r="C26" s="172">
         <f>Statement!AC123</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
@@ -34407,9 +34442,9 @@
       <c r="E34" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="F34" s="178" t="str">
+      <c r="F34" s="178">
         <f>Statement!AC147</f>
-        <v>N/A</v>
+        <v>39.061403508771932</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
@@ -34428,14 +34463,14 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>6.8737400982368482E-2</v>
+        <v>2.7550586709298063E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
       </c>
       <c r="F38" s="171">
         <f>Statement!AC166</f>
-        <v>5.7011402280456092E-2</v>
+        <v>5.4127608104021771E-2</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
@@ -34444,14 +34479,14 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>3.5572022529564311E-2</v>
+        <v>2.2931744878340054E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
       </c>
       <c r="F39" s="171">
         <f>Statement!AC167</f>
-        <v>0.86277255451090218</v>
+        <v>0.78379195645600241</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
@@ -34460,14 +34495,14 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.4196076204537067E-3</v>
+        <v>1.3833937415267132E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
       </c>
       <c r="F40" s="171">
         <f>Statement!AC168</f>
-        <v>0.91978395679135827</v>
+        <v>0.83791956456002414</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
@@ -34476,7 +34511,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>3.0690564746951567E-2</v>
+        <v>1.7973717183144063E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34485,7 +34520,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.2718575633314005E-2</v>
+        <v>1.9214957683060262E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34529,7 +34564,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>3.7500411828526492E-3</v>
+        <v>3.6543784550605407E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34548,14 +34583,14 @@
       </c>
       <c r="C52" s="171">
         <f>Statement!AC171</f>
-        <v>6.0319042871385842E-2</v>
+        <v>5.1921608551794347E-2</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>303</v>
       </c>
       <c r="F52" s="171">
         <f>Statement!AC175</f>
-        <v>5.0777923987924765E-2</v>
+        <v>3.2355445467915474E-2</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.2">
@@ -34564,14 +34599,14 @@
       </c>
       <c r="C53" s="171">
         <f>Statement!AC172</f>
-        <v>2.8098150011610805E-2</v>
+        <v>1.5790695874293676E-2</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>300</v>
       </c>
       <c r="F53" s="171">
         <f>Statement!AC176</f>
-        <v>0.10900631439016284</v>
+        <v>0.10638839399338254</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.2">
@@ -34580,7 +34615,7 @@
       </c>
       <c r="F54" s="171">
         <f>Statement!AC177</f>
-        <v>1.0202177293934682</v>
+        <v>1.1146666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -34709,7 +34744,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>352.21</v>
+        <v>361.43</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34738,7 +34773,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>140531.78999999998</v>
+        <v>144210.57</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34767,7 +34802,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>140004.78999999998</v>
+        <v>143683.57</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34792,11 +34827,11 @@
       </c>
       <c r="G9" s="170">
         <f>Statement!Q148</f>
-        <v>22.199341021416803</v>
+        <v>54.580378237889889</v>
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>14.548120611317636</v>
+        <v>36.296867669337487</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34825,7 +34860,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>10.44852407307067</v>
+        <v>10.722040986144439</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34854,7 +34889,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>14.344292644404332</v>
+        <v>14.719791290613719</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34883,7 +34918,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>10.837122842325256</v>
+        <v>11.121880176484249</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34912,7 +34947,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>31.440554682236691</v>
+        <v>32.266689871996405</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35006,11 +35041,11 @@
       </c>
       <c r="G18" s="171">
         <f>Statement!Q101</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
       <c r="I18" s="171">
         <f>Statement!AC101</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35046,11 +35081,11 @@
       </c>
       <c r="G21" s="173">
         <f>Statement!Q17</f>
-        <v>9424</v>
+        <v>3833</v>
       </c>
       <c r="I21" s="173">
         <f>Statement!AC17</f>
-        <v>9424</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -35079,7 +35114,7 @@
       </c>
       <c r="I22" s="173">
         <f>Statement!AC58</f>
-        <v>6018</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
@@ -35104,11 +35139,11 @@
       </c>
       <c r="G23" s="191">
         <f t="shared" si="0"/>
-        <v>5495</v>
+        <v>-96</v>
       </c>
       <c r="I23" s="191">
         <f t="shared" si="0"/>
-        <v>3406</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35144,11 +35179,11 @@
       </c>
       <c r="G26" s="171">
         <f>Statement!Q119</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
       <c r="I26" s="171">
         <f>Statement!AC119</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -35202,11 +35237,11 @@
       </c>
       <c r="G28" s="172">
         <f>Statement!Q121</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
       <c r="I28" s="172">
         <f>Statement!AC121</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -35260,11 +35295,11 @@
       </c>
       <c r="G30" s="172">
         <f>Statement!Q123</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
       <c r="I30" s="172">
         <f>Statement!AC123</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35300,11 +35335,11 @@
       </c>
       <c r="G33" s="171">
         <f t="shared" si="1"/>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
       <c r="I33" s="171">
         <f>I28</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
@@ -35329,11 +35364,11 @@
       </c>
       <c r="G34" s="171">
         <f t="shared" si="2"/>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
       <c r="I34" s="171">
         <f>I30</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
@@ -35358,7 +35393,7 @@
       </c>
       <c r="G35" s="171">
         <f>Statement!Q138</f>
-        <v>0.50818716392752861</v>
+        <v>0.47457141111040485</v>
       </c>
       <c r="I35" s="171">
         <f>Statement!AC138</f>
@@ -35643,9 +35678,9 @@
         <f>Statement!Q147</f>
         <v>39.061403508771932</v>
       </c>
-      <c r="I48" s="178" t="str">
+      <c r="I48" s="178">
         <f>Statement!AC147</f>
-        <v>N/A</v>
+        <v>39.061403508771932</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35681,11 +35716,11 @@
       </c>
       <c r="G51" s="171">
         <f>Statement!Q160</f>
-        <v>4.5046382189239335E-2</v>
+        <v>1.8321602603072407E-2</v>
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>6.8737400982368482E-2</v>
+        <v>2.7550586709298063E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35714,7 +35749,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>3.5572022529564311E-2</v>
+        <v>2.2931744878340054E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35743,7 +35778,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.4196076204537067E-3</v>
+        <v>1.3833937415267132E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35772,7 +35807,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>3.0690564746951567E-2</v>
+        <v>1.7973717183144063E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35801,7 +35836,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>3.2718575633314005E-2</v>
+        <v>1.9214957683060262E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35841,7 +35876,7 @@
       </c>
       <c r="I58" s="171">
         <f>Statement!AC166</f>
-        <v>5.7011402280456092E-2</v>
+        <v>5.4127608104021771E-2</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
@@ -35870,7 +35905,7 @@
       </c>
       <c r="I59" s="171">
         <f>Statement!AC167</f>
-        <v>0.86277255451090218</v>
+        <v>0.78379195645600241</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
@@ -35899,7 +35934,7 @@
       </c>
       <c r="I60" s="171">
         <f>Statement!AC168</f>
-        <v>0.91978395679135827</v>
+        <v>0.83791956456002414</v>
       </c>
     </row>
     <row r="62" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36037,7 +36072,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>3.7500411828526492E-3</v>
+        <v>3.6543784550605407E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36077,7 +36112,7 @@
       </c>
       <c r="I71" s="171">
         <f>Statement!AC171</f>
-        <v>6.0319042871385842E-2</v>
+        <v>5.1921608551794347E-2</v>
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
@@ -36106,7 +36141,7 @@
       </c>
       <c r="I72" s="171">
         <f>Statement!AC172</f>
-        <v>2.8098150011610805E-2</v>
+        <v>1.5790695874293676E-2</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36146,7 +36181,7 @@
       </c>
       <c r="I75" s="171">
         <f>Statement!AC175</f>
-        <v>5.0777923987924765E-2</v>
+        <v>3.2355445467915474E-2</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
@@ -36175,7 +36210,7 @@
       </c>
       <c r="I76" s="171">
         <f>Statement!AC176</f>
-        <v>0.10900631439016284</v>
+        <v>0.10638839399338254</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
@@ -36204,7 +36239,7 @@
       </c>
       <c r="I77" s="171">
         <f>Statement!AC177</f>
-        <v>1.0202177293934682</v>
+        <v>1.1146666666666667</v>
       </c>
     </row>
     <row r="79" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36370,7 +36405,7 @@
       </c>
       <c r="G85" s="171">
         <f>Statement!Q96</f>
-        <v>4.7358490566037732</v>
+        <v>1.3329275715155204</v>
       </c>
       <c r="I85" s="193"/>
     </row>
@@ -36527,14 +36562,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="250" t="s">
+      <c r="C3" s="248" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="F3" s="252" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="251"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36601,19 +36636,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="248">
+      <c r="C7" s="251">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="249"/>
-      <c r="F7" s="248">
+      <c r="D7" s="252"/>
+      <c r="F7" s="251">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="249"/>
+      <c r="G7" s="252"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36640,19 +36675,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="248">
+      <c r="C9" s="251">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="249"/>
-      <c r="F9" s="248">
+      <c r="D9" s="252"/>
+      <c r="F9" s="251">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="249"/>
+      <c r="G9" s="252"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36679,19 +36714,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="248">
+      <c r="C11" s="251">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="249"/>
-      <c r="F11" s="248">
+      <c r="D11" s="252"/>
+      <c r="F11" s="251">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="249"/>
+      <c r="G11" s="252"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36718,19 +36753,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="248">
+      <c r="C13" s="251">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="249"/>
-      <c r="F13" s="248">
+      <c r="D13" s="252"/>
+      <c r="F13" s="251">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="249"/>
+      <c r="G13" s="252"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36757,19 +36792,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="248">
+      <c r="C15" s="251">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="249"/>
-      <c r="F15" s="248">
+      <c r="D15" s="252"/>
+      <c r="F15" s="251">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="249"/>
+      <c r="G15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36777,11 +36812,11 @@
       </c>
       <c r="C16" s="196">
         <f>Statement!Z17</f>
-        <v>3205</v>
+        <v>1016</v>
       </c>
       <c r="D16" s="194">
         <f>Statement!AA17</f>
-        <v>3195</v>
+        <v>1507</v>
       </c>
       <c r="F16" s="196">
         <f>Statement!W17</f>
@@ -36789,26 +36824,26 @@
       </c>
       <c r="G16" s="194">
         <f>Statement!AA17</f>
-        <v>3195</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="248">
+      <c r="C17" s="251">
         <f>Statement!AA96</f>
-        <v>-3.1201248049921998E-3</v>
-      </c>
-      <c r="D17" s="249"/>
-      <c r="F17" s="248">
+        <v>0.48326771653543305</v>
+      </c>
+      <c r="D17" s="252"/>
+      <c r="F17" s="251">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
-        <v>11.678571428571429</v>
-      </c>
-      <c r="G17" s="249"/>
+        <v>4.9801587301587302</v>
+      </c>
+      <c r="G17" s="252"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36835,22 +36870,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="248">
+      <c r="C19" s="251">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="249"/>
-      <c r="F19" s="248">
+      <c r="D19" s="252"/>
+      <c r="F19" s="251">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="249"/>
+      <c r="G19" s="252"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36858,11 +36893,11 @@
       </c>
       <c r="C20" s="197">
         <f>Statement!Z25</f>
-        <v>8.1999999999999993</v>
+        <v>2.6253229974160206</v>
       </c>
       <c r="D20" s="198">
         <f>Statement!AA25</f>
-        <v>8.2100000000000009</v>
+        <v>3.8740359897172238</v>
       </c>
       <c r="F20" s="197">
         <f>Statement!W25</f>
@@ -36870,29 +36905,29 @@
       </c>
       <c r="G20" s="198">
         <f>Statement!AA25</f>
-        <v>8.2100000000000009</v>
+        <v>3.8740359897172238</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="248">
+      <c r="C21" s="251">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
-        <v>1.219512195122142E-3</v>
-      </c>
-      <c r="D21" s="249"/>
-      <c r="F21" s="248">
+        <v>0.47564166143756464</v>
+      </c>
+      <c r="D21" s="252"/>
+      <c r="F21" s="251">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
-        <v>11.253731343283583</v>
-      </c>
-      <c r="G21" s="249"/>
+        <v>4.7821432682346625</v>
+      </c>
+      <c r="G21" s="252"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36941,22 +36976,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="248">
+      <c r="C25" s="251">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="249"/>
-      <c r="F25" s="248">
+      <c r="D25" s="252"/>
+      <c r="F25" s="251">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="249"/>
+      <c r="G25" s="252"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36984,22 +37019,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="248">
+      <c r="C27" s="251">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="249"/>
-      <c r="F27" s="248">
+      <c r="D27" s="252"/>
+      <c r="F27" s="251">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="249"/>
+      <c r="G27" s="252"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37027,49 +37062,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="248">
+      <c r="C29" s="251">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="249"/>
-      <c r="F29" s="248">
+      <c r="D29" s="252"/>
+      <c r="F29" s="251">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="249"/>
+      <c r="G29" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -37307,7 +37342,7 @@
       </c>
       <c r="L59" s="64">
         <f>Statement!Q17</f>
-        <v>9424</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
@@ -37397,7 +37432,7 @@
       </c>
       <c r="L61" s="64">
         <f>Statement!Q156</f>
-        <v>3535.7563856638062</v>
+        <v>3255.5018544274453</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.2">
@@ -37532,7 +37567,7 @@
       </c>
       <c r="L64" s="58">
         <f>Statement!Q101</f>
-        <v>0.72946822509482157</v>
+        <v>0.29669479061846893</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
@@ -37715,7 +37750,7 @@
       </c>
       <c r="L68" s="214">
         <f>Statement!Q121</f>
-        <v>0.67989322559699872</v>
+        <v>0.276531274799798</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
@@ -37760,7 +37795,7 @@
       </c>
       <c r="L69" s="214">
         <f>Statement!Q123</f>
-        <v>1.0631768953068592</v>
+        <v>0.432423285198556</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
@@ -37805,7 +37840,7 @@
       </c>
       <c r="L70" s="214">
         <f>Statement!Q138</f>
-        <v>0.50818716392752861</v>
+        <v>0.47457141111040485</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
@@ -37940,7 +37975,7 @@
       </c>
       <c r="L73" s="223">
         <f>Statement!Q203</f>
-        <v>645.59242105263149</v>
+        <v>262.58019417388977</v>
       </c>
     </row>
   </sheetData>
@@ -38126,19 +38161,19 @@
       </c>
       <c r="G59" s="64">
         <f>Statement!X17</f>
-        <v>1182</v>
+        <v>571</v>
       </c>
       <c r="H59" s="64">
         <f>Statement!Y17</f>
-        <v>1842</v>
+        <v>739</v>
       </c>
       <c r="I59" s="64">
         <f>Statement!Z17</f>
-        <v>3205</v>
+        <v>1016</v>
       </c>
       <c r="J59" s="64">
         <f>Statement!AA17</f>
-        <v>3195</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.2">
@@ -38237,19 +38272,19 @@
       </c>
       <c r="G62" s="58">
         <f>Statement!X101</f>
-        <v>0.41944641589779985</v>
+        <v>0.20262597586941092</v>
       </c>
       <c r="H62" s="58">
         <f>Statement!Y101</f>
-        <v>0.61054027179317205</v>
+        <v>0.24494530991050711</v>
       </c>
       <c r="I62" s="58">
         <f>Statement!Z101</f>
-        <v>0.96044351213664969</v>
+        <v>0.30446508840275699</v>
       </c>
       <c r="J62" s="58">
         <f>Statement!AA101</f>
-        <v>0.8526821457165733</v>
+        <v>0.40218841740058714</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
@@ -38392,11 +38427,11 @@
       </c>
       <c r="H66" s="64">
         <f>Statement!Y155</f>
-        <v>1146</v>
+        <v>600</v>
       </c>
       <c r="I66" s="64">
         <f>Statement!Z155</f>
-        <v>2071</v>
+        <v>925</v>
       </c>
       <c r="J66" s="64">
         <f>Statement!AA155</f>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587EAAFF-9FB0-6A45-879B-DC975DF0E066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E0D096-0118-254D-B68D-5BF38EDEFE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -200,7 +200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="444">
   <si>
     <t>Ticker</t>
   </si>
@@ -1529,6 +1529,9 @@
   </si>
   <si>
     <t>Removed 5591 form Net Income to take out the one time gain from selling Sandisk and adjusted EPS and also the Quarterly values</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2142,7 +2145,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2483,6 +2486,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2490,12 +2499,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2516,15 +2519,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12898,8 +12904,8 @@
     <v>799.87</v>
     <v>117.23</v>
     <v>2.2572000000000001</v>
-    <v>9.2200000000000006</v>
-    <v>2.6178E-2</v>
+    <v>11.18</v>
+    <v>3.1741999999999999E-2</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12907,24 +12913,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>361.78500000000003</v>
+    <v>364.20729999999998</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46315.693459166403</v>
+    <v>46315.734375323438</v>
     <v>4</v>
     <v>342.59</v>
-    <v>135018682240</v>
+    <v>135750875520</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>349.5</v>
-    <v>14.8879</v>
+    <v>14.9686</v>
     <v>352.21</v>
-    <v>361.43</v>
+    <v>363.39</v>
     <v>373568000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>3912645</v>
+    <v>4647428</v>
     <v>8943779</v>
     <v>2000</v>
   </rv>
@@ -13792,7 +13798,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13830,7 +13836,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>144210.57</v>
+        <v>144992.60999999999</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13857,7 +13863,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>143683.57</v>
+        <v>144465.60999999999</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13877,7 +13883,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13911,7 +13917,7 @@
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>36.296867669337487</v>
+        <v>36.493702078854966</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13931,14 +13937,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>9.2200000000000006</v>
+        <v>11.18</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>10.722040986144439</v>
+        <v>10.780185579379209</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13962,7 +13968,7 @@
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.2931744878340054E-2</v>
+        <v>2.2808058976247138E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13979,14 +13985,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>2.6178E-2</v>
+        <v>3.1741999999999999E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>2.7550586709298063E-2</v>
+        <v>2.7401988371561131E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13994,7 +14000,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.62342145942088167</v>
+        <v>-0.62545259384817753</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -14010,7 +14016,7 @@
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>1.7973717183144063E-2</v>
+        <v>1.787677316795663E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -14026,7 +14032,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.3833937415267132E-3</v>
+        <v>1.3759321940614768E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>360</v>
@@ -14067,10 +14073,10 @@
         <f>Statement!AC123</f>
         <v>0.432423285198556</v>
       </c>
-      <c r="H13" s="180" t="s">
+      <c r="H13" s="264" t="s">
         <v>432</v>
       </c>
-      <c r="I13" s="209">
+      <c r="I13" s="262">
         <f>'Reverse DCF'!C17</f>
         <v>0.32</v>
       </c>
@@ -14090,6 +14096,13 @@
         <f>Statement!AC138</f>
         <v>0.50818716392752861</v>
       </c>
+      <c r="H14" s="182" t="s">
+        <v>443</v>
+      </c>
+      <c r="I14" s="263">
+        <f>'Reverse DCF'!C16</f>
+        <v>368.09607588255449</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="181" t="s">
@@ -14097,7 +14110,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>3.6543784550605407E-3</v>
+        <v>3.63466800135538E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -18818,6 +18831,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18825,12 +18844,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19891,16 +19904,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20023,7 +20036,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20032,7 +20045,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>144210.57</v>
+        <v>144992.60999999999</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20102,7 +20115,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.2420582948518669E-3</v>
+        <v>7.2032785051088163E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20111,7 +20124,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99275794170514808</v>
+        <v>0.99279672149489118</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20138,7 +20151,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15202668596858779</v>
+        <v>0.15203154445576597</v>
       </c>
     </row>
   </sheetData>
@@ -21998,17 +22011,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22113,7 +22126,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22122,7 +22135,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.62342145942088167</v>
+        <v>-0.62545259384817753</v>
       </c>
     </row>
   </sheetData>
@@ -22981,10 +22994,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="259" t="s">
+      <c r="B14" s="260" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="260"/>
+      <c r="C14" s="261"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22992,7 +23005,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -23011,20 +23024,20 @@
       <c r="C17" s="156">
         <v>0.32</v>
       </c>
-      <c r="E17" s="261" t="s">
+      <c r="E17" s="259" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="261"/>
-      <c r="G17" s="261"/>
-      <c r="H17" s="261"/>
-      <c r="I17" s="261"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="259" t="s">
+      <c r="B19" s="260" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="260"/>
+      <c r="C19" s="261"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -23058,7 +23071,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>130476.23</v>
+        <v>131183.79</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23085,15 +23098,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>129949.22999999998</v>
+        <v>130656.79000000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="259" t="s">
+      <c r="B28" s="260" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="260"/>
+      <c r="C28" s="261"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23169,16 +23182,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29907,7 +29920,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29981,7 +29994,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31350,7 +31363,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>36.296867669337487</v>
+        <v>36.493702078854966</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31391,7 +31404,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>10.722040986144439</v>
+        <v>10.780185579379209</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31456,7 +31469,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>14.719791290613719</v>
+        <v>14.799615297833935</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31521,7 +31534,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>144210.57</v>
+        <v>144992.60999999999</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31586,7 +31599,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>143683.57</v>
+        <v>144465.60999999999</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31627,7 +31640,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>11.121880176484249</v>
+        <v>11.182414273550583</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31668,7 +31681,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>32.266689871996405</v>
+        <v>32.442310801706711</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31815,7 +31828,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="205">AC151/AC155</f>
-        <v>43.607671605684914</v>
+        <v>43.844151799213783</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31856,7 +31869,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="205"/>
-        <v>40.63729350319047</v>
+        <v>40.858473899886029</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31897,7 +31910,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="210">AC155/AC151</f>
-        <v>2.2931744878340054E-2</v>
+        <v>2.2808058976247138E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31938,7 +31951,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>2.7550586709298063E-2</v>
+        <v>2.7401988371561131E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31979,7 +31992,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.3833937415267132E-3</v>
+        <v>1.3759321940614768E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32020,7 +32033,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>1.7973717183144063E-2</v>
+        <v>1.787677316795663E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32061,7 +32074,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>1.9214957683060262E-2</v>
+        <v>1.9111318845836351E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32608,7 +32621,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>3.6543784550605407E-3</v>
+        <v>3.63466800135538E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -34102,7 +34115,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34118,7 +34131,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>144210.57</v>
+        <v>144992.60999999999</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34138,7 +34151,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>143683.57</v>
+        <v>144465.60999999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -34158,7 +34171,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>36.296867669337487</v>
+        <v>36.493702078854966</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -34178,7 +34191,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>10.722040986144439</v>
+        <v>10.780185579379209</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -34198,7 +34211,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>14.719791290613719</v>
+        <v>14.799615297833935</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34218,7 +34231,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>11.121880176484249</v>
+        <v>11.182414273550583</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34227,7 +34240,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>32.266689871996405</v>
+        <v>32.442310801706711</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34463,7 +34476,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.7550586709298063E-2</v>
+        <v>2.7401988371561131E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34479,7 +34492,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.2931744878340054E-2</v>
+        <v>2.2808058976247138E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34495,7 +34508,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.3833937415267132E-3</v>
+        <v>1.3759321940614768E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34511,7 +34524,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.7973717183144063E-2</v>
+        <v>1.787677316795663E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34520,7 +34533,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>1.9214957683060262E-2</v>
+        <v>1.9111318845836351E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34564,7 +34577,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>3.6543784550605407E-3</v>
+        <v>3.63466800135538E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34744,7 +34757,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>361.43</v>
+        <v>363.39</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34773,7 +34786,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>144210.57</v>
+        <v>144992.60999999999</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34802,7 +34815,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>143683.57</v>
+        <v>144465.60999999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34831,7 +34844,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>36.296867669337487</v>
+        <v>36.493702078854966</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34860,7 +34873,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>10.722040986144439</v>
+        <v>10.780185579379209</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34889,7 +34902,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>14.719791290613719</v>
+        <v>14.799615297833935</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34918,7 +34931,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>11.121880176484249</v>
+        <v>11.182414273550583</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34947,7 +34960,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>32.266689871996405</v>
+        <v>32.442310801706711</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35720,7 +35733,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>2.7550586709298063E-2</v>
+        <v>2.7401988371561131E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35749,7 +35762,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.2931744878340054E-2</v>
+        <v>2.2808058976247138E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35778,7 +35791,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.3833937415267132E-3</v>
+        <v>1.3759321940614768E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35807,7 +35820,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>1.7973717183144063E-2</v>
+        <v>1.787677316795663E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35836,7 +35849,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>1.9214957683060262E-2</v>
+        <v>1.9111318845836351E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36072,7 +36085,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>3.6543784550605407E-3</v>
+        <v>3.63466800135538E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36562,14 +36575,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="248" t="s">
+      <c r="C3" s="250" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="F3" s="250" t="s">
+      <c r="D3" s="251"/>
+      <c r="F3" s="252" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="249"/>
+      <c r="G3" s="251"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36636,19 +36649,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="251">
+      <c r="C7" s="248">
         <f>Statement!AA88</f>
         <v>0.12286484866646688</v>
       </c>
-      <c r="D7" s="252"/>
-      <c r="F7" s="251">
+      <c r="D7" s="249"/>
+      <c r="F7" s="248">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.43838771593090209</v>
       </c>
-      <c r="G7" s="252"/>
+      <c r="G7" s="249"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36675,19 +36688,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="251">
+      <c r="C9" s="248">
         <f>Statement!AA89</f>
         <v>3.4918723660445516E-2</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="F9" s="251">
+      <c r="D9" s="249"/>
+      <c r="F9" s="248">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1176853055916775</v>
       </c>
-      <c r="G9" s="252"/>
+      <c r="G9" s="249"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36714,19 +36727,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="251">
+      <c r="C11" s="248">
         <f>Statement!AA90</f>
         <v>0.21002386634844869</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="F11" s="251">
+      <c r="D11" s="249"/>
+      <c r="F11" s="248">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.90065604498594187</v>
       </c>
-      <c r="G11" s="252"/>
+      <c r="G11" s="249"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36753,19 +36766,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="251">
+      <c r="C13" s="248">
         <f>Statement!AA93</f>
         <v>-4.3209876543209874E-2</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="F13" s="251">
+      <c r="D13" s="249"/>
+      <c r="F13" s="248">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.20155038759689922</v>
       </c>
-      <c r="G13" s="252"/>
+      <c r="G13" s="249"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36792,19 +36805,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="251">
+      <c r="C15" s="248">
         <f>Statement!AA94</f>
         <v>0.3134453781512605</v>
       </c>
-      <c r="D15" s="252"/>
-      <c r="F15" s="251">
+      <c r="D15" s="249"/>
+      <c r="F15" s="248">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.2985294117647059</v>
       </c>
-      <c r="G15" s="252"/>
+      <c r="G15" s="249"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36831,19 +36844,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="251">
+      <c r="C17" s="248">
         <f>Statement!AA96</f>
         <v>0.48326771653543305</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="F17" s="251">
+      <c r="D17" s="249"/>
+      <c r="F17" s="248">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>4.9801587301587302</v>
       </c>
-      <c r="G17" s="252"/>
+      <c r="G17" s="249"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36870,22 +36883,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="251">
+      <c r="C19" s="248">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>5.1679586563307496E-3</v>
       </c>
-      <c r="D19" s="252"/>
-      <c r="F19" s="251">
+      <c r="D19" s="249"/>
+      <c r="F19" s="248">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>7.4585635359116026E-2</v>
       </c>
-      <c r="G19" s="252"/>
+      <c r="G19" s="249"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36912,22 +36925,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="251">
+      <c r="C21" s="248">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.47564166143756464</v>
       </c>
-      <c r="D21" s="252"/>
-      <c r="F21" s="251">
+      <c r="D21" s="249"/>
+      <c r="F21" s="248">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>4.7821432682346625</v>
       </c>
-      <c r="G21" s="252"/>
+      <c r="G21" s="249"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36976,22 +36989,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="251">
+      <c r="C25" s="248">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.12213997308209959</v>
       </c>
-      <c r="D25" s="252"/>
-      <c r="F25" s="251">
+      <c r="D25" s="249"/>
+      <c r="F25" s="248">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.43194504079003865</v>
       </c>
-      <c r="G25" s="252"/>
+      <c r="G25" s="249"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37019,22 +37032,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="251">
+      <c r="C27" s="248">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.25698324022346369</v>
       </c>
-      <c r="D27" s="252"/>
-      <c r="F27" s="251">
+      <c r="D27" s="249"/>
+      <c r="F27" s="248">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.6071428571428571</v>
       </c>
-      <c r="G27" s="252"/>
+      <c r="G27" s="249"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37062,49 +37075,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="251">
+      <c r="C29" s="248">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>5.3763440860215058E-3</v>
       </c>
-      <c r="D29" s="252"/>
-      <c r="F29" s="251">
+      <c r="D29" s="249"/>
+      <c r="F29" s="248">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.375</v>
       </c>
-      <c r="G29" s="252"/>
+      <c r="G29" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B994B6-92DF-E042-A7A7-B3E494814720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C06DEA9-635E-7B4D-81C3-511B90A38444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1548,7 +1548,7 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1723,12 +1723,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="20">
@@ -2504,12 +2498,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2517,6 +2505,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2537,14 +2531,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12829,11 +12823,11 @@
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
     <v>121.715</v>
-    <v>2.2645</v>
+    <v>2.2770999999999999</v>
     <v>-10.52</v>
     <v>-2.9702000000000003E-2</v>
-    <v>-3.37</v>
-    <v>-9.8060000000000005E-3</v>
+    <v>-2.5459999999999998</v>
+    <v>-7.4080000000000005E-3</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12845,21 +12839,20 @@
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46318.951283032031</v>
+    <v>46318.999974375001</v>
     <v>4</v>
     <v>339.55</v>
-    <v>128384114560</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>346.1</v>
-    <v>13.3001</v>
+    <v>13.7073</v>
     <v>354.19</v>
     <v>343.67</v>
-    <v>340.3</v>
+    <v>341.12400000000002</v>
     <v>373568000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>13929525</v>
+    <v>13953729</v>
     <v>9268205</v>
     <v>2000</v>
   </rv>
@@ -12884,17 +12877,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>7</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -12955,7 +12948,6 @@
     <k n="Last trade time"/>
     <k n="LearnMoreOnLink" t="r"/>
     <k n="Low"/>
-    <k n="Market cap"/>
     <k n="Name" t="s"/>
     <k n="Official name" t="s"/>
     <k n="Open"/>
@@ -13007,7 +12999,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13037,7 +13029,6 @@
       <v t="s">52 week low</v>
       <v t="s">Volume</v>
       <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
       <v t="s">Beta</v>
       <v t="s">P/E</v>
       <v t="s">Shares outstanding</v>
@@ -13119,14 +13110,13 @@
       <v>5</v>
       <v>5</v>
       <v>6</v>
-      <v>7</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
       <v>5</v>
+      <v>7</v>
       <v>8</v>
       <v>9</v>
-      <v>10</v>
       <v>5</v>
       <v>1</v>
       <v>1</v>
@@ -13136,9 +13126,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13166,7 +13156,7 @@
       <v>1</v>
       <v>1</v>
       <v>1</v>
-      <v>10</v>
+      <v>9</v>
     </spb>
     <spb s="9">
       <v>from previous close</v>
@@ -13212,7 +13202,6 @@
     <k n="Volume" t="i"/>
     <k n="Employees" t="i"/>
     <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
     <k n="52 week low" t="i"/>
     <k n="52 week high" t="i"/>
     <k n="Previous close" t="i"/>
@@ -13310,9 +13299,6 @@
       <rpv i="0">#,##0</rpv>
     </rSty>
     <rSty dxfid="3"/>
-    <rSty dxfid="1">
-      <rpv i="0">_([$$-en-US]* #,##0_);_([$$-en-US]* (#,##0);_([$$-en-US]* "-"_);_(@_)</rpv>
-    </rSty>
     <rSty dxfid="2"/>
     <rSty dxfid="6">
       <rpv i="0">0</rpv>
@@ -13843,7 +13829,7 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>340.3</v>
+        <v>341.12400000000002</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
@@ -13894,7 +13880,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-3.37</v>
+        <v>-2.5459999999999998</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
@@ -13942,7 +13928,7 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-9.8060000000000005E-3</v>
+        <v>-7.4080000000000005E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
@@ -13997,7 +13983,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2645</v>
+        <v>2.2770999999999999</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -14170,7 +14156,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14185,7 +14171,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18800,12 +18786,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18813,6 +18793,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19873,16 +19859,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20032,7 +20018,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20041,7 +20027,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.2645</v>
+        <v>2.2770999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20111,7 +20097,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1514325</v>
+        <v>0.1523495</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20120,7 +20106,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15072434225701747</v>
+        <v>0.15163609611438572</v>
       </c>
     </row>
   </sheetData>
@@ -21980,17 +21966,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22963,10 +22949,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="267" t="s">
+      <c r="B14" s="266" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="268"/>
+      <c r="C14" s="267"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22993,20 +22979,20 @@
       <c r="C17" s="156">
         <v>0.3</v>
       </c>
-      <c r="E17" s="266" t="s">
+      <c r="E17" s="268" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="266"/>
-      <c r="G17" s="266"/>
-      <c r="H17" s="266"/>
-      <c r="I17" s="266"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="268"/>
+      <c r="H17" s="268"/>
+      <c r="I17" s="268"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="267" t="s">
+      <c r="B19" s="266" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="268"/>
+      <c r="C19" s="267"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -23072,10 +23058,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="267" t="s">
+      <c r="B28" s="266" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="268"/>
+      <c r="C28" s="267"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23151,16 +23137,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -36546,14 +36532,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="257" t="s">
+      <c r="C3" s="255" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="F3" s="259" t="s">
+      <c r="D3" s="256"/>
+      <c r="F3" s="257" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="258"/>
+      <c r="G3" s="256"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36620,19 +36606,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="255">
+      <c r="C7" s="258">
         <f>Statement!AA88</f>
         <v>0.16920202828929812</v>
       </c>
-      <c r="D7" s="256"/>
-      <c r="F7" s="255">
+      <c r="D7" s="259"/>
+      <c r="F7" s="258">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.55464868701206527</v>
       </c>
-      <c r="G7" s="256"/>
+      <c r="G7" s="259"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36659,19 +36645,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="255">
+      <c r="C9" s="258">
         <f>Statement!AA89</f>
         <v>7.4461896451425244E-2</v>
       </c>
-      <c r="D9" s="256"/>
-      <c r="F9" s="255">
+      <c r="D9" s="259"/>
+      <c r="F9" s="258">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.16090509113764928</v>
       </c>
-      <c r="G9" s="256"/>
+      <c r="G9" s="259"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36698,19 +36684,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="255">
+      <c r="C11" s="258">
         <f>Statement!AA90</f>
         <v>0.2495069033530572</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="F11" s="255">
+      <c r="D11" s="259"/>
+      <c r="F11" s="258">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0651996740016301</v>
       </c>
-      <c r="G11" s="256"/>
+      <c r="G11" s="259"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36737,19 +36723,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="255">
+      <c r="C13" s="258">
         <f>Statement!AA93</f>
         <v>4.9462365591397849E-2</v>
       </c>
-      <c r="D13" s="256"/>
-      <c r="F13" s="255">
+      <c r="D13" s="259"/>
+      <c r="F13" s="258">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.12183908045977011</v>
       </c>
-      <c r="G13" s="256"/>
+      <c r="G13" s="259"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36776,19 +36762,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="255">
+      <c r="C15" s="258">
         <f>Statement!AA94</f>
         <v>0.30902111324376197</v>
       </c>
-      <c r="D15" s="256"/>
-      <c r="F15" s="255">
+      <c r="D15" s="259"/>
+      <c r="F15" s="258">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5833333333333333</v>
       </c>
-      <c r="G15" s="256"/>
+      <c r="G15" s="259"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36815,19 +36801,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="255">
+      <c r="C17" s="258">
         <f>Statement!AA96</f>
         <v>0.18049104180491041</v>
       </c>
-      <c r="D17" s="256"/>
-      <c r="F17" s="255">
+      <c r="D17" s="259"/>
+      <c r="F17" s="258">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1155866900175133</v>
       </c>
-      <c r="G17" s="256"/>
+      <c r="G17" s="259"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36854,22 +36840,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="255">
+      <c r="C19" s="258">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.2853470437017995E-2</v>
       </c>
-      <c r="D19" s="256"/>
-      <c r="F19" s="255">
+      <c r="D19" s="259"/>
+      <c r="F19" s="258">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.1276595744680851E-2</v>
       </c>
-      <c r="G19" s="256"/>
+      <c r="G19" s="259"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36896,22 +36882,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="255">
+      <c r="C21" s="258">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.19513603185136022</v>
       </c>
-      <c r="D21" s="256"/>
-      <c r="F21" s="255">
+      <c r="D21" s="259"/>
+      <c r="F21" s="258">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.0488266199649741</v>
       </c>
-      <c r="G21" s="256"/>
+      <c r="G21" s="259"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36960,22 +36946,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="255">
+      <c r="C25" s="258">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.15600599700149931</v>
       </c>
-      <c r="D25" s="256"/>
-      <c r="F25" s="255">
+      <c r="D25" s="259"/>
+      <c r="F25" s="258">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.53596812749003997</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="259"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37003,22 +36989,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="255">
+      <c r="C27" s="258">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.36297777777777784</v>
       </c>
-      <c r="D27" s="256"/>
-      <c r="F27" s="255">
+      <c r="D27" s="259"/>
+      <c r="F27" s="258">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1004794520547947</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="259"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37046,49 +37032,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="255">
+      <c r="C29" s="258">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.17139037433155085</v>
       </c>
-      <c r="D29" s="256"/>
-      <c r="F29" s="255">
+      <c r="D29" s="259"/>
+      <c r="F29" s="258">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.35216049382716058</v>
       </c>
-      <c r="G29" s="256"/>
+      <c r="G29" s="259"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C06DEA9-635E-7B4D-81C3-511B90A38444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8826C12D-18BC-AE40-BF69-97882E8C711A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="5" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -187,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="452">
   <si>
     <t>Ticker</t>
   </si>
@@ -1531,6 +1531,18 @@
   </si>
   <si>
     <t>Q1 diluted avg shares will be 380M</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2498,6 +2510,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2505,12 +2523,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2531,14 +2543,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12822,12 +12834,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>121.715</v>
+    <v>121.85</v>
     <v>2.2770999999999999</v>
-    <v>-10.52</v>
-    <v>-2.9702000000000003E-2</v>
-    <v>-2.5459999999999998</v>
-    <v>-7.4080000000000005E-3</v>
+    <v>12.46</v>
+    <v>3.6255999999999997E-2</v>
+    <v>0.27</v>
+    <v>7.582E-4</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12835,25 +12847,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>360.66</v>
+    <v>364.13</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46318.999974375001</v>
+    <v>46321.959045601565</v>
     <v>4</v>
-    <v>339.55</v>
+    <v>340.3</v>
+    <v>133038771840</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>346.1</v>
-    <v>13.7073</v>
-    <v>354.19</v>
+    <v>346.28</v>
+    <v>13.782299999999999</v>
     <v>343.67</v>
-    <v>341.12400000000002</v>
+    <v>356.13</v>
+    <v>356.4</v>
     <v>373568000</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>13953729</v>
-    <v>9268205</v>
+    <v>9702708</v>
+    <v>9285597</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12948,6 +12961,7 @@
     <k n="Last trade time"/>
     <k n="LearnMoreOnLink" t="r"/>
     <k n="Low"/>
+    <k n="Market cap"/>
     <k n="Name" t="s"/>
     <k n="Official name" t="s"/>
     <k n="Open"/>
@@ -12999,7 +13013,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13029,6 +13043,7 @@
       <v t="s">52 week low</v>
       <v t="s">Volume</v>
       <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
       <v t="s">Beta</v>
       <v t="s">P/E</v>
       <v t="s">Shares outstanding</v>
@@ -13110,13 +13125,14 @@
       <v>5</v>
       <v>5</v>
       <v>6</v>
+      <v>7</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
       <v>5</v>
-      <v>7</v>
       <v>8</v>
       <v>9</v>
+      <v>10</v>
       <v>5</v>
       <v>1</v>
       <v>1</v>
@@ -13126,9 +13142,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13156,7 +13172,7 @@
       <v>1</v>
       <v>1</v>
       <v>1</v>
-      <v>9</v>
+      <v>10</v>
     </spb>
     <spb s="9">
       <v>from previous close</v>
@@ -13202,6 +13218,7 @@
     <k n="Volume" t="i"/>
     <k n="Employees" t="i"/>
     <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
     <k n="52 week low" t="i"/>
     <k n="52 week high" t="i"/>
     <k n="Previous close" t="i"/>
@@ -13299,6 +13316,9 @@
       <rpv i="0">#,##0</rpv>
     </rSty>
     <rSty dxfid="3"/>
+    <rSty dxfid="1">
+      <rpv i="0">_([$$-en-US]* #,##0_);_([$$-en-US]* (#,##0);_([$$-en-US]* "-"_);_(@_)</rpv>
+    </rSty>
     <rSty dxfid="2"/>
     <rSty dxfid="6">
       <rpv i="0">0</rpv>
@@ -13755,7 +13775,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>137124.33000000002</v>
+        <v>142095.87</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13782,7 +13802,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>136599.33000000002</v>
+        <v>141570.87</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13802,7 +13822,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13829,14 +13849,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>341.12400000000002</v>
+        <v>356.4</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>26.29659672902098</v>
+        <v>27.249998525056714</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13856,14 +13876,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-10.52</v>
+        <v>12.46</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>9.1423054481425226</v>
+        <v>9.4737662270404641</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13880,14 +13900,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-2.5459999999999998</v>
+        <v>0.27</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.9600873893057485E-2</v>
+        <v>2.856522149447412E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13904,14 +13924,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.9702000000000003E-2</v>
+        <v>3.6255999999999997E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>3.802773455077546E-2</v>
+        <v>3.6697249692710536E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13919,7 +13939,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.40722848901714304</v>
+        <v>-0.42796791851436705</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13928,14 +13948,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-7.4080000000000005E-3</v>
+        <v>7.582E-4</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.2169661649395111E-2</v>
+        <v>2.1394006736437873E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13951,7 +13971,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.6003724503157099E-3</v>
+        <v>1.5443798612866089E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>359</v>
@@ -13967,7 +13987,7 @@
       </c>
       <c r="C12" s="205" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>121.715</v>
+        <v>121.85</v>
       </c>
       <c r="E12" s="181" t="s">
         <v>101</v>
@@ -14006,7 +14026,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>9268205</v>
+        <v>9285597</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -14029,7 +14049,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>3.8286422256356692E-3</v>
+        <v>3.6946886633650931E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -18786,6 +18806,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18793,12 +18819,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19859,16 +19879,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19991,7 +20011,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20000,7 +20020,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>137124.33000000002</v>
+        <v>142095.87</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20070,7 +20090,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.720984331246297E-3</v>
+        <v>5.521928248946162E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20079,7 +20099,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99427901566875365</v>
+        <v>0.99447807175105385</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20106,7 +20126,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15163609611438572</v>
+        <v>0.15166091830832054</v>
       </c>
     </row>
   </sheetData>
@@ -21966,17 +21986,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22081,7 +22101,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22090,7 +22110,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.40722848901714304</v>
+        <v>-0.42796791851436705</v>
       </c>
     </row>
   </sheetData>
@@ -22949,10 +22969,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="267" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="267"/>
+      <c r="C14" s="268"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22960,7 +22980,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22979,20 +22999,20 @@
       <c r="C17" s="156">
         <v>0.3</v>
       </c>
-      <c r="E17" s="268" t="s">
+      <c r="E17" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="268"/>
-      <c r="G17" s="268"/>
-      <c r="H17" s="268"/>
-      <c r="I17" s="268"/>
+      <c r="F17" s="266"/>
+      <c r="G17" s="266"/>
+      <c r="H17" s="266"/>
+      <c r="I17" s="266"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="266" t="s">
+      <c r="B19" s="267" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="267"/>
+      <c r="C19" s="268"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -23026,7 +23046,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>124064.87000000001</v>
+        <v>128562.93</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23053,15 +23073,15 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>123539.87000000001</v>
+        <v>128037.93</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="266" t="s">
+      <c r="B28" s="267" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="267"/>
+      <c r="C28" s="268"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23137,16 +23157,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29874,7 +29894,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29948,7 +29968,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31317,7 +31337,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>26.29659672902098</v>
+        <v>27.249998525056714</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31358,7 +31378,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>9.1423054481425226</v>
+        <v>9.4737662270404641</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31423,7 +31443,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>13.271808943089431</v>
+        <v>13.752987804878048</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31488,7 +31508,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>137124.33000000002</v>
+        <v>142095.87</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31553,7 +31573,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>136599.33000000002</v>
+        <v>141570.87</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31594,7 +31614,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>9.4323525756111053</v>
+        <v>9.775643557519679</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31635,7 +31655,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>23.935400385491505</v>
+        <v>24.806530576485017</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31782,7 +31802,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="199">AC151/AC155</f>
-        <v>33.782786400591284</v>
+        <v>35.007605321507761</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31823,7 +31843,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="199"/>
-        <v>33.790157415681229</v>
+        <v>35.019952021543169</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31864,7 +31884,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="204">AC155/AC151</f>
-        <v>2.9600873893057485E-2</v>
+        <v>2.856522149447412E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31905,7 +31925,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.802773455077546E-2</v>
+        <v>3.6697249692710536E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31946,7 +31966,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.6003724503157099E-3</v>
+        <v>1.5443798612866089E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31987,7 +32007,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.2169661649395111E-2</v>
+        <v>2.1394006736437873E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32028,7 +32048,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.3635484672924197E-2</v>
+        <v>2.2808544681840508E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32575,7 +32595,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>3.8286422256356692E-3</v>
+        <v>3.6946886633650931E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -34039,7 +34059,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -34072,7 +34092,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34088,7 +34108,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>137124.33000000002</v>
+        <v>142095.87</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34108,7 +34128,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>136599.33000000002</v>
+        <v>141570.87</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -34128,7 +34148,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>26.29659672902098</v>
+        <v>27.249998525056714</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -34148,7 +34168,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>9.1423054481425226</v>
+        <v>9.4737662270404641</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -34168,7 +34188,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>13.271808943089431</v>
+        <v>13.752987804878048</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34188,7 +34208,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>9.4323525756111053</v>
+        <v>9.775643557519679</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34197,7 +34217,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>23.935400385491505</v>
+        <v>24.806530576485017</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34433,7 +34453,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>3.802773455077546E-2</v>
+        <v>3.6697249692710536E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34449,7 +34469,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.9600873893057485E-2</v>
+        <v>2.856522149447412E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34465,7 +34485,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.6003724503157099E-3</v>
+        <v>1.5443798612866089E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34481,7 +34501,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.2169661649395111E-2</v>
+        <v>2.1394006736437873E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34490,7 +34510,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.3635484672924197E-2</v>
+        <v>2.2808544681840508E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34534,7 +34554,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>3.8286422256356692E-3</v>
+        <v>3.6946886633650931E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34588,8 +34608,51 @@
         <v>1.462915601023018</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="254" t="s">
+        <v>448</v>
+      </c>
+      <c r="C57" s="254"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58" s="170">
+        <f ca="1">Statement!AC157</f>
+        <v>35.007605321507761</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C59" s="170">
+        <f ca="1">Statement!AC158</f>
+        <v>35.019952021543169</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="C60" s="171">
+        <f>Statement!AC164</f>
+        <v>0.27914497288591406</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="C61" s="171">
+        <f>Statement!AC165</f>
+        <v>0.28027896699350918</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -34615,7 +34678,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="B1:I94"/>
+  <dimension ref="B1:I100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -34714,7 +34777,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>343.67</v>
+        <v>356.13</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34743,7 +34806,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>137124.33000000002</v>
+        <v>142095.87</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34772,7 +34835,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>136599.33000000002</v>
+        <v>141570.87</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34801,7 +34864,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>26.29659672902098</v>
+        <v>27.249998525056714</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34830,7 +34893,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>9.1423054481425226</v>
+        <v>9.4737662270404641</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34859,7 +34922,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>13.271808943089431</v>
+        <v>13.752987804878048</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34888,7 +34951,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>9.4323525756111053</v>
+        <v>9.775643557519679</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34917,7 +34980,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>23.935400385491505</v>
+        <v>24.806530576485017</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35690,7 +35753,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>3.802773455077546E-2</v>
+        <v>3.6697249692710536E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35719,7 +35782,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.9600873893057485E-2</v>
+        <v>2.856522149447412E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35748,7 +35811,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.6003724503157099E-3</v>
+        <v>1.5443798612866089E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35777,7 +35840,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.2169661649395111E-2</v>
+        <v>2.1394006736437873E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35806,7 +35869,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.3635484672924197E-2</v>
+        <v>2.2808544681840508E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36042,7 +36105,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>3.8286422256356692E-3</v>
+        <v>3.6946886633650931E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36379,101 +36442,136 @@
       </c>
       <c r="I85" s="193"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C88" s="170">
+        <f>Statement!M157</f>
+        <v>27.199305555555561</v>
+      </c>
+      <c r="D88" s="170">
+        <f>Statement!N157</f>
+        <v>-8.1301357466063351</v>
+      </c>
+      <c r="E88" s="170">
+        <f>Statement!O157</f>
+        <v>-24.15344795539033</v>
+      </c>
+      <c r="F88" s="170">
+        <f>Statement!P157</f>
+        <v>22.472692307692306</v>
+      </c>
+      <c r="G88" s="170">
+        <f>Statement!Q157</f>
+        <v>65.032053220441483</v>
+      </c>
+      <c r="I88" s="170">
+        <f ca="1">Statement!AC157</f>
+        <v>35.007605321507761</v>
+      </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
-        <f>Statement!B191</f>
-        <v>Cloud</v>
-      </c>
-      <c r="C89" s="171">
-        <f>Statement!M191</f>
-        <v>0.4008387209505504</v>
-      </c>
-      <c r="D89" s="171">
-        <f>Statement!N191</f>
-        <v>-0.40713483846825493</v>
-      </c>
-      <c r="E89" s="171">
-        <f>Statement!O191</f>
-        <v>6.2907637281716805E-2</v>
-      </c>
-      <c r="F89" s="171">
-        <f>Statement!P191</f>
-        <v>0.65102929532858278</v>
-      </c>
-      <c r="G89" s="171">
-        <f>Statement!Q191</f>
-        <v>0.37753266994365187</v>
-      </c>
-      <c r="I89" s="193"/>
+      <c r="B89" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" s="170">
+        <f>Statement!M158</f>
+        <v>38.981647804001206</v>
+      </c>
+      <c r="D89" s="170">
+        <f>Statement!N158</f>
+        <v>-41.203385300668153</v>
+      </c>
+      <c r="E89" s="170">
+        <f>Statement!O158</f>
+        <v>-50.513688394276627</v>
+      </c>
+      <c r="F89" s="170">
+        <f>Statement!P158</f>
+        <v>19.085923994038748</v>
+      </c>
+      <c r="G89" s="170">
+        <f>Statement!Q158</f>
+        <v>65.898902717022324</v>
+      </c>
+      <c r="I89" s="170">
+        <f ca="1">Statement!AC158</f>
+        <v>35.019952021543169</v>
+      </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
-        <f>Statement!B192</f>
-        <v>Client</v>
+      <c r="B90" s="20" t="s">
+        <v>449</v>
       </c>
       <c r="C90" s="171">
-        <f>Statement!M192</f>
-        <v>-2.8155473149292679E-2</v>
+        <f>Statement!M164</f>
+        <v>2.2420831520460437E-2</v>
       </c>
       <c r="D90" s="171">
-        <f>Statement!N192</f>
-        <v>-0.90234595816845675</v>
+        <f>Statement!N164</f>
+        <v>-7.1782573940847319E-2</v>
       </c>
       <c r="E90" s="171">
-        <f>Statement!O192</f>
-        <v>-0.16497829232995659</v>
+        <f>Statement!O164</f>
+        <v>-9.9572581921798325E-2</v>
       </c>
       <c r="F90" s="171">
-        <f>Statement!P192</f>
-        <v>-3.6395147313691506E-2</v>
+        <f>Statement!P164</f>
+        <v>0.14096638655462185</v>
       </c>
       <c r="G90" s="171">
-        <f>Statement!Q192</f>
-        <v>0.30575539568345322</v>
-      </c>
-      <c r="I90" s="193"/>
+        <f>Statement!Q164</f>
+        <v>0.25199333186991602</v>
+      </c>
+      <c r="I90" s="171">
+        <f>Statement!AC164</f>
+        <v>0.27914497288591406</v>
+      </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="str">
-        <f>Statement!B193</f>
-        <v>Consumer</v>
+      <c r="B91" s="20" t="s">
+        <v>450</v>
       </c>
       <c r="C91" s="171">
-        <f>Statement!M193</f>
-        <v>-5.5640632976008166E-2</v>
+        <f>Statement!M165</f>
+        <v>2.2987282498802747E-2</v>
       </c>
       <c r="D91" s="171">
-        <f>Statement!N193</f>
-        <v>-0.78081081081081083</v>
+        <f>Statement!N165</f>
+        <v>-0.24732214228617105</v>
       </c>
       <c r="E91" s="171">
-        <f>Statement!O193</f>
-        <v>-0.15166461159062886</v>
+        <f>Statement!O165</f>
+        <v>-0.17033401931296502</v>
       </c>
       <c r="F91" s="171">
-        <f>Statement!P193</f>
-        <v>-9.4476744186046513E-2</v>
+        <f>Statement!P165</f>
+        <v>0.1065126050420168</v>
       </c>
       <c r="G91" s="171">
-        <f>Statement!Q193</f>
-        <v>0.12841091492776885</v>
-      </c>
-      <c r="I91" s="193"/>
+        <f>Statement!Q165</f>
+        <v>0.25597956498180974</v>
+      </c>
+      <c r="I91" s="171">
+        <f>Statement!AC165</f>
+        <v>0.28027896699350918</v>
+      </c>
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>311</v>
+        <v>451</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -36507,6 +36605,98 @@
         <v>3.1818181818181817</v>
       </c>
       <c r="I94" s="193"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
+        <f>Statement!B191</f>
+        <v>Cloud</v>
+      </c>
+      <c r="C98" s="171">
+        <f>Statement!M191</f>
+        <v>0.4008387209505504</v>
+      </c>
+      <c r="D98" s="171">
+        <f>Statement!N191</f>
+        <v>-0.40713483846825493</v>
+      </c>
+      <c r="E98" s="171">
+        <f>Statement!O191</f>
+        <v>6.2907637281716805E-2</v>
+      </c>
+      <c r="F98" s="171">
+        <f>Statement!P191</f>
+        <v>0.65102929532858278</v>
+      </c>
+      <c r="G98" s="171">
+        <f>Statement!Q191</f>
+        <v>0.37753266994365187</v>
+      </c>
+      <c r="I98" s="193"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
+        <f>Statement!B192</f>
+        <v>Client</v>
+      </c>
+      <c r="C99" s="171">
+        <f>Statement!M192</f>
+        <v>-2.8155473149292679E-2</v>
+      </c>
+      <c r="D99" s="171">
+        <f>Statement!N192</f>
+        <v>-0.90234595816845675</v>
+      </c>
+      <c r="E99" s="171">
+        <f>Statement!O192</f>
+        <v>-0.16497829232995659</v>
+      </c>
+      <c r="F99" s="171">
+        <f>Statement!P192</f>
+        <v>-3.6395147313691506E-2</v>
+      </c>
+      <c r="G99" s="171">
+        <f>Statement!Q192</f>
+        <v>0.30575539568345322</v>
+      </c>
+      <c r="I99" s="193"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="str">
+        <f>Statement!B193</f>
+        <v>Consumer</v>
+      </c>
+      <c r="C100" s="171">
+        <f>Statement!M193</f>
+        <v>-5.5640632976008166E-2</v>
+      </c>
+      <c r="D100" s="171">
+        <f>Statement!N193</f>
+        <v>-0.78081081081081083</v>
+      </c>
+      <c r="E100" s="171">
+        <f>Statement!O193</f>
+        <v>-0.15166461159062886</v>
+      </c>
+      <c r="F100" s="171">
+        <f>Statement!P193</f>
+        <v>-9.4476744186046513E-2</v>
+      </c>
+      <c r="G100" s="171">
+        <f>Statement!Q193</f>
+        <v>0.12841091492776885</v>
+      </c>
+      <c r="I100" s="193"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36532,14 +36722,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="255" t="s">
+      <c r="C3" s="257" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="256"/>
-      <c r="F3" s="257" t="s">
+      <c r="D3" s="258"/>
+      <c r="F3" s="259" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="256"/>
+      <c r="G3" s="258"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36606,19 +36796,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="258">
+      <c r="C7" s="255">
         <f>Statement!AA88</f>
         <v>0.16920202828929812</v>
       </c>
-      <c r="D7" s="259"/>
-      <c r="F7" s="258">
+      <c r="D7" s="256"/>
+      <c r="F7" s="255">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.55464868701206527</v>
       </c>
-      <c r="G7" s="259"/>
+      <c r="G7" s="256"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36645,19 +36835,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="258">
+      <c r="C9" s="255">
         <f>Statement!AA89</f>
         <v>7.4461896451425244E-2</v>
       </c>
-      <c r="D9" s="259"/>
-      <c r="F9" s="258">
+      <c r="D9" s="256"/>
+      <c r="F9" s="255">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.16090509113764928</v>
       </c>
-      <c r="G9" s="259"/>
+      <c r="G9" s="256"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36684,19 +36874,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="258">
+      <c r="C11" s="255">
         <f>Statement!AA90</f>
         <v>0.2495069033530572</v>
       </c>
-      <c r="D11" s="259"/>
-      <c r="F11" s="258">
+      <c r="D11" s="256"/>
+      <c r="F11" s="255">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0651996740016301</v>
       </c>
-      <c r="G11" s="259"/>
+      <c r="G11" s="256"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36723,19 +36913,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="258">
+      <c r="C13" s="255">
         <f>Statement!AA93</f>
         <v>4.9462365591397849E-2</v>
       </c>
-      <c r="D13" s="259"/>
-      <c r="F13" s="258">
+      <c r="D13" s="256"/>
+      <c r="F13" s="255">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.12183908045977011</v>
       </c>
-      <c r="G13" s="259"/>
+      <c r="G13" s="256"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36762,19 +36952,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="258">
+      <c r="C15" s="255">
         <f>Statement!AA94</f>
         <v>0.30902111324376197</v>
       </c>
-      <c r="D15" s="259"/>
-      <c r="F15" s="258">
+      <c r="D15" s="256"/>
+      <c r="F15" s="255">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5833333333333333</v>
       </c>
-      <c r="G15" s="259"/>
+      <c r="G15" s="256"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36801,19 +36991,19 @@
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="258">
+      <c r="C17" s="255">
         <f>Statement!AA96</f>
         <v>0.18049104180491041</v>
       </c>
-      <c r="D17" s="259"/>
-      <c r="F17" s="258">
+      <c r="D17" s="256"/>
+      <c r="F17" s="255">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>2.1155866900175133</v>
       </c>
-      <c r="G17" s="259"/>
+      <c r="G17" s="256"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -36840,22 +37030,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="258">
+      <c r="C19" s="255">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.2853470437017995E-2</v>
       </c>
-      <c r="D19" s="259"/>
-      <c r="F19" s="258">
+      <c r="D19" s="256"/>
+      <c r="F19" s="255">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.1276595744680851E-2</v>
       </c>
-      <c r="G19" s="259"/>
+      <c r="G19" s="256"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -36882,22 +37072,22 @@
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="258">
+      <c r="C21" s="255">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>0.19513603185136022</v>
       </c>
-      <c r="D21" s="259"/>
-      <c r="F21" s="258">
+      <c r="D21" s="256"/>
+      <c r="F21" s="255">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>2.0488266199649741</v>
       </c>
-      <c r="G21" s="259"/>
+      <c r="G21" s="256"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36946,22 +37136,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="258">
+      <c r="C25" s="255">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.15600599700149931</v>
       </c>
-      <c r="D25" s="259"/>
-      <c r="F25" s="258">
+      <c r="D25" s="256"/>
+      <c r="F25" s="255">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.53596812749003997</v>
       </c>
-      <c r="G25" s="259"/>
+      <c r="G25" s="256"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -36989,22 +37179,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="258">
+      <c r="C27" s="255">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.36297777777777784</v>
       </c>
-      <c r="D27" s="259"/>
-      <c r="F27" s="258">
+      <c r="D27" s="256"/>
+      <c r="F27" s="255">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1004794520547947</v>
       </c>
-      <c r="G27" s="259"/>
+      <c r="G27" s="256"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37032,49 +37222,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="258">
+      <c r="C29" s="255">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.17139037433155085</v>
       </c>
-      <c r="D29" s="259"/>
-      <c r="F29" s="258">
+      <c r="D29" s="256"/>
+      <c r="F29" s="255">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.35216049382716058</v>
       </c>
-      <c r="G29" s="259"/>
+      <c r="G29" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8826C12D-18BC-AE40-BF69-97882E8C711A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41AC76B-D179-A445-A00F-62AAE057C09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="5" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -12835,11 +12835,11 @@
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
     <v>121.85</v>
-    <v>2.2770999999999999</v>
-    <v>12.46</v>
-    <v>3.6255999999999997E-2</v>
-    <v>0.27</v>
-    <v>7.582E-4</v>
+    <v>2.2606999999999999</v>
+    <v>24.75</v>
+    <v>6.9497000000000003E-2</v>
+    <v>-3.28</v>
+    <v>-8.6119999999999999E-3</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12847,26 +12847,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>364.13</v>
+    <v>388.08</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46321.959045601565</v>
+    <v>46322.995692441407</v>
     <v>4</v>
-    <v>340.3</v>
-    <v>133038771840</v>
+    <v>358.24</v>
+    <v>142572258504</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>346.28</v>
-    <v>13.782299999999999</v>
-    <v>343.67</v>
+    <v>359.95</v>
+    <v>14.7402</v>
     <v>356.13</v>
-    <v>356.4</v>
-    <v>373568000</v>
+    <v>380.88</v>
+    <v>377.6</v>
+    <v>374323300</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>9702708</v>
-    <v>9285597</v>
+    <v>9152731</v>
+    <v>9368632</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12890,17 +12890,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>7.0000000000000007E-2</v>
+    <v>1.4039999999999999E-3</v>
     <v>US</v>
-    <v>50.03</v>
+    <v>50.07</v>
     <v>Index</v>
     <v>7</v>
-    <v>49.55</v>
+    <v>49.72</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
-    <v>49.88</v>
+    <v>49.76</v>
+    <v>49.86</v>
+    <v>49.93</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="F3" s="183">
         <f ca="1">Statement!AC151</f>
-        <v>142095.87</v>
+        <v>151971.12</v>
       </c>
       <c r="H3" s="181" t="str">
         <f>'AVG target price'!B5</f>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="F4" s="184">
         <f ca="1">Statement!AC152</f>
-        <v>141570.87</v>
+        <v>151446.12</v>
       </c>
       <c r="H4" s="181" t="str">
         <f>'AVG target price'!B6</f>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="C5" s="204" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
       <c r="E5" s="181" t="s">
         <v>242</v>
@@ -13849,14 +13849,14 @@
       </c>
       <c r="C6" s="204" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>356.4</v>
+        <v>377.6</v>
       </c>
       <c r="E6" s="181" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>27.249998525056714</v>
+        <v>29.143794227455146</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13876,14 +13876,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>12.46</v>
+        <v>24.75</v>
       </c>
       <c r="E7" s="182" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="187">
         <f ca="1">Statement!AC149</f>
-        <v>9.4737662270404641</v>
+        <v>10.132165446761498</v>
       </c>
       <c r="H7" s="181" t="str">
         <f>'AVG target price'!B9</f>
@@ -13900,14 +13900,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.27</v>
+        <v>-3.28</v>
       </c>
       <c r="E8" s="181" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="188">
         <f ca="1">Statement!AC159</f>
-        <v>2.856522149447412E-2</v>
+        <v>2.6709022082616749E-2</v>
       </c>
       <c r="H8" s="180" t="str">
         <f>'AVG target price'!B10</f>
@@ -13924,14 +13924,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.6255999999999997E-2</v>
+        <v>6.9497000000000003E-2</v>
       </c>
       <c r="E9" s="181" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>3.6697249692710536E-2</v>
+        <v>3.4312622172508411E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.42796791851436705</v>
+        <v>-0.46513919035003554</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13948,14 +13948,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>7.582E-4</v>
+        <v>-8.6119999999999999E-3</v>
       </c>
       <c r="E10" s="181" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="188">
         <f ca="1">Statement!AC162</f>
-        <v>2.1394006736437873E-2</v>
+        <v>2.0003800722137206E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F11" s="189">
         <f ca="1">Statement!AC161</f>
-        <v>1.5443798612866089E-3</v>
+        <v>1.4440243646292796E-3</v>
       </c>
       <c r="H11" s="180" t="s">
         <v>359</v>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="C13" s="205" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2770999999999999</v>
+        <v>2.2606999999999999</v>
       </c>
       <c r="E13" s="181" t="s">
         <v>103</v>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="I13" s="244">
         <f>'Reverse DCF'!C17</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="C14" s="206" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>9285597</v>
+        <v>9368632</v>
       </c>
       <c r="E14" s="182" t="s">
         <v>104</v>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="I14" s="245">
         <f>'Reverse DCF'!C16</f>
-        <v>343.05356307563164</v>
+        <v>381.16577148628357</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F15" s="188">
         <f ca="1">Statement!AC174</f>
-        <v>3.6946886633650931E-3</v>
+        <v>3.4546037431322477E-3</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="F26" s="215" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="F27" s="216">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9930000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>142095.87</v>
+        <v>151971.12</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9930000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20047,7 +20047,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.2770999999999999</v>
+        <v>2.2606999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>5.521928248946162E-3</v>
+        <v>5.1649605931181515E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99447807175105385</v>
+        <v>0.99483503940688189</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1523495</v>
+        <v>0.1516615</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.15166091830832054</v>
+        <v>0.15102098548940654</v>
       </c>
     </row>
   </sheetData>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="C11" s="133">
         <f ca="1">Overview!C5</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22110,7 +22110,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.42796791851436705</v>
+        <v>-0.46513919035003554</v>
       </c>
     </row>
   </sheetData>
@@ -22827,23 +22827,23 @@
       </c>
       <c r="H7" s="126">
         <f>G7*(1+$C$17)</f>
-        <v>4232.1524107556788</v>
+        <v>4329.8174663885029</v>
       </c>
       <c r="I7" s="126">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>5501.7981339823828</v>
+        <v>5758.6572302967088</v>
       </c>
       <c r="J7" s="126">
         <f t="shared" si="0"/>
-        <v>7152.3375741770978</v>
+        <v>7659.0141162946229</v>
       </c>
       <c r="K7" s="126">
         <f t="shared" si="0"/>
-        <v>9298.0388464302268</v>
+        <v>10186.488774671849</v>
       </c>
       <c r="L7" s="126">
         <f t="shared" si="0"/>
-        <v>12087.450500359295</v>
+        <v>13548.03007031356</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -22875,7 +22875,7 @@
       <c r="K8" s="137"/>
       <c r="L8" s="126">
         <f>L7*(1+C20)/(C21-C20)</f>
-        <v>154114.99387958102</v>
+        <v>172737.3833964979</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -22929,23 +22929,23 @@
       <c r="G10" s="138"/>
       <c r="H10" s="126">
         <f>H7/(1+$C$21)^H9</f>
-        <v>3847.411282505162</v>
+        <v>3936.1976967168207</v>
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" si="1">I7/(1+$C$21)^I9</f>
-        <v>4546.9406065970097</v>
+        <v>4759.2208514848826</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" si="1"/>
-        <v>5373.6570805237379</v>
+        <v>5754.3306658862666</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" si="1"/>
-        <v>6350.6856406189636</v>
+        <v>6957.5088960261228</v>
       </c>
       <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>7505.355757095138</v>
+        <v>8412.2607561043114</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -22964,7 +22964,7 @@
       <c r="K11" s="137"/>
       <c r="L11" s="126">
         <f>L8/(1+C21)^L9</f>
-        <v>95693.28590296302</v>
+        <v>107256.32464032999</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22980,7 +22980,7 @@
       </c>
       <c r="C15" s="154">
         <f ca="1">Overview!C5</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22989,7 +22989,7 @@
       </c>
       <c r="C16" s="154">
         <f>C36</f>
-        <v>343.05356307563164</v>
+        <v>381.16577148628357</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22997,7 +22997,7 @@
         <v>323</v>
       </c>
       <c r="C17" s="156">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="E17" s="266" t="s">
         <v>224</v>
@@ -23046,7 +23046,7 @@
       </c>
       <c r="C23" s="159">
         <f ca="1">C15*C22</f>
-        <v>128562.93</v>
+        <v>137497.68</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -23073,7 +23073,7 @@
       </c>
       <c r="C26" s="160">
         <f ca="1">C23+C25-C24</f>
-        <v>128037.93</v>
+        <v>136972.68</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="C29" s="159">
         <f>SUM(H10:L10)</f>
-        <v>27624.050367340009</v>
+        <v>29819.518866218405</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="C30" s="159">
         <f>L11</f>
-        <v>95693.28590296302</v>
+        <v>107256.32464032999</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="C31" s="162">
         <f>C29+C30</f>
-        <v>123317.33627030303</v>
+        <v>137075.84350654838</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23134,7 +23134,7 @@
       </c>
       <c r="C34" s="162">
         <f>C31+C32-C33</f>
-        <v>123842.33627030303</v>
+        <v>137600.84350654838</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="C36" s="165">
         <f>C34/C35</f>
-        <v>343.05356307563164</v>
+        <v>381.16577148628357</v>
       </c>
     </row>
   </sheetData>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29968,7 +29968,7 @@
       </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -31337,7 +31337,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>27.249998525056714</v>
+        <v>29.143794227455146</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31378,7 +31378,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>9.4737662270404641</v>
+        <v>10.132165446761498</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31443,7 +31443,7 @@
       </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>13.752987804878048</v>
+        <v>14.708780487804878</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31508,7 +31508,7 @@
       </c>
       <c r="AC151" s="141">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>142095.87</v>
+        <v>151971.12</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31573,7 +31573,7 @@
       </c>
       <c r="AC152" s="141">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>141570.87</v>
+        <v>151446.12</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31614,7 +31614,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="179">
         <f ca="1">AC152/AC5</f>
-        <v>9.775643557519679</v>
+        <v>10.45754177599779</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31655,7 +31655,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="179">
         <f ca="1">AC152/AC11</f>
-        <v>24.806530576485017</v>
+        <v>26.536905554582091</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31802,7 +31802,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="199">AC151/AC155</f>
-        <v>35.007605321507761</v>
+        <v>37.44053215077605</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31843,7 +31843,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="199"/>
-        <v>35.019952021543169</v>
+        <v>37.462762334150163</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31884,7 +31884,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="204">AC155/AC151</f>
-        <v>2.856522149447412E-2</v>
+        <v>2.6709022082616749E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31925,7 +31925,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.6697249692710536E-2</v>
+        <v>3.4312622172508411E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31966,7 +31966,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="152">
         <f ca="1">AC81/AC115</f>
-        <v>1.5443798612866089E-3</v>
+        <v>1.4440243646292796E-3</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -32007,7 +32007,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="152">
         <f ca="1">-AC62/AC151</f>
-        <v>2.1394006736437873E-2</v>
+        <v>2.0003800722137206E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -32048,7 +32048,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="152">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.2808544681840508E-2</v>
+        <v>2.1326420440936411E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32595,7 +32595,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="152">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>3.6946886633650931E-3</v>
+        <v>3.4546037431322477E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -34092,7 +34092,7 @@
       </c>
       <c r="C5" s="168">
         <f ca="1">Overview!C5</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="C6" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>142095.87</v>
+        <v>151971.12</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34128,7 +34128,7 @@
       </c>
       <c r="C7" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>141570.87</v>
+        <v>151446.12</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -34148,7 +34148,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>27.249998525056714</v>
+        <v>29.143794227455146</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -34168,7 +34168,7 @@
       </c>
       <c r="C9" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>9.4737662270404641</v>
+        <v>10.132165446761498</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -34188,7 +34188,7 @@
       </c>
       <c r="C10" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>13.752987804878048</v>
+        <v>14.708780487804878</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34208,7 +34208,7 @@
       </c>
       <c r="C11" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>9.775643557519679</v>
+        <v>10.45754177599779</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34217,7 +34217,7 @@
       </c>
       <c r="C12" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>24.806530576485017</v>
+        <v>26.536905554582091</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34453,7 +34453,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>3.6697249692710536E-2</v>
+        <v>3.4312622172508411E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34469,7 +34469,7 @@
       </c>
       <c r="C39" s="211">
         <f ca="1">Statement!AC159</f>
-        <v>2.856522149447412E-2</v>
+        <v>2.6709022082616749E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -34485,7 +34485,7 @@
       </c>
       <c r="C40" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.5443798612866089E-3</v>
+        <v>1.4440243646292796E-3</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>272</v>
@@ -34501,7 +34501,7 @@
       </c>
       <c r="C41" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.1394006736437873E-2</v>
+        <v>2.0003800722137206E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -34510,7 +34510,7 @@
       </c>
       <c r="C42" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.2808544681840508E-2</v>
+        <v>2.1326420440936411E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34554,7 +34554,7 @@
       </c>
       <c r="F48" s="171">
         <f ca="1">Statement!AC174</f>
-        <v>3.6946886633650931E-3</v>
+        <v>3.4546037431322477E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34620,7 +34620,7 @@
       </c>
       <c r="C58" s="170">
         <f ca="1">Statement!AC157</f>
-        <v>35.007605321507761</v>
+        <v>37.44053215077605</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.2">
@@ -34629,7 +34629,7 @@
       </c>
       <c r="C59" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>35.019952021543169</v>
+        <v>37.462762334150163</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
@@ -34777,7 +34777,7 @@
       </c>
       <c r="I6" s="168">
         <f ca="1">Statement!AC114</f>
-        <v>356.13</v>
+        <v>380.88</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="I7" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>142095.87</v>
+        <v>151971.12</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34835,7 +34835,7 @@
       </c>
       <c r="I8" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>141570.87</v>
+        <v>151446.12</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>27.249998525056714</v>
+        <v>29.143794227455146</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34893,7 +34893,7 @@
       </c>
       <c r="I10" s="170">
         <f ca="1">Statement!AC149</f>
-        <v>9.4737662270404641</v>
+        <v>10.132165446761498</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="I11" s="170">
         <f ca="1">Statement!AC150</f>
-        <v>13.752987804878048</v>
+        <v>14.708780487804878</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34951,7 +34951,7 @@
       </c>
       <c r="I12" s="170">
         <f ca="1">Statement!AC153</f>
-        <v>9.775643557519679</v>
+        <v>10.45754177599779</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="I13" s="170">
         <f ca="1">Statement!AC154</f>
-        <v>24.806530576485017</v>
+        <v>26.536905554582091</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35753,7 +35753,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>3.6697249692710536E-2</v>
+        <v>3.4312622172508411E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35782,7 +35782,7 @@
       </c>
       <c r="I52" s="171">
         <f ca="1">Statement!AC159</f>
-        <v>2.856522149447412E-2</v>
+        <v>2.6709022082616749E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="I53" s="171">
         <f ca="1">Statement!AC161</f>
-        <v>1.5443798612866089E-3</v>
+        <v>1.4440243646292796E-3</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35840,7 +35840,7 @@
       </c>
       <c r="I54" s="171">
         <f ca="1">Statement!AC162</f>
-        <v>2.1394006736437873E-2</v>
+        <v>2.0003800722137206E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35869,7 +35869,7 @@
       </c>
       <c r="I55" s="171">
         <f ca="1">Statement!AC163</f>
-        <v>2.2808544681840508E-2</v>
+        <v>2.1326420440936411E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36105,7 +36105,7 @@
       </c>
       <c r="I68" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>3.6946886633650931E-3</v>
+        <v>3.4546037431322477E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36479,7 +36479,7 @@
       </c>
       <c r="I88" s="170">
         <f ca="1">Statement!AC157</f>
-        <v>35.007605321507761</v>
+        <v>37.44053215077605</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.2">
@@ -36508,7 +36508,7 @@
       </c>
       <c r="I89" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>35.019952021543169</v>
+        <v>37.462762334150163</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F5D77A-39A9-5740-B8BE-115C7347002B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8BCD5CD-D1A9-594F-A263-F4CB3A3D3F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1530,9 +1530,6 @@
     <t>Q2 OpEx will be 400M-410M</t>
   </si>
   <si>
-    <t>Q1 diluted avg shares will be 380M</t>
-  </si>
-  <si>
     <t>FCF ratios</t>
   </si>
   <si>
@@ -1543,6 +1540,9 @@
   </si>
   <si>
     <t>Other standard growth rates</t>
+  </si>
+  <si>
+    <t>Q2 diluted avg shares will be 380M</t>
   </si>
 </sst>
 </file>
@@ -2500,6 +2500,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2507,12 +2513,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2533,14 +2533,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5694,7 +5694,7 @@
                   <c:v>1296</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1674</c:v>
+                  <c:v>1779</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6145,7 +6145,7 @@
                   <c:v>0.34587670136108889</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.38210454234193109</c:v>
+                  <c:v>0.40607167313398768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="I3" s="207">
         <f>'AVG target price'!C5</f>
-        <v>134.78631881428217</v>
+        <v>134.26210569437919</v>
       </c>
       <c r="K3" s="242" t="s">
         <v>434</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="I4" s="207">
         <f>'AVG target price'!C6</f>
-        <v>208.05785097830486</v>
+        <v>207.5336378584019</v>
       </c>
       <c r="K4" s="242" t="s">
         <v>435</v>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="F5" s="186">
         <f>Statement!AC25</f>
-        <v>12.061052931138622</v>
+        <v>12.334490431138622</v>
       </c>
       <c r="H5" s="181" t="str">
         <f>'AVG target price'!B7</f>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="I5" s="207">
         <f>'AVG target price'!C7</f>
-        <v>194.8174579933449</v>
+        <v>198.75316421543269</v>
       </c>
       <c r="K5" s="242" t="s">
         <v>436</v>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="F6" s="186">
         <f ca="1">Statement!AC148</f>
-        <v>30.354729565508791</v>
+        <v>29.681809884561535</v>
       </c>
       <c r="H6" s="181" t="str">
         <f>'AVG target price'!B8</f>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="I6" s="207">
         <f>'AVG target price'!C8</f>
-        <v>247.82365364889631</v>
+        <v>247.29944052899336</v>
       </c>
       <c r="K6" s="243" t="s">
         <v>437</v>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="I7" s="207">
         <f>'AVG target price'!C9</f>
-        <v>247.81384924656501</v>
+        <v>247.28963612666203</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="I8" s="208">
         <f>'AVG target price'!C10</f>
-        <v>206.65982613627867</v>
+        <v>207.02759688477386</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="F9" s="188">
         <f ca="1">Statement!AC160</f>
-        <v>3.2943795392473905E-2</v>
+        <v>3.3690667917124967E-2</v>
       </c>
       <c r="H9" s="180" t="str">
         <f>'AVG target price'!B12</f>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="I9" s="209">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.43552531715528486</v>
+        <v>-0.43452078095442942</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F12" s="188">
         <f>Statement!AC121</f>
-        <v>0.32656787695765149</v>
+        <v>0.33394199030830818</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="F13" s="188">
         <f>Statement!AC123</f>
-        <v>0.49743260590500638</v>
+        <v>0.50866495507060328</v>
       </c>
       <c r="H13" s="246" t="s">
         <v>430</v>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="F14" s="189">
         <f>Statement!AC138</f>
-        <v>0.53461952829149839</v>
+        <v>0.54669158215614522</v>
       </c>
       <c r="H14" s="182" t="s">
         <v>440</v>
@@ -14328,7 +14328,7 @@
         <v>387</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
@@ -18694,11 +18694,11 @@
       </c>
       <c r="I44" s="123">
         <f t="shared" si="13"/>
-        <v>0.90909090909090917</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="J44" s="123">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.91666666666666674</v>
       </c>
       <c r="K44" s="123">
         <f t="shared" si="13"/>
@@ -18739,11 +18739,11 @@
       </c>
       <c r="I45" s="25">
         <f>I7*I46</f>
-        <v>1398.692631875</v>
+        <v>1525.8465074999999</v>
       </c>
       <c r="J45" s="25">
         <f>J7*J46</f>
-        <v>1470.0397860293749</v>
+        <v>1603.6797665774998</v>
       </c>
       <c r="K45" s="25">
         <f>K7*K46</f>
@@ -18782,10 +18782,10 @@
         <v>5.5E-2</v>
       </c>
       <c r="I46" s="97">
-        <v>5.5E-2</v>
+        <v>0.06</v>
       </c>
       <c r="J46" s="97">
-        <v>5.5E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K46" s="97">
         <v>0.05</v>
@@ -18796,6 +18796,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18803,12 +18809,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19503,11 +19503,11 @@
       </c>
       <c r="I21" s="88">
         <f>'WC &amp; Investments'!I45</f>
-        <v>1398.692631875</v>
+        <v>1525.8465074999999</v>
       </c>
       <c r="J21" s="88">
         <f>'WC &amp; Investments'!J45</f>
-        <v>1470.0397860293749</v>
+        <v>1603.6797665774998</v>
       </c>
       <c r="K21" s="88">
         <f>'WC &amp; Investments'!K45</f>
@@ -19703,11 +19703,11 @@
       </c>
       <c r="I28" s="94">
         <f t="shared" si="7"/>
-        <v>6999.9449575226045</v>
+        <v>6872.7910818976034</v>
       </c>
       <c r="J28" s="94">
         <f t="shared" si="7"/>
-        <v>6535.4559104403033</v>
+        <v>6401.8159298921782</v>
       </c>
       <c r="K28" s="94">
         <f t="shared" si="7"/>
@@ -19869,16 +19869,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20306,11 +20306,11 @@
       </c>
       <c r="I7" s="112">
         <f>'FCF &amp; Other'!I28</f>
-        <v>6999.9449575226045</v>
+        <v>6872.7910818976034</v>
       </c>
       <c r="J7" s="112">
         <f>'FCF &amp; Other'!J28</f>
-        <v>6535.4559104403033</v>
+        <v>6401.8159298921782</v>
       </c>
       <c r="K7" s="112">
         <f>'FCF &amp; Other'!K28</f>
@@ -20426,11 +20426,11 @@
       </c>
       <c r="I10" s="126">
         <f t="shared" ref="I10:L10" si="0">I7/(1+$C$15)^I9</f>
-        <v>5785.0784772914076</v>
+        <v>5679.9926296674403</v>
       </c>
       <c r="J10" s="126">
         <f t="shared" si="0"/>
-        <v>4910.1847561534951</v>
+        <v>4809.7790607754896</v>
       </c>
       <c r="K10" s="126">
         <f t="shared" si="0"/>
@@ -20495,7 +20495,7 @@
       </c>
       <c r="C19" s="64">
         <f>SUM(H10:L10)</f>
-        <v>21293.79229658049</v>
+        <v>21088.300753578515</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="C21" s="94">
         <f>C19+C20</f>
-        <v>52311.236975198612</v>
+        <v>52105.745432196636</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="C24" s="94">
         <f>C21+C22-C23</f>
-        <v>52836.236975198612</v>
+        <v>52630.745432196636</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="C26" s="239">
         <f>C24/C25</f>
-        <v>134.78631881428217</v>
+        <v>134.26210569437919</v>
       </c>
     </row>
   </sheetData>
@@ -20801,11 +20801,11 @@
       </c>
       <c r="I8" s="92">
         <f>'FCF &amp; Other'!I28</f>
-        <v>6999.9449575226045</v>
+        <v>6872.7910818976034</v>
       </c>
       <c r="J8" s="92">
         <f>'FCF &amp; Other'!J28</f>
-        <v>6535.4559104403033</v>
+        <v>6401.8159298921782</v>
       </c>
       <c r="K8" s="92">
         <f>'FCF &amp; Other'!K28</f>
@@ -20832,11 +20832,11 @@
       </c>
       <c r="I9" s="92">
         <f>DCF!I10</f>
-        <v>5785.0784772914076</v>
+        <v>5679.9926296674403</v>
       </c>
       <c r="J9" s="92">
         <f>DCF!J10</f>
-        <v>4910.1847561534951</v>
+        <v>4809.7790607754896</v>
       </c>
       <c r="K9" s="92">
         <f>DCF!K10</f>
@@ -21031,15 +21031,15 @@
       </c>
       <c r="I15" s="95">
         <f t="shared" si="3"/>
-        <v>0.57994166764899646</v>
+        <v>0.55124205536317394</v>
       </c>
       <c r="J15" s="95">
         <f t="shared" si="3"/>
-        <v>-6.635609992663305E-2</v>
+        <v>-6.8527494345919662E-2</v>
       </c>
       <c r="K15" s="95">
         <f t="shared" si="3"/>
-        <v>-0.10989062360877787</v>
+        <v>-9.1309302144786608E-2</v>
       </c>
       <c r="L15" s="95">
         <f t="shared" si="3"/>
@@ -21142,15 +21142,15 @@
       </c>
       <c r="J19" s="141">
         <f t="shared" si="5"/>
-        <v>378.49314662273468</v>
+        <v>374.70821515650732</v>
       </c>
       <c r="K19" s="141">
         <f t="shared" si="5"/>
-        <v>378.49314662273468</v>
+        <v>374.70821515650732</v>
       </c>
       <c r="L19" s="141">
         <f t="shared" si="5"/>
-        <v>382.27807808896205</v>
+        <v>374.70821515650732</v>
       </c>
       <c r="N19" s="91"/>
     </row>
@@ -21182,13 +21182,13 @@
         <v>-0.01</v>
       </c>
       <c r="J20" s="97">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="K20" s="97">
         <v>0</v>
       </c>
       <c r="L20" s="97">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="N20" s="91"/>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="C45" s="108">
         <f>SUM(H9:K9)+C44</f>
-        <v>81033.677583495504</v>
+        <v>80828.186040493543</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C48" s="108">
         <f>C45+C46-C47</f>
-        <v>81558.677583495504</v>
+        <v>81353.186040493543</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21704,7 +21704,7 @@
       </c>
       <c r="C50" s="239">
         <f>C48/C49</f>
-        <v>208.05785097830486</v>
+        <v>207.5336378584019</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="C56" s="24">
         <f>L19</f>
-        <v>382.27807808896205</v>
+        <v>374.70821515650732</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
@@ -21754,7 +21754,7 @@
       </c>
       <c r="C57" s="24">
         <f>(C53*C55)/C56</f>
-        <v>328.27874634753761</v>
+        <v>334.91064021314446</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="C58" s="239">
         <f>C57/(1+C54)^5</f>
-        <v>194.8174579933449</v>
+        <v>198.75316421543269</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21822,7 +21822,7 @@
       </c>
       <c r="C66" s="108">
         <f>SUM(H9:K9)+C65</f>
-        <v>96621.872230367357</v>
+        <v>96416.380687365396</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="C69" s="108">
         <f>C66+C67-C68</f>
-        <v>97146.872230367357</v>
+        <v>96941.380687365396</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21867,7 +21867,7 @@
       </c>
       <c r="C71" s="239">
         <f>C69/C70</f>
-        <v>247.82365364889631</v>
+        <v>247.29944052899336</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="C79" s="108">
         <f>SUM(H9:K9)+C78</f>
-        <v>96618.028904653489</v>
+        <v>96412.537361651513</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="C82" s="108">
         <f>C79+C80-C81</f>
-        <v>97143.028904653489</v>
+        <v>96937.537361651513</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21971,22 +21971,22 @@
       </c>
       <c r="C84" s="239">
         <f>C82/C83</f>
-        <v>247.81384924656501</v>
+        <v>247.28963612666203</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22037,7 +22037,7 @@
       </c>
       <c r="C5" s="133">
         <f>DCF!C26</f>
-        <v>134.78631881428217</v>
+        <v>134.26210569437919</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="C6" s="133">
         <f>Multiples!C50</f>
-        <v>208.05785097830486</v>
+        <v>207.5336378584019</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -22055,7 +22055,7 @@
       </c>
       <c r="C7" s="133">
         <f>Multiples!C58</f>
-        <v>194.8174579933449</v>
+        <v>198.75316421543269</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="C8" s="133">
         <f>Multiples!C71</f>
-        <v>247.82365364889631</v>
+        <v>247.29944052899336</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="C9" s="133">
         <f>Multiples!C84</f>
-        <v>247.81384924656501</v>
+        <v>247.28963612666203</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="C10" s="239">
         <f>AVERAGE(C5:C9)</f>
-        <v>206.65982613627867</v>
+        <v>207.02759688477386</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C12" s="152">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.43552531715528486</v>
+        <v>-0.43452078095442942</v>
       </c>
     </row>
   </sheetData>
@@ -22959,10 +22959,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="262" t="s">
+      <c r="B14" s="263" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="263"/>
+      <c r="C14" s="264"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="153" t="s">
@@ -22989,20 +22989,20 @@
       <c r="C17" s="156">
         <v>0.35499999999999998</v>
       </c>
-      <c r="E17" s="264" t="s">
+      <c r="E17" s="262" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="264"/>
-      <c r="G17" s="264"/>
-      <c r="H17" s="264"/>
-      <c r="I17" s="264"/>
+      <c r="F17" s="262"/>
+      <c r="G17" s="262"/>
+      <c r="H17" s="262"/>
+      <c r="I17" s="262"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="262" t="s">
+      <c r="B19" s="263" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="263"/>
+      <c r="C19" s="264"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="157" t="s">
@@ -23068,10 +23068,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="262" t="s">
+      <c r="B28" s="263" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="263"/>
+      <c r="C28" s="264"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="157" t="s">
@@ -23147,16 +23147,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -24039,11 +24039,11 @@
         <v>-263</v>
       </c>
       <c r="AA15" s="62">
-        <v>-364</v>
+        <v>-259</v>
       </c>
       <c r="AC15" s="62">
         <f t="shared" si="0"/>
-        <v>-976</v>
+        <v>-871</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
@@ -24163,12 +24163,12 @@
         <v>1296</v>
       </c>
       <c r="AA17" s="18">
-        <v>1674</v>
+        <v>1779</v>
       </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="61">
         <f t="shared" si="0"/>
-        <v>4650</v>
+        <v>4755</v>
       </c>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
@@ -24550,11 +24550,11 @@
         <v>3.7028571428571428</v>
       </c>
       <c r="AA22" s="26">
-        <v>4.5737704918032787</v>
+        <v>4.860655737704918</v>
       </c>
       <c r="AC22" s="26">
         <f>SUM(X22:AA22)</f>
-        <v>13.195013530975011</v>
+        <v>13.481898776876651</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
@@ -24624,11 +24624,11 @@
       </c>
       <c r="AA23" s="65">
         <f t="shared" si="15"/>
-        <v>4.5737704918032787</v>
+        <v>4.860655737704918</v>
       </c>
       <c r="AC23" s="65">
         <f>AC22/AC$84</f>
-        <v>13.195013530975011</v>
+        <v>13.481898776876651</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
@@ -24684,11 +24684,11 @@
         <v>3.3316195372750643</v>
       </c>
       <c r="AA24" s="26">
-        <v>4.359375</v>
+        <v>4.6328125</v>
       </c>
       <c r="AC24" s="26">
         <f>SUM(X24:AA24)</f>
-        <v>12.061052931138622</v>
+        <v>12.334490431138622</v>
       </c>
     </row>
     <row r="25" spans="1:31" s="30" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -24761,12 +24761,12 @@
       </c>
       <c r="AA25" s="66">
         <f t="shared" si="18"/>
-        <v>4.359375</v>
+        <v>4.6328125</v>
       </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="66">
         <f>AC24/AC$84</f>
-        <v>12.061052931138622</v>
+        <v>12.334490431138622</v>
       </c>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
@@ -27184,11 +27184,11 @@
       </c>
       <c r="AA68" s="64">
         <f t="shared" ref="AA68:AC68" si="32">AA5-AA6-AA10+AA12+AA13+AA15-AA16</f>
-        <v>1674</v>
+        <v>1779</v>
       </c>
       <c r="AC68" s="64">
         <f t="shared" si="32"/>
-        <v>4650</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="69" spans="1:31" s="41" customFormat="1" x14ac:dyDescent="0.2">
@@ -28089,11 +28089,11 @@
       </c>
       <c r="AA82" s="46">
         <f t="shared" si="61"/>
-        <v>0.17860647693817469</v>
+        <v>0.12708537782139354</v>
       </c>
       <c r="AC82" s="46">
         <f>IF(AND(AC14&gt;0,AC15&lt;0),-(AC15)/AC14,0)</f>
-        <v>0.17348027017419126</v>
+        <v>0.15481692143618911</v>
       </c>
     </row>
     <row r="83" spans="1:31" x14ac:dyDescent="0.2">
@@ -29001,7 +29001,7 @@
 IF(AA17=0,0,IF(AA17&gt;0,1,-1)),
 (AA17-Z17)/ABS(Z17)
 )</f>
-        <v>0.29166666666666669</v>
+        <v>0.37268518518518517</v>
       </c>
       <c r="AB96" s="1"/>
       <c r="AC96" s="67"/>
@@ -29240,12 +29240,12 @@
       </c>
       <c r="AA101" s="55">
         <f t="shared" si="105"/>
-        <v>0.38210454234193109</v>
+        <v>0.40607167313398768</v>
       </c>
       <c r="AB101" s="1"/>
       <c r="AC101" s="55">
         <f>AC109/AC5</f>
-        <v>0.32108824747962988</v>
+        <v>0.32833862726142798</v>
       </c>
       <c r="AD101" s="1"/>
       <c r="AE101" s="1"/>
@@ -29358,11 +29358,11 @@
       </c>
       <c r="AA104" s="81">
         <f t="shared" si="109"/>
-        <v>0.17860647693817469</v>
+        <v>0.12708537782139354</v>
       </c>
       <c r="AC104" s="81">
         <f>IF(AND(AC82&gt;=0,AC11&gt;=0),AC82,0)</f>
-        <v>0.17348027017419126</v>
+        <v>0.15481692143618911</v>
       </c>
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.2">
@@ -29578,7 +29578,7 @@
       <c r="AA107" s="67"/>
       <c r="AC107" s="25">
         <f>AC11*(1-AC104)</f>
-        <v>4716.9480981158904</v>
+        <v>4823.4598293636691</v>
       </c>
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.2">
@@ -29722,11 +29722,11 @@
       </c>
       <c r="AA109" s="126">
         <f t="shared" si="122"/>
-        <v>1674</v>
+        <v>1779</v>
       </c>
       <c r="AC109" s="126">
         <f>AC16+AC17</f>
-        <v>4650</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
@@ -30032,7 +30032,7 @@
       <c r="AA119" s="77"/>
       <c r="AC119" s="74">
         <f>AC109/AC5</f>
-        <v>0.32108824747962988</v>
+        <v>0.32833862726142798</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -30114,7 +30114,7 @@
       <c r="AA121" s="79"/>
       <c r="AC121" s="76">
         <f>AC119*AC120</f>
-        <v>0.32656787695765149</v>
+        <v>0.33394199030830818</v>
       </c>
     </row>
     <row r="122" spans="1:31" x14ac:dyDescent="0.2">
@@ -30196,7 +30196,7 @@
       <c r="AA123" s="79"/>
       <c r="AC123" s="76">
         <f>AC121*AC122</f>
-        <v>0.49743260590500638</v>
+        <v>0.50866495507060328</v>
       </c>
     </row>
     <row r="125" spans="1:31" x14ac:dyDescent="0.2">
@@ -30562,7 +30562,7 @@
       </c>
       <c r="Z133" s="225">
         <f t="shared" ref="Z133" si="149">AA24</f>
-        <v>4.359375</v>
+        <v>4.6328125</v>
       </c>
       <c r="AA133" s="225">
         <f t="shared" ref="AA133" si="150">AB24</f>
@@ -30702,7 +30702,7 @@
       <c r="AA138" s="49"/>
       <c r="AC138" s="81">
         <f>AC107/(AC106+AC110-AC105)</f>
-        <v>0.53461952829149839</v>
+        <v>0.54669158215614522</v>
       </c>
     </row>
     <row r="139" spans="2:29" x14ac:dyDescent="0.2">
@@ -31328,7 +31328,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>30.354729565508791</v>
+        <v>29.681809884561535</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -31752,7 +31752,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="64">
         <f t="shared" ref="AC156" si="194">AC107+AC52+AC108+AC54+AC56+AC57+AC55</f>
-        <v>3645.9480981158904</v>
+        <v>3752.4598293636691</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31834,7 +31834,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="197"/>
-        <v>39.218912653718995</v>
+        <v>38.105703059384339</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31916,7 +31916,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.2943795392473905E-2</v>
+        <v>3.3690667917124967E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -32080,7 +32080,7 @@
       <c r="AA164" s="49"/>
       <c r="AC164" s="152">
         <f>AC156/AC5</f>
-        <v>0.25175722262918732</v>
+        <v>0.25911198932217022</v>
       </c>
     </row>
     <row r="165" spans="2:29" x14ac:dyDescent="0.2">
@@ -34139,7 +34139,7 @@
       </c>
       <c r="C8" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>30.354729565508791</v>
+        <v>29.681809884561535</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -34234,7 +34234,7 @@
       </c>
       <c r="F16" s="169">
         <f>Statement!AC17</f>
-        <v>4650</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -34259,14 +34259,14 @@
       </c>
       <c r="C18" s="171">
         <f>Statement!AC101</f>
-        <v>0.32108824747962988</v>
+        <v>0.32833862726142798</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>253</v>
       </c>
       <c r="F18" s="173">
         <f>IF(OR(F16&lt;=0, F17&lt;=0),"N/A",F16-F17)</f>
-        <v>-211</v>
+        <v>-106</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -34285,14 +34285,14 @@
       </c>
       <c r="C22" s="171">
         <f>Statement!AC119</f>
-        <v>0.32108824747962988</v>
+        <v>0.32833862726142798</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>101</v>
       </c>
       <c r="F22" s="171">
         <f>C24</f>
-        <v>0.32656787695765149</v>
+        <v>0.33394199030830818</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="F23" s="171">
         <f>C26</f>
-        <v>0.49743260590500638</v>
+        <v>0.50866495507060328</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
@@ -34317,14 +34317,14 @@
       </c>
       <c r="C24" s="172">
         <f>Statement!AC121</f>
-        <v>0.32656787695765149</v>
+        <v>0.33394199030830818</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>104</v>
       </c>
       <c r="F24" s="171">
         <f>Statement!AC138</f>
-        <v>0.53461952829149839</v>
+        <v>0.54669158215614522</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
@@ -34342,7 +34342,7 @@
       </c>
       <c r="C26" s="172">
         <f>Statement!AC123</f>
-        <v>0.49743260590500638</v>
+        <v>0.50866495507060328</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="C38" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>3.2943795392473905E-2</v>
+        <v>3.3690667917124967E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -34601,7 +34601,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B57" s="250" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C57" s="250"/>
     </row>
@@ -34620,21 +34620,21 @@
       </c>
       <c r="C59" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>39.218912653718995</v>
+        <v>38.105703059384339</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C60" s="171">
         <f>Statement!AC164</f>
-        <v>0.25175722262918732</v>
+        <v>0.25911198932217022</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="20" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C61" s="171">
         <f>Statement!AC165</f>
@@ -34855,7 +34855,7 @@
       </c>
       <c r="I9" s="170">
         <f ca="1">Statement!AC148</f>
-        <v>30.354729565508791</v>
+        <v>29.681809884561535</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -35069,7 +35069,7 @@
       </c>
       <c r="I18" s="171">
         <f>Statement!AC101</f>
-        <v>0.32108824747962988</v>
+        <v>0.32833862726142798</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35109,7 +35109,7 @@
       </c>
       <c r="I21" s="173">
         <f>Statement!AC17</f>
-        <v>4650</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -35167,7 +35167,7 @@
       </c>
       <c r="I23" s="191">
         <f t="shared" si="0"/>
-        <v>-211</v>
+        <v>-106</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35207,7 +35207,7 @@
       </c>
       <c r="I26" s="171">
         <f>Statement!AC119</f>
-        <v>0.32108824747962988</v>
+        <v>0.32833862726142798</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="I28" s="172">
         <f>Statement!AC121</f>
-        <v>0.32656787695765149</v>
+        <v>0.33394199030830818</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
@@ -35323,7 +35323,7 @@
       </c>
       <c r="I30" s="172">
         <f>Statement!AC123</f>
-        <v>0.49743260590500638</v>
+        <v>0.50866495507060328</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35363,7 +35363,7 @@
       </c>
       <c r="I33" s="171">
         <f>I28</f>
-        <v>0.32656787695765149</v>
+        <v>0.33394199030830818</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
@@ -35392,7 +35392,7 @@
       </c>
       <c r="I34" s="171">
         <f>I30</f>
-        <v>0.49743260590500638</v>
+        <v>0.50866495507060328</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
@@ -35421,7 +35421,7 @@
       </c>
       <c r="I35" s="171">
         <f>Statement!AC138</f>
-        <v>0.53461952829149839</v>
+        <v>0.54669158215614522</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35744,7 +35744,7 @@
       </c>
       <c r="I51" s="171">
         <f ca="1">Statement!AC160</f>
-        <v>3.2943795392473905E-2</v>
+        <v>3.3690667917124967E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -36435,7 +36435,7 @@
     </row>
     <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B87" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -36499,12 +36499,12 @@
       </c>
       <c r="I89" s="170">
         <f ca="1">Statement!AC158</f>
-        <v>39.218912653718995</v>
+        <v>38.105703059384339</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B90" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C90" s="171">
         <f>Statement!M164</f>
@@ -36528,12 +36528,12 @@
       </c>
       <c r="I90" s="171">
         <f>Statement!AC164</f>
-        <v>0.25175722262918732</v>
+        <v>0.25911198932217022</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B91" s="20" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C91" s="171">
         <f>Statement!M165</f>
@@ -36562,7 +36562,7 @@
     </row>
     <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B93" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -36713,14 +36713,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="253" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="F3" s="253" t="s">
+      <c r="D3" s="254"/>
+      <c r="F3" s="255" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="252"/>
+      <c r="G3" s="254"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36787,19 +36787,19 @@
       <c r="B7" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="254">
+      <c r="C7" s="251">
         <f>Statement!AA88</f>
         <v>0.16920202828929812</v>
       </c>
-      <c r="D7" s="255"/>
-      <c r="F7" s="254">
+      <c r="D7" s="252"/>
+      <c r="F7" s="251">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.55464868701206527</v>
       </c>
-      <c r="G7" s="255"/>
+      <c r="G7" s="252"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="203" t="s">
@@ -36826,19 +36826,19 @@
       <c r="B9" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="254">
+      <c r="C9" s="251">
         <f>Statement!AA89</f>
         <v>7.4461896451425244E-2</v>
       </c>
-      <c r="D9" s="255"/>
-      <c r="F9" s="254">
+      <c r="D9" s="252"/>
+      <c r="F9" s="251">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.16090509113764928</v>
       </c>
-      <c r="G9" s="255"/>
+      <c r="G9" s="252"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="203" t="s">
@@ -36865,19 +36865,19 @@
       <c r="B11" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="254">
+      <c r="C11" s="251">
         <f>Statement!AA90</f>
         <v>0.2495069033530572</v>
       </c>
-      <c r="D11" s="255"/>
-      <c r="F11" s="254">
+      <c r="D11" s="252"/>
+      <c r="F11" s="251">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>1.0651996740016301</v>
       </c>
-      <c r="G11" s="255"/>
+      <c r="G11" s="252"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="203" t="s">
@@ -36904,19 +36904,19 @@
       <c r="B13" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="254">
+      <c r="C13" s="251">
         <f>Statement!AA93</f>
         <v>4.9462365591397849E-2</v>
       </c>
-      <c r="D13" s="255"/>
-      <c r="F13" s="254">
+      <c r="D13" s="252"/>
+      <c r="F13" s="251">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>0.12183908045977011</v>
       </c>
-      <c r="G13" s="255"/>
+      <c r="G13" s="252"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="203" t="s">
@@ -36943,19 +36943,19 @@
       <c r="B15" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="254">
+      <c r="C15" s="251">
         <f>Statement!AA94</f>
         <v>0.30902111324376197</v>
       </c>
-      <c r="D15" s="255"/>
-      <c r="F15" s="254">
+      <c r="D15" s="252"/>
+      <c r="F15" s="251">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5833333333333333</v>
       </c>
-      <c r="G15" s="255"/>
+      <c r="G15" s="252"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="203" t="s">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="D16" s="194">
         <f>Statement!AA17</f>
-        <v>1674</v>
+        <v>1779</v>
       </c>
       <c r="F16" s="196">
         <f>Statement!W17</f>
@@ -36975,26 +36975,26 @@
       </c>
       <c r="G16" s="194">
         <f>Statement!AA17</f>
-        <v>1674</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="254">
+      <c r="C17" s="251">
         <f>Statement!AA96</f>
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="D17" s="255"/>
-      <c r="F17" s="254">
+        <v>0.37268518518518517</v>
+      </c>
+      <c r="D17" s="252"/>
+      <c r="F17" s="251">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
-        <v>1.8517887563884157</v>
-      </c>
-      <c r="G17" s="255"/>
+        <v>2.0306643952299828</v>
+      </c>
+      <c r="G17" s="252"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="203" t="s">
@@ -37021,22 +37021,22 @@
       <c r="B19" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="254">
+      <c r="C19" s="251">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-1.2853470437017995E-2</v>
       </c>
-      <c r="D19" s="255"/>
-      <c r="F19" s="254">
+      <c r="D19" s="252"/>
+      <c r="F19" s="251">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>2.1276595744680851E-2</v>
       </c>
-      <c r="G19" s="255"/>
+      <c r="G19" s="252"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="203" t="s">
@@ -37048,7 +37048,7 @@
       </c>
       <c r="D20" s="198">
         <f>Statement!AA25</f>
-        <v>4.359375</v>
+        <v>4.6328125</v>
       </c>
       <c r="F20" s="197">
         <f>Statement!W25</f>
@@ -37056,29 +37056,29 @@
       </c>
       <c r="G20" s="198">
         <f>Statement!AA25</f>
-        <v>4.359375</v>
+        <v>4.6328125</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="254">
+      <c r="C21" s="251">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
-        <v>0.30848524305555552</v>
-      </c>
-      <c r="D21" s="255"/>
-      <c r="F21" s="254">
+        <v>0.39055869020061729</v>
+      </c>
+      <c r="D21" s="252"/>
+      <c r="F21" s="251">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
-        <v>1.7923764906303237</v>
-      </c>
-      <c r="G21" s="255"/>
+        <v>1.9675255536626917</v>
+      </c>
+      <c r="G21" s="252"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37127,22 +37127,22 @@
       <c r="B25" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="254">
+      <c r="C25" s="251">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.15600599700149931</v>
       </c>
-      <c r="D25" s="255"/>
-      <c r="F25" s="254">
+      <c r="D25" s="252"/>
+      <c r="F25" s="251">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.53596812749003997</v>
       </c>
-      <c r="G25" s="255"/>
+      <c r="G25" s="252"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -37170,22 +37170,22 @@
       <c r="B27" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="254">
+      <c r="C27" s="251">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.36297777777777784</v>
       </c>
-      <c r="D27" s="255"/>
-      <c r="F27" s="254">
+      <c r="D27" s="252"/>
+      <c r="F27" s="251">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>1.1004794520547947</v>
       </c>
-      <c r="G27" s="255"/>
+      <c r="G27" s="252"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="str">
@@ -37213,49 +37213,49 @@
       <c r="B29" s="202" t="s">
         <v>314</v>
       </c>
-      <c r="C29" s="254">
+      <c r="C29" s="251">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.17139037433155085</v>
       </c>
-      <c r="D29" s="255"/>
-      <c r="F29" s="254">
+      <c r="D29" s="252"/>
+      <c r="F29" s="251">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.35216049382716058</v>
       </c>
-      <c r="G29" s="255"/>
+      <c r="G29" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -38324,7 +38324,7 @@
       </c>
       <c r="J59" s="64">
         <f>Statement!AA17</f>
-        <v>1674</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.2">
@@ -38435,7 +38435,7 @@
       </c>
       <c r="J62" s="58">
         <f>Statement!AA101</f>
-        <v>0.38210454234193109</v>
+        <v>0.40607167313398768</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.2">
